--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -550,22 +550,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>81000</v>
+        <v>54000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
       </c>
       <c r="Q4" t="n">
-        <v>60000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="5">
@@ -1329,22 +1329,22 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
         <v>27000</v>
       </c>
       <c r="O23" t="n">
-        <v>108000</v>
+        <v>81000</v>
       </c>
       <c r="P23" t="n">
         <v>20000</v>
       </c>
       <c r="Q23" t="n">
-        <v>80000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="24">
@@ -3730,10 +3730,10 @@
         <v>8</v>
       </c>
       <c r="N80" t="n">
-        <v>22267.552777778</v>
+        <v>26721.063333333</v>
       </c>
       <c r="O80" t="n">
-        <v>178140.422222224</v>
+        <v>213768.506666664</v>
       </c>
       <c r="P80" t="n">
         <v>46300</v>
@@ -4357,10 +4357,10 @@
         <v>3</v>
       </c>
       <c r="N95" t="n">
-        <v>61666.874171271</v>
+        <v>62706.203511236</v>
       </c>
       <c r="O95" t="n">
-        <v>185000.622513813</v>
+        <v>188118.610533708</v>
       </c>
       <c r="P95" t="n">
         <v>98900</v>
@@ -11373,10 +11373,10 @@
         <v>8</v>
       </c>
       <c r="N253" t="n">
-        <v>2582.2551367187</v>
+        <v>2582.2551307749</v>
       </c>
       <c r="O253" t="n">
-        <v>20658.0410937496</v>
+        <v>20658.0410461992</v>
       </c>
       <c r="P253" t="n">
         <v>4500</v>
@@ -13646,22 +13646,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N303" t="n">
         <v>2953.73</v>
       </c>
       <c r="O303" t="n">
-        <v>135871.58</v>
+        <v>132917.85</v>
       </c>
       <c r="P303" t="n">
         <v>4900</v>
       </c>
       <c r="Q303" t="n">
-        <v>225400</v>
+        <v>220500</v>
       </c>
     </row>
     <row r="304">
@@ -16259,10 +16259,10 @@
         <v>17</v>
       </c>
       <c r="N361" t="n">
-        <v>11921.4</v>
+        <v>11949.761776368</v>
       </c>
       <c r="O361" t="n">
-        <v>202663.8</v>
+        <v>203145.950198256</v>
       </c>
       <c r="P361" t="n">
         <v>19900</v>
@@ -16754,10 +16754,10 @@
         <v>183</v>
       </c>
       <c r="N372" t="n">
-        <v>1630.9242345815</v>
+        <v>1630.9242415885</v>
       </c>
       <c r="O372" t="n">
-        <v>298459.1349284145</v>
+        <v>298459.1362106955</v>
       </c>
       <c r="P372" t="n">
         <v>2500</v>
@@ -16984,10 +16984,10 @@
         <v>45</v>
       </c>
       <c r="N377" t="n">
-        <v>2403.516914488</v>
+        <v>2403.5169237057</v>
       </c>
       <c r="O377" t="n">
-        <v>108158.26115196</v>
+        <v>108158.2615667565</v>
       </c>
       <c r="P377" t="n">
         <v>3500</v>
@@ -19326,22 +19326,22 @@
         <v>0</v>
       </c>
       <c r="L430" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M430" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N430" t="n">
-        <v>5449.5305454545</v>
+        <v>5449.5305504587</v>
       </c>
       <c r="O430" t="n">
-        <v>27247.6527272725</v>
+        <v>21798.1222018348</v>
       </c>
       <c r="P430" t="n">
         <v>6200</v>
       </c>
       <c r="Q430" t="n">
-        <v>31000</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="431">
@@ -19995,22 +19995,22 @@
         <v>0</v>
       </c>
       <c r="L446" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M446" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N446" t="n">
         <v>14060.64</v>
       </c>
       <c r="O446" t="n">
-        <v>126545.76</v>
+        <v>112485.12</v>
       </c>
       <c r="P446" t="n">
         <v>22900</v>
       </c>
       <c r="Q446" t="n">
-        <v>206100</v>
+        <v>183200</v>
       </c>
     </row>
     <row r="447">
@@ -21261,10 +21261,10 @@
         <v>1</v>
       </c>
       <c r="N475" t="n">
-        <v>16974.69</v>
+        <v>17078.829202454</v>
       </c>
       <c r="O475" t="n">
-        <v>16974.69</v>
+        <v>17078.829202454</v>
       </c>
       <c r="P475" t="n">
         <v>26900</v>
@@ -23366,10 +23366,10 @@
         <v>20</v>
       </c>
       <c r="N523" t="n">
-        <v>7700</v>
+        <v>7812.5456760049</v>
       </c>
       <c r="O523" t="n">
-        <v>154000</v>
+        <v>156250.913520098</v>
       </c>
       <c r="P523" t="n">
         <v>13900</v>
@@ -23820,22 +23820,22 @@
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M533" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N533" t="n">
-        <v>5218.1705812417</v>
+        <v>5218.1705827815</v>
       </c>
       <c r="O533" t="n">
-        <v>78272.5587186255</v>
+        <v>67836.2175761595</v>
       </c>
       <c r="P533" t="n">
         <v>8500</v>
       </c>
       <c r="Q533" t="n">
-        <v>127500</v>
+        <v>110500</v>
       </c>
     </row>
     <row r="534">
@@ -27273,22 +27273,22 @@
         <v>0</v>
       </c>
       <c r="L608" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M608" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N608" t="n">
         <v>28720</v>
       </c>
       <c r="O608" t="n">
-        <v>287200</v>
+        <v>258480</v>
       </c>
       <c r="P608" t="n">
         <v>35900</v>
       </c>
       <c r="Q608" t="n">
-        <v>359000</v>
+        <v>323100</v>
       </c>
     </row>
     <row r="609">
@@ -27874,22 +27874,22 @@
         <v>0</v>
       </c>
       <c r="L621" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M621" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N621" t="n">
         <v>13922</v>
       </c>
       <c r="O621" t="n">
-        <v>264518</v>
+        <v>250596</v>
       </c>
       <c r="P621" t="n">
         <v>22900</v>
       </c>
       <c r="Q621" t="n">
-        <v>435100</v>
+        <v>412200</v>
       </c>
     </row>
     <row r="622">
@@ -30167,22 +30167,22 @@
         <v>0</v>
       </c>
       <c r="L671" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M671" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N671" t="n">
         <v>5215</v>
       </c>
       <c r="O671" t="n">
-        <v>307685</v>
+        <v>302470</v>
       </c>
       <c r="P671" t="n">
         <v>8900</v>
       </c>
       <c r="Q671" t="n">
-        <v>525100</v>
+        <v>516200</v>
       </c>
     </row>
     <row r="672">
@@ -31044,22 +31044,22 @@
         <v>0</v>
       </c>
       <c r="L690" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M690" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N690" t="n">
-        <v>1516.0387516479</v>
+        <v>1516.0387513947</v>
       </c>
       <c r="O690" t="n">
-        <v>51545.3175560286</v>
+        <v>48513.2400446304</v>
       </c>
       <c r="P690" t="n">
         <v>2300</v>
       </c>
       <c r="Q690" t="n">
-        <v>78200</v>
+        <v>73600</v>
       </c>
     </row>
     <row r="691">
@@ -32017,10 +32017,10 @@
         <v>1</v>
       </c>
       <c r="N711" t="n">
-        <v>3033.6882666667</v>
+        <v>3033.6856944444</v>
       </c>
       <c r="O711" t="n">
-        <v>3033.6882666667</v>
+        <v>3033.6856944444</v>
       </c>
       <c r="P711" t="n">
         <v>4500</v>
@@ -32374,22 +32374,22 @@
         <v>0</v>
       </c>
       <c r="L719" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M719" t="n">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="N719" t="n">
         <v>1801</v>
       </c>
       <c r="O719" t="n">
-        <v>590728</v>
+        <v>547504</v>
       </c>
       <c r="P719" t="n">
         <v>2900</v>
       </c>
       <c r="Q719" t="n">
-        <v>951200</v>
+        <v>881600</v>
       </c>
     </row>
     <row r="720">
@@ -36351,22 +36351,22 @@
         <v>0</v>
       </c>
       <c r="L804" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M804" t="n">
-        <v>246</v>
+        <v>186</v>
       </c>
       <c r="N804" t="n">
-        <v>517.29416017244</v>
+        <v>517.81142476254</v>
       </c>
       <c r="O804" t="n">
-        <v>127254.3634024202</v>
+        <v>96312.92500583244</v>
       </c>
       <c r="P804" t="n">
         <v>900</v>
       </c>
       <c r="Q804" t="n">
-        <v>221400</v>
+        <v>167400</v>
       </c>
     </row>
     <row r="805">
@@ -36446,22 +36446,22 @@
         <v>0</v>
       </c>
       <c r="L806" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M806" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N806" t="n">
         <v>2571.14</v>
       </c>
       <c r="O806" t="n">
-        <v>30853.68</v>
+        <v>28282.54</v>
       </c>
       <c r="P806" t="n">
         <v>6900</v>
       </c>
       <c r="Q806" t="n">
-        <v>82800</v>
+        <v>75900</v>
       </c>
     </row>
     <row r="807">
@@ -37193,10 +37193,10 @@
         <v>239</v>
       </c>
       <c r="N822" t="n">
-        <v>703.79482873668</v>
+        <v>703.79482793718</v>
       </c>
       <c r="O822" t="n">
-        <v>168206.9640680665</v>
+        <v>168206.963876986</v>
       </c>
       <c r="P822" t="n">
         <v>900</v>
@@ -47032,22 +47032,22 @@
         <v>0</v>
       </c>
       <c r="L1027" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1027" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N1027" t="n">
-        <v>366.39971428571</v>
+        <v>366.39971014493</v>
       </c>
       <c r="O1027" t="n">
-        <v>21617.58314285689</v>
+        <v>21251.18318840594</v>
       </c>
       <c r="P1027" t="n">
         <v>2900</v>
       </c>
       <c r="Q1027" t="n">
-        <v>171100</v>
+        <v>168200</v>
       </c>
     </row>
     <row r="1028">
@@ -48199,22 +48199,22 @@
         <v>0</v>
       </c>
       <c r="L1052" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1052" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="N1052" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1052" t="n">
-        <v>129422.7</v>
+        <v>123539.85</v>
       </c>
       <c r="P1052" t="n">
         <v>1900</v>
       </c>
       <c r="Q1052" t="n">
-        <v>209000</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="1053">
@@ -48351,10 +48351,10 @@
         <v>17</v>
       </c>
       <c r="N1055" t="n">
-        <v>3181.9</v>
+        <v>3248.0517671518</v>
       </c>
       <c r="O1055" t="n">
-        <v>54092.3</v>
+        <v>55216.8800415806</v>
       </c>
       <c r="P1055" t="n">
         <v>5100</v>
@@ -53017,22 +53017,22 @@
         <v>0</v>
       </c>
       <c r="L1157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1157" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N1157" t="n">
-        <v>1952.66</v>
+        <v>1991.055</v>
       </c>
       <c r="O1157" t="n">
-        <v>52721.82</v>
+        <v>51767.43</v>
       </c>
       <c r="P1157" t="n">
         <v>3500</v>
       </c>
       <c r="Q1157" t="n">
-        <v>94500</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="1158">
@@ -54446,22 +54446,22 @@
         <v>0</v>
       </c>
       <c r="L1188" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1188" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="N1188" t="n">
-        <v>6336</v>
+        <v>6620.7640449438</v>
       </c>
       <c r="O1188" t="n">
-        <v>240768</v>
+        <v>225105.9775280892</v>
       </c>
       <c r="P1188" t="n">
         <v>7500</v>
       </c>
       <c r="Q1188" t="n">
-        <v>285000</v>
+        <v>255000</v>
       </c>
     </row>
     <row r="1189">
@@ -54584,22 +54584,22 @@
         <v>0</v>
       </c>
       <c r="L1191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1191" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N1191" t="n">
         <v>3872</v>
       </c>
       <c r="O1191" t="n">
-        <v>232320</v>
+        <v>228448</v>
       </c>
       <c r="P1191" t="n">
         <v>4900</v>
       </c>
       <c r="Q1191" t="n">
-        <v>294000</v>
+        <v>289100</v>
       </c>
     </row>
     <row r="1192">
@@ -54676,22 +54676,22 @@
         <v>0</v>
       </c>
       <c r="L1193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1193" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N1193" t="n">
         <v>4400</v>
       </c>
       <c r="O1193" t="n">
-        <v>39600</v>
+        <v>35200</v>
       </c>
       <c r="P1193" t="n">
         <v>5900</v>
       </c>
       <c r="Q1193" t="n">
-        <v>53100</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="1194">
@@ -62112,22 +62112,22 @@
         <v>0</v>
       </c>
       <c r="L1353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1353" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N1353" t="n">
-        <v>4171.6685988024</v>
+        <v>4171.6685954382</v>
       </c>
       <c r="O1353" t="n">
-        <v>66746.6975808384</v>
+        <v>58403.3603361348</v>
       </c>
       <c r="P1353" t="n">
         <v>5000</v>
       </c>
       <c r="Q1353" t="n">
-        <v>80000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="1354">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -856,10 +856,10 @@
         <v>351</v>
       </c>
       <c r="N11" t="n">
-        <v>1811.3087912088</v>
+        <v>1811.3088176353</v>
       </c>
       <c r="O11" t="n">
-        <v>635769.3857142888</v>
+        <v>635769.3949899903</v>
       </c>
       <c r="P11" t="n">
         <v>2600</v>
@@ -6014,22 +6014,22 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N133" t="n">
         <v>8500</v>
       </c>
       <c r="O133" t="n">
-        <v>42500</v>
+        <v>34000</v>
       </c>
       <c r="P133" t="n">
         <v>10200</v>
       </c>
       <c r="Q133" t="n">
-        <v>51000</v>
+        <v>40800</v>
       </c>
     </row>
     <row r="134">
@@ -11793,10 +11793,10 @@
         <v>279</v>
       </c>
       <c r="N262" t="n">
-        <v>3158.8608362663</v>
+        <v>3158.8608369301</v>
       </c>
       <c r="O262" t="n">
-        <v>881322.1733182977</v>
+        <v>881322.173503498</v>
       </c>
       <c r="P262" t="n">
         <v>5600</v>
@@ -12745,22 +12745,22 @@
         <v>0</v>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M283" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N283" t="n">
-        <v>3795.7100076147</v>
+        <v>3795.7100076161</v>
       </c>
       <c r="O283" t="n">
-        <v>136645.5602741292</v>
+        <v>132849.8502665635</v>
       </c>
       <c r="P283" t="n">
         <v>6200</v>
       </c>
       <c r="Q283" t="n">
-        <v>223200</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="284">
@@ -14778,10 +14778,10 @@
         <v>61</v>
       </c>
       <c r="N328" t="n">
-        <v>1592.5654585153</v>
+        <v>1592.5654545455</v>
       </c>
       <c r="O328" t="n">
-        <v>97146.4929694333</v>
+        <v>97146.4927272755</v>
       </c>
       <c r="P328" t="n">
         <v>3900</v>
@@ -16892,10 +16892,10 @@
         <v>53</v>
       </c>
       <c r="N375" t="n">
-        <v>1550.1944427152</v>
+        <v>1550.1944587288</v>
       </c>
       <c r="O375" t="n">
-        <v>82160.30546390561</v>
+        <v>82160.3063126264</v>
       </c>
       <c r="P375" t="n">
         <v>2500</v>
@@ -16938,10 +16938,10 @@
         <v>51</v>
       </c>
       <c r="N376" t="n">
-        <v>1579.38564</v>
+        <v>1579.3847234043</v>
       </c>
       <c r="O376" t="n">
-        <v>80548.66764</v>
+        <v>80548.6208936193</v>
       </c>
       <c r="P376" t="n">
         <v>2900</v>
@@ -16978,22 +16978,22 @@
         <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M377" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N377" t="n">
-        <v>2403.5172431982</v>
+        <v>2403.5172815804</v>
       </c>
       <c r="O377" t="n">
-        <v>108158.275943919</v>
+        <v>96140.69126321599</v>
       </c>
       <c r="P377" t="n">
         <v>3500</v>
       </c>
       <c r="Q377" t="n">
-        <v>157500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="378">
@@ -18240,10 +18240,10 @@
         <v>14</v>
       </c>
       <c r="N405" t="n">
-        <v>204.05094594595</v>
+        <v>204.05098591549</v>
       </c>
       <c r="O405" t="n">
-        <v>2856.7132432433</v>
+        <v>2856.71380281686</v>
       </c>
       <c r="P405" t="n">
         <v>500</v>
@@ -19449,22 +19449,22 @@
         <v>0</v>
       </c>
       <c r="L433" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M433" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N433" t="n">
         <v>2517.22</v>
       </c>
       <c r="O433" t="n">
-        <v>138447.1</v>
+        <v>130895.44</v>
       </c>
       <c r="P433" t="n">
         <v>4200</v>
       </c>
       <c r="Q433" t="n">
-        <v>231000</v>
+        <v>218400</v>
       </c>
     </row>
     <row r="434">
@@ -19496,10 +19496,10 @@
         <v>83</v>
       </c>
       <c r="N434" t="n">
-        <v>2029.8740849673</v>
+        <v>2029.874091653</v>
       </c>
       <c r="O434" t="n">
-        <v>168479.5490522859</v>
+        <v>168479.549607199</v>
       </c>
       <c r="P434" t="n">
         <v>3600</v>
@@ -20123,22 +20123,22 @@
         <v>0</v>
       </c>
       <c r="L449" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M449" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N449" t="n">
-        <v>3731.024440678</v>
+        <v>3731.0244863014</v>
       </c>
       <c r="O449" t="n">
-        <v>231323.515322036</v>
+        <v>220130.4446917826</v>
       </c>
       <c r="P449" t="n">
         <v>5200</v>
       </c>
       <c r="Q449" t="n">
-        <v>322400</v>
+        <v>306800</v>
       </c>
     </row>
     <row r="450">
@@ -21429,22 +21429,22 @@
         <v>0</v>
       </c>
       <c r="L479" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M479" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N479" t="n">
         <v>5431.12</v>
       </c>
       <c r="O479" t="n">
-        <v>43448.96</v>
+        <v>38017.84</v>
       </c>
       <c r="P479" t="n">
         <v>8900</v>
       </c>
       <c r="Q479" t="n">
-        <v>71200</v>
+        <v>62300</v>
       </c>
     </row>
     <row r="480">
@@ -28018,10 +28018,10 @@
         <v>58</v>
       </c>
       <c r="N624" t="n">
-        <v>4907.8225450902</v>
+        <v>4907.8225656566</v>
       </c>
       <c r="O624" t="n">
-        <v>284653.7076152316</v>
+        <v>284653.7088080828</v>
       </c>
       <c r="P624" t="n">
         <v>8200</v>
@@ -31050,10 +31050,10 @@
         <v>32</v>
       </c>
       <c r="N690" t="n">
-        <v>1516.0387513947</v>
+        <v>1516.0387508879</v>
       </c>
       <c r="O690" t="n">
-        <v>48513.2400446304</v>
+        <v>48513.2400284128</v>
       </c>
       <c r="P690" t="n">
         <v>2300</v>
@@ -31326,10 +31326,10 @@
         <v>158</v>
       </c>
       <c r="N696" t="n">
-        <v>1803.0164892802</v>
+        <v>1803.016504221</v>
       </c>
       <c r="O696" t="n">
-        <v>284876.6053062716</v>
+        <v>284876.607666918</v>
       </c>
       <c r="P696" t="n">
         <v>2500</v>
@@ -31510,10 +31510,10 @@
         <v>237</v>
       </c>
       <c r="N700" t="n">
-        <v>2056.0823128492</v>
+        <v>2056.0822725571</v>
       </c>
       <c r="O700" t="n">
-        <v>487291.5081452604</v>
+        <v>487291.4985960327</v>
       </c>
       <c r="P700" t="n">
         <v>2900</v>
@@ -32063,10 +32063,10 @@
         <v>2</v>
       </c>
       <c r="N712" t="n">
-        <v>2546.982132964</v>
+        <v>2546.9817919075</v>
       </c>
       <c r="O712" t="n">
-        <v>5093.964265928</v>
+        <v>5093.963583815</v>
       </c>
       <c r="P712" t="n">
         <v>3900</v>
@@ -36357,10 +36357,10 @@
         <v>186</v>
       </c>
       <c r="N804" t="n">
-        <v>517.29429288703</v>
+        <v>517.29430006698</v>
       </c>
       <c r="O804" t="n">
-        <v>96216.73847698758</v>
+        <v>96216.73981245828</v>
       </c>
       <c r="P804" t="n">
         <v>900</v>
@@ -43800,10 +43800,10 @@
         <v>99</v>
       </c>
       <c r="N960" t="n">
-        <v>1783.7988736264</v>
+        <v>1783.7988731104</v>
       </c>
       <c r="O960" t="n">
-        <v>176596.0884890136</v>
+        <v>176596.0884379296</v>
       </c>
       <c r="P960" t="n">
         <v>1500</v>
@@ -55786,22 +55786,22 @@
         <v>0</v>
       </c>
       <c r="L1217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1217" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N1217" t="n">
         <v>4000</v>
       </c>
       <c r="O1217" t="n">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="P1217" t="n">
         <v>3000</v>
       </c>
       <c r="Q1217" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1218">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -1090,10 +1090,10 @@
         <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>4072</v>
+        <v>4088.8962655602</v>
       </c>
       <c r="O17" t="n">
-        <v>57008</v>
+        <v>57244.5477178428</v>
       </c>
       <c r="P17" t="n">
         <v>7500</v>
@@ -9675,10 +9675,10 @@
         <v>23</v>
       </c>
       <c r="N214" t="n">
-        <v>1950.2139862543</v>
+        <v>1950.2139585731</v>
       </c>
       <c r="O214" t="n">
-        <v>44854.9216838489</v>
+        <v>44854.9210471813</v>
       </c>
       <c r="P214" t="n">
         <v>2900</v>
@@ -9941,10 +9941,10 @@
         <v>6</v>
       </c>
       <c r="N220" t="n">
-        <v>4937.3101654135</v>
+        <v>4937.310165538</v>
       </c>
       <c r="O220" t="n">
-        <v>29623.860992481</v>
+        <v>29623.860993228</v>
       </c>
       <c r="P220" t="n">
         <v>7500</v>
@@ -10681,10 +10681,10 @@
         <v>9</v>
       </c>
       <c r="N237" t="n">
-        <v>13593.35</v>
+        <v>13626.343567961</v>
       </c>
       <c r="O237" t="n">
-        <v>122340.15</v>
+        <v>122637.092111649</v>
       </c>
       <c r="P237" t="n">
         <v>25500</v>
@@ -11373,10 +11373,10 @@
         <v>5</v>
       </c>
       <c r="N253" t="n">
-        <v>2582.2550509317</v>
+        <v>2582.2550435432</v>
       </c>
       <c r="O253" t="n">
-        <v>12911.2752546585</v>
+        <v>12911.275217716</v>
       </c>
       <c r="P253" t="n">
         <v>4500</v>
@@ -11465,10 +11465,10 @@
         <v>5</v>
       </c>
       <c r="N255" t="n">
-        <v>5216.8959642591</v>
+        <v>5220.0054239309</v>
       </c>
       <c r="O255" t="n">
-        <v>26084.4798212955</v>
+        <v>26100.0271196545</v>
       </c>
       <c r="P255" t="n">
         <v>8500</v>
@@ -12623,10 +12623,10 @@
         <v>27</v>
       </c>
       <c r="N280" t="n">
-        <v>6507</v>
+        <v>6513.4596293845</v>
       </c>
       <c r="O280" t="n">
-        <v>175689</v>
+        <v>175863.4099933815</v>
       </c>
       <c r="P280" t="n">
         <v>9900</v>
@@ -13293,10 +13293,10 @@
         <v>2</v>
       </c>
       <c r="N295" t="n">
-        <v>8012</v>
+        <v>8051.1465798046</v>
       </c>
       <c r="O295" t="n">
-        <v>16024</v>
+        <v>16102.2931596092</v>
       </c>
       <c r="P295" t="n">
         <v>13200</v>
@@ -13424,10 +13424,10 @@
         <v>16</v>
       </c>
       <c r="N298" t="n">
-        <v>3594.2531526391</v>
+        <v>3594.2531477516</v>
       </c>
       <c r="O298" t="n">
-        <v>57508.0504422256</v>
+        <v>57508.0503640256</v>
       </c>
       <c r="P298" t="n">
         <v>6500</v>
@@ -13739,10 +13739,10 @@
         <v>9</v>
       </c>
       <c r="N305" t="n">
-        <v>14822.378827839</v>
+        <v>14840.499095355</v>
       </c>
       <c r="O305" t="n">
-        <v>133401.409450551</v>
+        <v>133564.491858195</v>
       </c>
       <c r="P305" t="n">
         <v>24900</v>
@@ -14048,10 +14048,10 @@
         <v>7</v>
       </c>
       <c r="N312" t="n">
-        <v>2665.4</v>
+        <v>2668.7380087664</v>
       </c>
       <c r="O312" t="n">
-        <v>18657.8</v>
+        <v>18681.1660613648</v>
       </c>
       <c r="P312" t="n">
         <v>20900</v>
@@ -14778,10 +14778,10 @@
         <v>60</v>
       </c>
       <c r="N328" t="n">
-        <v>1592.5653777778</v>
+        <v>1592.5653736655</v>
       </c>
       <c r="O328" t="n">
-        <v>95553.922666668</v>
+        <v>95553.92241992999</v>
       </c>
       <c r="P328" t="n">
         <v>3900</v>
@@ -15126,10 +15126,10 @@
         <v>13</v>
       </c>
       <c r="N336" t="n">
-        <v>6242.93</v>
+        <v>6260.7161253561</v>
       </c>
       <c r="O336" t="n">
-        <v>81158.09</v>
+        <v>81389.30962962929</v>
       </c>
       <c r="P336" t="n">
         <v>10400</v>
@@ -16575,10 +16575,10 @@
         <v>14</v>
       </c>
       <c r="N368" t="n">
-        <v>9903</v>
+        <v>9918.473437500001</v>
       </c>
       <c r="O368" t="n">
-        <v>138642</v>
+        <v>138858.628125</v>
       </c>
       <c r="P368" t="n">
         <v>15900</v>
@@ -16754,10 +16754,10 @@
         <v>176</v>
       </c>
       <c r="N372" t="n">
-        <v>1630.9243202247</v>
+        <v>1630.9243287363</v>
       </c>
       <c r="O372" t="n">
-        <v>287042.6803595472</v>
+        <v>287042.6818575888</v>
       </c>
       <c r="P372" t="n">
         <v>2500</v>
@@ -16892,10 +16892,10 @@
         <v>37</v>
       </c>
       <c r="N375" t="n">
-        <v>1550.1945107573</v>
+        <v>1550.1945200974</v>
       </c>
       <c r="O375" t="n">
-        <v>57357.1968980201</v>
+        <v>57357.1972436038</v>
       </c>
       <c r="P375" t="n">
         <v>2500</v>
@@ -16984,10 +16984,10 @@
         <v>36</v>
       </c>
       <c r="N377" t="n">
-        <v>2403.5178067661</v>
+        <v>2403.5178733813</v>
       </c>
       <c r="O377" t="n">
-        <v>86526.6410435796</v>
+        <v>86526.6434417268</v>
       </c>
       <c r="P377" t="n">
         <v>3500</v>
@@ -19496,10 +19496,10 @@
         <v>83</v>
       </c>
       <c r="N434" t="n">
-        <v>2029.8740983607</v>
+        <v>2029.8741050903</v>
       </c>
       <c r="O434" t="n">
-        <v>168479.5501639381</v>
+        <v>168479.5507224949</v>
       </c>
       <c r="P434" t="n">
         <v>3600</v>
@@ -20646,22 +20646,22 @@
         <v>0</v>
       </c>
       <c r="L461" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M461" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N461" t="n">
         <v>3591.13</v>
       </c>
       <c r="O461" t="n">
-        <v>43093.56</v>
+        <v>39502.43</v>
       </c>
       <c r="P461" t="n">
         <v>6300</v>
       </c>
       <c r="Q461" t="n">
-        <v>75600</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="462">
@@ -21302,10 +21302,10 @@
         <v>2</v>
       </c>
       <c r="N476" t="n">
-        <v>4100.45</v>
+        <v>4114.8123467601</v>
       </c>
       <c r="O476" t="n">
-        <v>8200.9</v>
+        <v>8229.6246935202</v>
       </c>
       <c r="P476" t="n">
         <v>26900</v>
@@ -21481,10 +21481,10 @@
         <v>16</v>
       </c>
       <c r="N480" t="n">
-        <v>1561.0038892883</v>
+        <v>1561.0040101523</v>
       </c>
       <c r="O480" t="n">
-        <v>24976.0622286128</v>
+        <v>24976.0641624368</v>
       </c>
       <c r="P480" t="n">
         <v>2900</v>
@@ -22001,10 +22001,10 @@
         <v>8</v>
       </c>
       <c r="N492" t="n">
-        <v>7969.950169361</v>
+        <v>7988.3991280864</v>
       </c>
       <c r="O492" t="n">
-        <v>63759.601354888</v>
+        <v>63907.1930246912</v>
       </c>
       <c r="P492" t="n">
         <v>12900</v>
@@ -24821,7 +24821,7 @@
         </is>
       </c>
       <c r="J555" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
@@ -24830,19 +24830,19 @@
         <v>0</v>
       </c>
       <c r="M555" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N555" t="n">
-        <v>25749.15</v>
+        <v>24523</v>
       </c>
       <c r="O555" t="n">
-        <v>77247.45000000001</v>
+        <v>171661</v>
       </c>
       <c r="P555" t="n">
         <v>41900</v>
       </c>
       <c r="Q555" t="n">
-        <v>125700</v>
+        <v>293300</v>
       </c>
     </row>
     <row r="556">
@@ -26457,10 +26457,10 @@
         <v>11</v>
       </c>
       <c r="N590" t="n">
-        <v>13687</v>
+        <v>13795.340369393</v>
       </c>
       <c r="O590" t="n">
-        <v>150557</v>
+        <v>151748.744063323</v>
       </c>
       <c r="P590" t="n">
         <v>21900</v>
@@ -26869,10 +26869,10 @@
         <v>17</v>
       </c>
       <c r="N599" t="n">
-        <v>8858.16</v>
+        <v>8872.673642818099</v>
       </c>
       <c r="O599" t="n">
-        <v>150588.72</v>
+        <v>150835.4519279077</v>
       </c>
       <c r="P599" t="n">
         <v>15500</v>
@@ -28258,10 +28258,10 @@
         <v>57</v>
       </c>
       <c r="N629" t="n">
-        <v>3903.7390742358</v>
+        <v>3903.7391243433</v>
       </c>
       <c r="O629" t="n">
-        <v>222513.1272314406</v>
+        <v>222513.1300875681</v>
       </c>
       <c r="P629" t="n">
         <v>7500</v>
@@ -28304,10 +28304,10 @@
         <v>3</v>
       </c>
       <c r="N630" t="n">
-        <v>33000</v>
+        <v>33980.198019802</v>
       </c>
       <c r="O630" t="n">
-        <v>99000</v>
+        <v>101940.594059406</v>
       </c>
       <c r="P630" t="n">
         <v>52900</v>
@@ -28626,10 +28626,10 @@
         <v>3</v>
       </c>
       <c r="N637" t="n">
-        <v>6849.2</v>
+        <v>6855.7044634378</v>
       </c>
       <c r="O637" t="n">
-        <v>20547.6</v>
+        <v>20567.1133903134</v>
       </c>
       <c r="P637" t="n">
         <v>11500</v>
@@ -31014,10 +31014,10 @@
         <v>24</v>
       </c>
       <c r="N689" t="n">
-        <v>1516.0387464358</v>
+        <v>1516.0387455416</v>
       </c>
       <c r="O689" t="n">
-        <v>36384.9299144592</v>
+        <v>36384.9298929984</v>
       </c>
       <c r="P689" t="n">
         <v>2300</v>
@@ -31106,10 +31106,10 @@
         <v>169</v>
       </c>
       <c r="N691" t="n">
-        <v>2458.5126157653</v>
+        <v>2500.9617517986</v>
       </c>
       <c r="O691" t="n">
-        <v>415488.6320643357</v>
+        <v>422662.5360539634</v>
       </c>
       <c r="P691" t="n">
         <v>3500</v>
@@ -31198,10 +31198,10 @@
         <v>87</v>
       </c>
       <c r="N693" t="n">
-        <v>1771.089398827</v>
+        <v>1835.6884042553</v>
       </c>
       <c r="O693" t="n">
-        <v>154084.777697949</v>
+        <v>159704.8911702111</v>
       </c>
       <c r="P693" t="n">
         <v>2500</v>
@@ -31244,10 +31244,10 @@
         <v>186</v>
       </c>
       <c r="N694" t="n">
-        <v>2079.3833258511</v>
+        <v>2079.3833208536</v>
       </c>
       <c r="O694" t="n">
-        <v>386765.2986083046</v>
+        <v>386765.2976787696</v>
       </c>
       <c r="P694" t="n">
         <v>2900</v>
@@ -31290,10 +31290,10 @@
         <v>145</v>
       </c>
       <c r="N695" t="n">
-        <v>1803.0166107644</v>
+        <v>1837.4143839428</v>
       </c>
       <c r="O695" t="n">
-        <v>261437.408560838</v>
+        <v>266425.085671706</v>
       </c>
       <c r="P695" t="n">
         <v>2500</v>
@@ -31336,10 +31336,10 @@
         <v>33</v>
       </c>
       <c r="N696" t="n">
-        <v>3306.5944272446</v>
+        <v>3645.1535836177</v>
       </c>
       <c r="O696" t="n">
-        <v>109117.6160990718</v>
+        <v>120290.0682593841</v>
       </c>
       <c r="P696" t="n">
         <v>4900</v>
@@ -31474,10 +31474,10 @@
         <v>233</v>
       </c>
       <c r="N699" t="n">
-        <v>2056.0822493428</v>
+        <v>2093.8229560229</v>
       </c>
       <c r="O699" t="n">
-        <v>479067.1640968724</v>
+        <v>487860.7487533357</v>
       </c>
       <c r="P699" t="n">
         <v>2900</v>
@@ -31566,10 +31566,10 @@
         <v>95</v>
       </c>
       <c r="N701" t="n">
-        <v>1655.9295385779</v>
+        <v>1751.31108</v>
       </c>
       <c r="O701" t="n">
-        <v>157313.3061649005</v>
+        <v>166374.5526</v>
       </c>
       <c r="P701" t="n">
         <v>2500</v>
@@ -31845,10 +31845,10 @@
         <v>1</v>
       </c>
       <c r="N707" t="n">
-        <v>1592.2824611033</v>
+        <v>1592.2825142045</v>
       </c>
       <c r="O707" t="n">
-        <v>1592.2824611033</v>
+        <v>1592.2825142045</v>
       </c>
       <c r="P707" t="n">
         <v>2500</v>
@@ -32246,22 +32246,22 @@
         <v>0</v>
       </c>
       <c r="L716" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M716" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N716" t="n">
         <v>14003</v>
       </c>
       <c r="O716" t="n">
-        <v>154033</v>
+        <v>0</v>
       </c>
       <c r="P716" t="n">
         <v>22500</v>
       </c>
       <c r="Q716" t="n">
-        <v>247500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="717">
@@ -32578,10 +32578,10 @@
         <v>45</v>
       </c>
       <c r="N723" t="n">
-        <v>5215</v>
+        <v>5227.7693437806</v>
       </c>
       <c r="O723" t="n">
-        <v>234675</v>
+        <v>235249.620470127</v>
       </c>
       <c r="P723" t="n">
         <v>8900</v>
@@ -36321,10 +36321,10 @@
         <v>162</v>
       </c>
       <c r="N803" t="n">
-        <v>517.2943625967</v>
+        <v>517.29445253004</v>
       </c>
       <c r="O803" t="n">
-        <v>83801.68674066541</v>
+        <v>83801.70130986648</v>
       </c>
       <c r="P803" t="n">
         <v>900</v>
@@ -36732,7 +36732,7 @@
         </is>
       </c>
       <c r="J812" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K812" t="n">
         <v>0</v>
@@ -36741,10 +36741,10 @@
         <v>0</v>
       </c>
       <c r="M812" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N812" t="n">
-        <v>573461.5600000001</v>
+        <v>81923.08</v>
       </c>
       <c r="O812" t="n">
         <v>573461.5600000001</v>
@@ -36753,7 +36753,7 @@
         <v>106500</v>
       </c>
       <c r="Q812" t="n">
-        <v>106500</v>
+        <v>745500</v>
       </c>
     </row>
     <row r="813">
@@ -36926,10 +36926,10 @@
         <v>106</v>
       </c>
       <c r="N816" t="n">
-        <v>3110.8379310345</v>
+        <v>3110.8378564067</v>
       </c>
       <c r="O816" t="n">
-        <v>329748.820689657</v>
+        <v>329748.8127791102</v>
       </c>
       <c r="P816" t="n">
         <v>4500</v>
@@ -37157,10 +37157,10 @@
         <v>211</v>
       </c>
       <c r="N821" t="n">
-        <v>703.79481075491</v>
+        <v>703.79479136392</v>
       </c>
       <c r="O821" t="n">
-        <v>148500.705069286</v>
+        <v>148500.7009777871</v>
       </c>
       <c r="P821" t="n">
         <v>900</v>
@@ -41188,22 +41188,22 @@
         <v>0</v>
       </c>
       <c r="L906" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M906" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N906" t="n">
         <v>9874.620000000001</v>
       </c>
       <c r="O906" t="n">
-        <v>118495.44</v>
+        <v>108620.82</v>
       </c>
       <c r="P906" t="n">
         <v>14700</v>
       </c>
       <c r="Q906" t="n">
-        <v>176400</v>
+        <v>161700</v>
       </c>
     </row>
     <row r="907">
@@ -42159,7 +42159,7 @@
         </is>
       </c>
       <c r="J926" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K926" t="n">
         <v>0</v>
@@ -42168,19 +42168,19 @@
         <v>0</v>
       </c>
       <c r="M926" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N926" t="n">
-        <v>18165.666666667</v>
+        <v>10899.4</v>
       </c>
       <c r="O926" t="n">
-        <v>90828.333333335</v>
+        <v>119893.4</v>
       </c>
       <c r="P926" t="n">
         <v>41500</v>
       </c>
       <c r="Q926" t="n">
-        <v>207500</v>
+        <v>456500</v>
       </c>
     </row>
     <row r="927">
@@ -42744,7 +42744,7 @@
         </is>
       </c>
       <c r="J938" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K938" t="n">
         <v>0</v>
@@ -42753,19 +42753,19 @@
         <v>0</v>
       </c>
       <c r="M938" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N938" t="n">
-        <v>4044.3722222222</v>
+        <v>2799.95</v>
       </c>
       <c r="O938" t="n">
-        <v>24266.2333333332</v>
+        <v>27999.5</v>
       </c>
       <c r="P938" t="n">
         <v>53500</v>
       </c>
       <c r="Q938" t="n">
-        <v>321000</v>
+        <v>535000</v>
       </c>
     </row>
     <row r="939">
@@ -48879,10 +48879,10 @@
         <v>15</v>
       </c>
       <c r="N1066" t="n">
-        <v>1757.3206205251</v>
+        <v>1757.3206220096</v>
       </c>
       <c r="O1066" t="n">
-        <v>26359.8093078765</v>
+        <v>26359.809330144</v>
       </c>
       <c r="P1066" t="n">
         <v>2000</v>
@@ -54640,22 +54640,22 @@
         <v>0</v>
       </c>
       <c r="L1192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N1192" t="n">
         <v>4400</v>
       </c>
       <c r="O1192" t="n">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="P1192" t="n">
         <v>5900</v>
       </c>
       <c r="Q1192" t="n">
-        <v>5900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1193">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -1090,10 +1090,10 @@
         <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>4088.8962655602</v>
+        <v>4072</v>
       </c>
       <c r="O17" t="n">
-        <v>57244.5477178428</v>
+        <v>57008</v>
       </c>
       <c r="P17" t="n">
         <v>7500</v>
@@ -3395,10 +3395,10 @@
         <v>9</v>
       </c>
       <c r="N72" t="n">
-        <v>15899.011607143</v>
+        <v>15711.964345238</v>
       </c>
       <c r="O72" t="n">
-        <v>143091.104464287</v>
+        <v>141407.679107142</v>
       </c>
       <c r="P72" t="n">
         <v>28500</v>
@@ -5163,10 +5163,10 @@
         <v>5</v>
       </c>
       <c r="N113" t="n">
-        <v>544.6367953668</v>
+        <v>538.40061776062</v>
       </c>
       <c r="O113" t="n">
-        <v>2723.183976834</v>
+        <v>2692.0030888031</v>
       </c>
       <c r="P113" t="n">
         <v>6800</v>
@@ -5563,10 +5563,10 @@
         <v>1</v>
       </c>
       <c r="N122" t="n">
-        <v>2644.1214388489</v>
+        <v>2570.16</v>
       </c>
       <c r="O122" t="n">
-        <v>2644.1214388489</v>
+        <v>2570.16</v>
       </c>
       <c r="P122" t="n">
         <v>4700</v>
@@ -6066,10 +6066,10 @@
         <v>6</v>
       </c>
       <c r="N134" t="n">
-        <v>4368.6523333333</v>
+        <v>4273.6816666667</v>
       </c>
       <c r="O134" t="n">
-        <v>26211.9139999998</v>
+        <v>25642.0900000002</v>
       </c>
       <c r="P134" t="n">
         <v>6500</v>
@@ -6273,10 +6273,10 @@
         <v>1</v>
       </c>
       <c r="N139" t="n">
-        <v>2659.1657943925</v>
+        <v>2563.34</v>
       </c>
       <c r="O139" t="n">
-        <v>2659.1657943925</v>
+        <v>2563.34</v>
       </c>
       <c r="P139" t="n">
         <v>4700</v>
@@ -9634,10 +9634,10 @@
         <v>4</v>
       </c>
       <c r="N213" t="n">
-        <v>10897.588251121</v>
+        <v>10752.93</v>
       </c>
       <c r="O213" t="n">
-        <v>43590.353004484</v>
+        <v>43011.72</v>
       </c>
       <c r="P213" t="n">
         <v>18400</v>
@@ -10635,10 +10635,10 @@
         <v>28</v>
       </c>
       <c r="N236" t="n">
-        <v>12796.783333333</v>
+        <v>12587</v>
       </c>
       <c r="O236" t="n">
-        <v>358309.933333324</v>
+        <v>352436</v>
       </c>
       <c r="P236" t="n">
         <v>18900</v>
@@ -10722,10 +10722,10 @@
         <v>13</v>
       </c>
       <c r="N238" t="n">
-        <v>17263.007447496</v>
+        <v>17207.41</v>
       </c>
       <c r="O238" t="n">
-        <v>224419.096817448</v>
+        <v>223696.33</v>
       </c>
       <c r="P238" t="n">
         <v>20000</v>
@@ -13372,22 +13372,22 @@
         <v>0</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M297" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N297" t="n">
-        <v>3594.2531182796</v>
+        <v>3594.2531034483</v>
       </c>
       <c r="O297" t="n">
-        <v>46725.2905376348</v>
+        <v>43131.0372413796</v>
       </c>
       <c r="P297" t="n">
         <v>6500</v>
       </c>
       <c r="Q297" t="n">
-        <v>84500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="298">
@@ -14323,10 +14323,10 @@
         <v>11</v>
       </c>
       <c r="N318" t="n">
-        <v>2718.841814346</v>
+        <v>2696.09</v>
       </c>
       <c r="O318" t="n">
-        <v>29907.259957806</v>
+        <v>29656.99</v>
       </c>
       <c r="P318" t="n">
         <v>8200</v>
@@ -15126,10 +15126,10 @@
         <v>13</v>
       </c>
       <c r="N336" t="n">
-        <v>6260.7161253561</v>
+        <v>6242.93</v>
       </c>
       <c r="O336" t="n">
-        <v>81389.30962962929</v>
+        <v>81158.09</v>
       </c>
       <c r="P336" t="n">
         <v>10400</v>
@@ -17110,10 +17110,10 @@
         <v>6</v>
       </c>
       <c r="N380" t="n">
-        <v>11749.140699301</v>
+        <v>11507.72</v>
       </c>
       <c r="O380" t="n">
-        <v>70494.844195806</v>
+        <v>69046.31999999999</v>
       </c>
       <c r="P380" t="n">
         <v>25800</v>
@@ -19949,22 +19949,22 @@
         <v>0</v>
       </c>
       <c r="L445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M445" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N445" t="n">
-        <v>4355.2256097561</v>
+        <v>4355.2256790123</v>
       </c>
       <c r="O445" t="n">
-        <v>100170.1890243903</v>
+        <v>95814.9649382706</v>
       </c>
       <c r="P445" t="n">
         <v>7900</v>
       </c>
       <c r="Q445" t="n">
-        <v>181700</v>
+        <v>173800</v>
       </c>
     </row>
     <row r="446">
@@ -21261,10 +21261,10 @@
         <v>7</v>
       </c>
       <c r="N475" t="n">
-        <v>27233.355818182</v>
+        <v>27123.764828283</v>
       </c>
       <c r="O475" t="n">
-        <v>190633.490727274</v>
+        <v>189866.353797981</v>
       </c>
       <c r="P475" t="n">
         <v>44500</v>
@@ -21527,10 +21527,10 @@
         <v>16</v>
       </c>
       <c r="N481" t="n">
-        <v>1561.0041954445</v>
+        <v>1561.004375</v>
       </c>
       <c r="O481" t="n">
-        <v>24976.067127112</v>
+        <v>24976.07</v>
       </c>
       <c r="P481" t="n">
         <v>2900</v>
@@ -22047,10 +22047,10 @@
         <v>8</v>
       </c>
       <c r="N493" t="n">
-        <v>7988.3991280864</v>
+        <v>7969.9501697531</v>
       </c>
       <c r="O493" t="n">
-        <v>63907.1930246912</v>
+        <v>63759.6013580248</v>
       </c>
       <c r="P493" t="n">
         <v>12900</v>
@@ -23504,10 +23504,10 @@
         <v>10</v>
       </c>
       <c r="N526" t="n">
-        <v>2647.8160651629</v>
+        <v>2634.61</v>
       </c>
       <c r="O526" t="n">
-        <v>26478.160651629</v>
+        <v>26346.1</v>
       </c>
       <c r="P526" t="n">
         <v>4200</v>
@@ -23688,10 +23688,10 @@
         <v>1</v>
       </c>
       <c r="N530" t="n">
-        <v>4397.0456179775</v>
+        <v>4163.1602247191</v>
       </c>
       <c r="O530" t="n">
-        <v>4397.0456179775</v>
+        <v>4163.1602247191</v>
       </c>
       <c r="P530" t="n">
         <v>6700</v>
@@ -23780,10 +23780,10 @@
         <v>16</v>
       </c>
       <c r="N532" t="n">
-        <v>2510.8902747909</v>
+        <v>2495.98</v>
       </c>
       <c r="O532" t="n">
-        <v>40174.2443966544</v>
+        <v>39935.68</v>
       </c>
       <c r="P532" t="n">
         <v>4100</v>
@@ -24423,10 +24423,10 @@
         <v>29</v>
       </c>
       <c r="N546" t="n">
-        <v>9379.0968275862</v>
+        <v>9188.98</v>
       </c>
       <c r="O546" t="n">
-        <v>271993.8079999998</v>
+        <v>266480.42</v>
       </c>
       <c r="P546" t="n">
         <v>12900</v>
@@ -25063,10 +25063,10 @@
         <v>5</v>
       </c>
       <c r="N560" t="n">
-        <v>16092.984749455</v>
+        <v>16058</v>
       </c>
       <c r="O560" t="n">
-        <v>80464.923747275</v>
+        <v>80290</v>
       </c>
       <c r="P560" t="n">
         <v>25900</v>
@@ -25109,10 +25109,10 @@
         <v>2</v>
       </c>
       <c r="N561" t="n">
-        <v>25576.890257559</v>
+        <v>25534</v>
       </c>
       <c r="O561" t="n">
-        <v>51153.780515118</v>
+        <v>51068</v>
       </c>
       <c r="P561" t="n">
         <v>40900</v>
@@ -25385,10 +25385,10 @@
         <v>8</v>
       </c>
       <c r="N567" t="n">
-        <v>9927.272727272701</v>
+        <v>9750</v>
       </c>
       <c r="O567" t="n">
-        <v>79418.18181818161</v>
+        <v>78000</v>
       </c>
       <c r="P567" t="n">
         <v>15600</v>
@@ -25523,10 +25523,10 @@
         <v>13</v>
       </c>
       <c r="N570" t="n">
-        <v>7278.6868686869</v>
+        <v>7230</v>
       </c>
       <c r="O570" t="n">
-        <v>94622.92929292971</v>
+        <v>93990</v>
       </c>
       <c r="P570" t="n">
         <v>11600</v>
@@ -26549,10 +26549,10 @@
         <v>11</v>
       </c>
       <c r="N592" t="n">
-        <v>13795.055263158</v>
+        <v>13687</v>
       </c>
       <c r="O592" t="n">
-        <v>151745.607894738</v>
+        <v>150557</v>
       </c>
       <c r="P592" t="n">
         <v>21900</v>
@@ -27982,10 +27982,10 @@
         <v>11</v>
       </c>
       <c r="N623" t="n">
-        <v>3412.5148218527</v>
+        <v>3396.38</v>
       </c>
       <c r="O623" t="n">
-        <v>37537.6630403797</v>
+        <v>37360.18</v>
       </c>
       <c r="P623" t="n">
         <v>6500</v>
@@ -28212,10 +28212,10 @@
         <v>59</v>
       </c>
       <c r="N628" t="n">
-        <v>13233.257042254</v>
+        <v>13210</v>
       </c>
       <c r="O628" t="n">
-        <v>780762.165492986</v>
+        <v>779390</v>
       </c>
       <c r="P628" t="n">
         <v>23900</v>
@@ -28626,10 +28626,10 @@
         <v>116</v>
       </c>
       <c r="N637" t="n">
-        <v>2657.2435094002</v>
+        <v>2629</v>
       </c>
       <c r="O637" t="n">
-        <v>308240.2470904232</v>
+        <v>304964</v>
       </c>
       <c r="P637" t="n">
         <v>4500</v>
@@ -28718,10 +28718,10 @@
         <v>3</v>
       </c>
       <c r="N639" t="n">
-        <v>6881.8463298379</v>
+        <v>6849.2</v>
       </c>
       <c r="O639" t="n">
-        <v>20645.5389895137</v>
+        <v>20547.6</v>
       </c>
       <c r="P639" t="n">
         <v>11500</v>
@@ -28810,10 +28810,10 @@
         <v>40</v>
       </c>
       <c r="N641" t="n">
-        <v>6279.1629563669</v>
+        <v>6268</v>
       </c>
       <c r="O641" t="n">
-        <v>251166.518254676</v>
+        <v>250720</v>
       </c>
       <c r="P641" t="n">
         <v>10900</v>
@@ -29270,10 +29270,10 @@
         <v>15</v>
       </c>
       <c r="N651" t="n">
-        <v>7639.2713286713</v>
+        <v>7635</v>
       </c>
       <c r="O651" t="n">
-        <v>114589.0699300695</v>
+        <v>114525</v>
       </c>
       <c r="P651" t="n">
         <v>13900</v>
@@ -29592,10 +29592,10 @@
         <v>9</v>
       </c>
       <c r="N658" t="n">
-        <v>11478.737327189</v>
+        <v>11348</v>
       </c>
       <c r="O658" t="n">
-        <v>103308.635944701</v>
+        <v>102132</v>
       </c>
       <c r="P658" t="n">
         <v>19900</v>
@@ -30183,10 +30183,10 @@
         <v>58</v>
       </c>
       <c r="N671" t="n">
-        <v>5322.5257731959</v>
+        <v>5215</v>
       </c>
       <c r="O671" t="n">
-        <v>308706.4948453622</v>
+        <v>302470</v>
       </c>
       <c r="P671" t="n">
         <v>8900</v>
@@ -30735,10 +30735,10 @@
         <v>30</v>
       </c>
       <c r="N683" t="n">
-        <v>3823.6153319644</v>
+        <v>3821</v>
       </c>
       <c r="O683" t="n">
-        <v>114708.459958932</v>
+        <v>114630</v>
       </c>
       <c r="P683" t="n">
         <v>5900</v>
@@ -30827,10 +30827,10 @@
         <v>1</v>
       </c>
       <c r="N685" t="n">
-        <v>50038.3125</v>
+        <v>48522</v>
       </c>
       <c r="O685" t="n">
-        <v>50038.3125</v>
+        <v>48522</v>
       </c>
       <c r="P685" t="n">
         <v>77900</v>
@@ -30873,10 +30873,10 @@
         <v>57</v>
       </c>
       <c r="N686" t="n">
-        <v>7295.3326848249</v>
+        <v>7253</v>
       </c>
       <c r="O686" t="n">
-        <v>415833.9630350193</v>
+        <v>413421</v>
       </c>
       <c r="P686" t="n">
         <v>11900</v>
@@ -32073,10 +32073,10 @@
         <v>44</v>
       </c>
       <c r="N712" t="n">
-        <v>2546.9807189542</v>
+        <v>2546.9805333333</v>
       </c>
       <c r="O712" t="n">
-        <v>112067.1516339848</v>
+        <v>112067.1434666652</v>
       </c>
       <c r="P712" t="n">
         <v>3900</v>
@@ -32483,10 +32483,10 @@
         <v>1</v>
       </c>
       <c r="N721" t="n">
-        <v>1185.8146867168</v>
+        <v>1185.3195655806</v>
       </c>
       <c r="O721" t="n">
-        <v>1185.8146867168</v>
+        <v>1185.3195655806</v>
       </c>
       <c r="P721" t="n">
         <v>1900</v>
@@ -33299,10 +33299,10 @@
         <v>2</v>
       </c>
       <c r="N738" t="n">
-        <v>3256.3775316456</v>
+        <v>3026.5160126582</v>
       </c>
       <c r="O738" t="n">
-        <v>6512.7550632912</v>
+        <v>6053.0320253164</v>
       </c>
       <c r="P738" t="n">
         <v>7000</v>
@@ -33860,10 +33860,10 @@
         <v>43</v>
       </c>
       <c r="N750" t="n">
-        <v>1537.958258381</v>
+        <v>1530.4499182339</v>
       </c>
       <c r="O750" t="n">
-        <v>66132.205110383</v>
+        <v>65809.34648405771</v>
       </c>
       <c r="P750" t="n">
         <v>2600</v>
@@ -37209,10 +37209,10 @@
         <v>161</v>
       </c>
       <c r="N822" t="n">
-        <v>703.7947715550901</v>
+        <v>704.67584580877</v>
       </c>
       <c r="O822" t="n">
-        <v>113310.9582203695</v>
+        <v>113452.811175212</v>
       </c>
       <c r="P822" t="n">
         <v>900</v>
@@ -38982,10 +38982,10 @@
         <v>1</v>
       </c>
       <c r="N860" t="n">
-        <v>29180.918333333</v>
+        <v>21885.688333333</v>
       </c>
       <c r="O860" t="n">
-        <v>29180.918333333</v>
+        <v>21885.688333333</v>
       </c>
       <c r="P860" t="n">
         <v>33500</v>
@@ -41053,10 +41053,10 @@
         <v>2</v>
       </c>
       <c r="N903" t="n">
-        <v>26089.656666667</v>
+        <v>24082.76</v>
       </c>
       <c r="O903" t="n">
-        <v>52179.313333334</v>
+        <v>48165.52</v>
       </c>
       <c r="P903" t="n">
         <v>56900</v>
@@ -43524,10 +43524,10 @@
         <v>6</v>
       </c>
       <c r="N954" t="n">
-        <v>5370.6369361702</v>
+        <v>5347.88</v>
       </c>
       <c r="O954" t="n">
-        <v>32223.8216170212</v>
+        <v>32087.28</v>
       </c>
       <c r="P954" t="n">
         <v>7900</v>
@@ -43573,10 +43573,10 @@
         <v>10</v>
       </c>
       <c r="N955" t="n">
-        <v>4593.1990728477</v>
+        <v>4578.04</v>
       </c>
       <c r="O955" t="n">
-        <v>45931.990728477</v>
+        <v>45780.4</v>
       </c>
       <c r="P955" t="n">
         <v>7500</v>
@@ -44836,10 +44836,10 @@
         <v>10</v>
       </c>
       <c r="N981" t="n">
-        <v>10912.902659574</v>
+        <v>10798.03</v>
       </c>
       <c r="O981" t="n">
-        <v>109129.02659574</v>
+        <v>107980.3</v>
       </c>
       <c r="P981" t="n">
         <v>45000</v>
@@ -45207,10 +45207,10 @@
         <v>11</v>
       </c>
       <c r="N989" t="n">
-        <v>5272.2028268551</v>
+        <v>5216.9</v>
       </c>
       <c r="O989" t="n">
-        <v>57994.2310954061</v>
+        <v>57385.89999999999</v>
       </c>
       <c r="P989" t="n">
         <v>20500</v>
@@ -45394,22 +45394,22 @@
         <v>0</v>
       </c>
       <c r="L993" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M993" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N993" t="n">
         <v>1024.29</v>
       </c>
       <c r="O993" t="n">
-        <v>51214.5</v>
+        <v>50190.21</v>
       </c>
       <c r="P993" t="n">
         <v>2900</v>
       </c>
       <c r="Q993" t="n">
-        <v>145000</v>
+        <v>142100</v>
       </c>
     </row>
     <row r="994">
@@ -45694,10 +45694,10 @@
         <v>3</v>
       </c>
       <c r="N999" t="n">
-        <v>7605.4495327103</v>
+        <v>7465.9</v>
       </c>
       <c r="O999" t="n">
-        <v>22816.3485981309</v>
+        <v>22397.7</v>
       </c>
       <c r="P999" t="n">
         <v>11900</v>
@@ -46423,10 +46423,10 @@
         <v>3</v>
       </c>
       <c r="N1014" t="n">
-        <v>44654.875337423</v>
+        <v>44113.604171779</v>
       </c>
       <c r="O1014" t="n">
-        <v>133964.626012269</v>
+        <v>132340.812515337</v>
       </c>
       <c r="P1014" t="n">
         <v>71900</v>
@@ -48364,10 +48364,10 @@
         <v>12</v>
       </c>
       <c r="N1055" t="n">
-        <v>3186.7802147239</v>
+        <v>3181.9</v>
       </c>
       <c r="O1055" t="n">
-        <v>38241.3625766868</v>
+        <v>38182.8</v>
       </c>
       <c r="P1055" t="n">
         <v>5100</v>
@@ -48683,10 +48683,10 @@
         <v>25</v>
       </c>
       <c r="N1062" t="n">
-        <v>2098.7012987013</v>
+        <v>1600</v>
       </c>
       <c r="O1062" t="n">
-        <v>52467.5324675325</v>
+        <v>40000</v>
       </c>
       <c r="P1062" t="n">
         <v>3500</v>
@@ -48729,10 +48729,10 @@
         <v>41</v>
       </c>
       <c r="N1063" t="n">
-        <v>707.69883076923</v>
+        <v>705.5279692307701</v>
       </c>
       <c r="O1063" t="n">
-        <v>29015.65206153843</v>
+        <v>28926.64673846157</v>
       </c>
       <c r="P1063" t="n">
         <v>1500</v>
@@ -52862,10 +52862,10 @@
         <v>18</v>
       </c>
       <c r="N1153" t="n">
-        <v>2655.5149832776</v>
+        <v>2644.9</v>
       </c>
       <c r="O1153" t="n">
-        <v>47799.2696989968</v>
+        <v>47608.2</v>
       </c>
       <c r="P1153" t="n">
         <v>3900</v>
@@ -54971,10 +54971,10 @@
         <v>5</v>
       </c>
       <c r="N1199" t="n">
-        <v>6162.2222222222</v>
+        <v>5900</v>
       </c>
       <c r="O1199" t="n">
-        <v>30811.111111111</v>
+        <v>29500</v>
       </c>
       <c r="P1199" t="n">
         <v>7100</v>
@@ -55109,10 +55109,10 @@
         <v>16</v>
       </c>
       <c r="N1202" t="n">
-        <v>26102.941176471</v>
+        <v>25000</v>
       </c>
       <c r="O1202" t="n">
-        <v>417647.058823536</v>
+        <v>400000</v>
       </c>
       <c r="P1202" t="n">
         <v>30000</v>
@@ -57523,10 +57523,10 @@
         <v>8</v>
       </c>
       <c r="N1254" t="n">
-        <v>1494.6085714286</v>
+        <v>1482.84</v>
       </c>
       <c r="O1254" t="n">
-        <v>11956.8685714288</v>
+        <v>11862.72</v>
       </c>
       <c r="P1254" t="n">
         <v>6500</v>
@@ -66601,22 +66601,22 @@
         <v>0</v>
       </c>
       <c r="L1451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1451" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N1451" t="n">
         <v>2465</v>
       </c>
       <c r="O1451" t="n">
-        <v>332775</v>
+        <v>330310</v>
       </c>
       <c r="P1451" t="n">
         <v>3000</v>
       </c>
       <c r="Q1451" t="n">
-        <v>405000</v>
+        <v>402000</v>
       </c>
     </row>
     <row r="1452">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -9634,10 +9634,10 @@
         <v>4</v>
       </c>
       <c r="N213" t="n">
-        <v>10899.560863636</v>
+        <v>10752.93</v>
       </c>
       <c r="O213" t="n">
-        <v>43598.243454544</v>
+        <v>43011.72</v>
       </c>
       <c r="P213" t="n">
         <v>18400</v>
@@ -9675,10 +9675,10 @@
         <v>23</v>
       </c>
       <c r="N214" t="n">
-        <v>1953.5860864553</v>
+        <v>1950.2139481268</v>
       </c>
       <c r="O214" t="n">
-        <v>44932.4799884719</v>
+        <v>44854.9208069164</v>
       </c>
       <c r="P214" t="n">
         <v>2900</v>
@@ -10681,10 +10681,10 @@
         <v>9</v>
       </c>
       <c r="N237" t="n">
-        <v>13609.886922141</v>
+        <v>13593.35</v>
       </c>
       <c r="O237" t="n">
-        <v>122488.982299269</v>
+        <v>122340.15</v>
       </c>
       <c r="P237" t="n">
         <v>25500</v>
@@ -11747,10 +11747,10 @@
         <v>279</v>
       </c>
       <c r="N261" t="n">
-        <v>3160.7464443118</v>
+        <v>3158.8608391782</v>
       </c>
       <c r="O261" t="n">
-        <v>881848.2579629922</v>
+        <v>881322.1741307178</v>
       </c>
       <c r="P261" t="n">
         <v>5600</v>
@@ -11975,10 +11975,10 @@
         <v>28</v>
       </c>
       <c r="N266" t="n">
-        <v>3283.163260274</v>
+        <v>3230.0662191781</v>
       </c>
       <c r="O266" t="n">
-        <v>91928.57128767201</v>
+        <v>90441.85413698679</v>
       </c>
       <c r="P266" t="n">
         <v>6200</v>
@@ -12485,10 +12485,10 @@
         <v>1</v>
       </c>
       <c r="N277" t="n">
-        <v>8820</v>
+        <v>8796</v>
       </c>
       <c r="O277" t="n">
-        <v>8820</v>
+        <v>8796</v>
       </c>
       <c r="P277" t="n">
         <v>14900</v>
@@ -14688,10 +14688,10 @@
         <v>40</v>
       </c>
       <c r="N326" t="n">
-        <v>4372.0654674395</v>
+        <v>4371.1712628708</v>
       </c>
       <c r="O326" t="n">
-        <v>174882.61869758</v>
+        <v>174846.850514832</v>
       </c>
       <c r="P326" t="n">
         <v>8900</v>
@@ -14947,10 +14947,10 @@
         <v>11</v>
       </c>
       <c r="N332" t="n">
-        <v>5371.5779551122</v>
+        <v>5331.69</v>
       </c>
       <c r="O332" t="n">
-        <v>59087.3575062342</v>
+        <v>58648.59</v>
       </c>
       <c r="P332" t="n">
         <v>7900</v>
@@ -16167,10 +16167,10 @@
         <v>4</v>
       </c>
       <c r="N359" t="n">
-        <v>3776.2176165803</v>
+        <v>3761.6</v>
       </c>
       <c r="O359" t="n">
-        <v>15104.8704663212</v>
+        <v>15046.4</v>
       </c>
       <c r="P359" t="n">
         <v>6900</v>
@@ -17151,10 +17151,10 @@
         <v>10</v>
       </c>
       <c r="N381" t="n">
-        <v>19114.611111111</v>
+        <v>18598</v>
       </c>
       <c r="O381" t="n">
-        <v>191146.11111111</v>
+        <v>185980</v>
       </c>
       <c r="P381" t="n">
         <v>21900</v>
@@ -19165,10 +19165,10 @@
         <v>6</v>
       </c>
       <c r="N426" t="n">
-        <v>7719.830483871</v>
+        <v>7537.4723387097</v>
       </c>
       <c r="O426" t="n">
-        <v>46318.982903226</v>
+        <v>45224.8340322582</v>
       </c>
       <c r="P426" t="n">
         <v>8900</v>
@@ -19373,10 +19373,10 @@
         <v>5</v>
       </c>
       <c r="N431" t="n">
-        <v>8799.4655328798</v>
+        <v>8794.48</v>
       </c>
       <c r="O431" t="n">
-        <v>43997.327664399</v>
+        <v>43972.39999999999</v>
       </c>
       <c r="P431" t="n">
         <v>14500</v>
@@ -21348,10 +21348,10 @@
         <v>8</v>
       </c>
       <c r="N477" t="n">
-        <v>4102.8563673709</v>
+        <v>4100.45</v>
       </c>
       <c r="O477" t="n">
-        <v>32822.8509389672</v>
+        <v>32803.6</v>
       </c>
       <c r="P477" t="n">
         <v>26900</v>
@@ -21481,10 +21481,10 @@
         <v>7</v>
       </c>
       <c r="N480" t="n">
-        <v>5455.0456387665</v>
+        <v>5431.12</v>
       </c>
       <c r="O480" t="n">
-        <v>38185.3194713655</v>
+        <v>38017.84</v>
       </c>
       <c r="P480" t="n">
         <v>8900</v>
@@ -24423,10 +24423,10 @@
         <v>29</v>
       </c>
       <c r="N546" t="n">
-        <v>9252.7923611111</v>
+        <v>9188.98</v>
       </c>
       <c r="O546" t="n">
-        <v>268330.9784722219</v>
+        <v>266480.42</v>
       </c>
       <c r="P546" t="n">
         <v>12900</v>
@@ -25017,10 +25017,10 @@
         <v>8</v>
       </c>
       <c r="N559" t="n">
-        <v>18023.2064</v>
+        <v>18016</v>
       </c>
       <c r="O559" t="n">
-        <v>144185.6512</v>
+        <v>144128</v>
       </c>
       <c r="P559" t="n">
         <v>29900</v>
@@ -26408,10 +26408,10 @@
         <v>1</v>
       </c>
       <c r="N589" t="n">
-        <v>7961.912</v>
+        <v>7108.85</v>
       </c>
       <c r="O589" t="n">
-        <v>7961.912</v>
+        <v>7108.85</v>
       </c>
       <c r="P589" t="n">
         <v>7900</v>
@@ -27145,10 +27145,10 @@
         <v>7</v>
       </c>
       <c r="N605" t="n">
-        <v>6074.962962963</v>
+        <v>5858</v>
       </c>
       <c r="O605" t="n">
-        <v>42524.740740741</v>
+        <v>41006</v>
       </c>
       <c r="P605" t="n">
         <v>9500</v>
@@ -29907,10 +29907,10 @@
         <v>62</v>
       </c>
       <c r="N665" t="n">
-        <v>60093.865363735</v>
+        <v>59834</v>
       </c>
       <c r="O665" t="n">
-        <v>3725819.65255157</v>
+        <v>3709708</v>
       </c>
       <c r="P665" t="n">
         <v>7900</v>
@@ -30321,10 +30321,10 @@
         <v>30</v>
       </c>
       <c r="N674" t="n">
-        <v>40318.846625767</v>
+        <v>40073</v>
       </c>
       <c r="O674" t="n">
-        <v>1209565.39877301</v>
+        <v>1202190</v>
       </c>
       <c r="P674" t="n">
         <v>64900</v>
@@ -30505,10 +30505,10 @@
         <v>1</v>
       </c>
       <c r="N678" t="n">
-        <v>3652.664695122</v>
+        <v>3639.35</v>
       </c>
       <c r="O678" t="n">
-        <v>3652.664695122</v>
+        <v>3639.35</v>
       </c>
       <c r="P678" t="n">
         <v>7500</v>
@@ -31152,10 +31152,10 @@
         <v>163</v>
       </c>
       <c r="N692" t="n">
-        <v>2463.8091310592</v>
+        <v>2458.5124991023</v>
       </c>
       <c r="O692" t="n">
-        <v>401600.8883626496</v>
+        <v>400737.5373536749</v>
       </c>
       <c r="P692" t="n">
         <v>3500</v>
@@ -34228,10 +34228,10 @@
         <v>6</v>
       </c>
       <c r="N758" t="n">
-        <v>3650.5019029126</v>
+        <v>3629.36</v>
       </c>
       <c r="O758" t="n">
-        <v>21903.0114174756</v>
+        <v>21776.16</v>
       </c>
       <c r="P758" t="n">
         <v>3900</v>
@@ -35639,10 +35639,10 @@
         <v>718</v>
       </c>
       <c r="N788" t="n">
-        <v>345.63428985635</v>
+        <v>345.55838597724</v>
       </c>
       <c r="O788" t="n">
-        <v>248165.4201168593</v>
+        <v>248110.9211316583</v>
       </c>
       <c r="P788" t="n">
         <v>600</v>
@@ -35781,10 +35781,10 @@
         <v>350</v>
       </c>
       <c r="N791" t="n">
-        <v>711.87861852814</v>
+        <v>711.33664519481</v>
       </c>
       <c r="O791" t="n">
-        <v>249157.516484849</v>
+        <v>248967.8258181835</v>
       </c>
       <c r="P791" t="n">
         <v>900</v>
@@ -36747,10 +36747,10 @@
         <v>1</v>
       </c>
       <c r="N812" t="n">
-        <v>3285.20748</v>
+        <v>3259.13444</v>
       </c>
       <c r="O812" t="n">
-        <v>3285.20748</v>
+        <v>3259.13444</v>
       </c>
       <c r="P812" t="n">
         <v>3600</v>
@@ -42269,10 +42269,10 @@
         <v>5</v>
       </c>
       <c r="N928" t="n">
-        <v>5480.6844036697</v>
+        <v>5430.86</v>
       </c>
       <c r="O928" t="n">
-        <v>27403.4220183485</v>
+        <v>27154.3</v>
       </c>
       <c r="P928" t="n">
         <v>13900</v>
@@ -43377,10 +43377,10 @@
         <v>3</v>
       </c>
       <c r="N951" t="n">
-        <v>4234.4238541667</v>
+        <v>4190.77</v>
       </c>
       <c r="O951" t="n">
-        <v>12703.2715625001</v>
+        <v>12572.31</v>
       </c>
       <c r="P951" t="n">
         <v>5900</v>
@@ -43426,10 +43426,10 @@
         <v>15</v>
       </c>
       <c r="N952" t="n">
-        <v>3503.9263942308</v>
+        <v>3499.72</v>
       </c>
       <c r="O952" t="n">
-        <v>52558.89591346199</v>
+        <v>52495.8</v>
       </c>
       <c r="P952" t="n">
         <v>6900</v>
@@ -43475,10 +43475,10 @@
         <v>6</v>
       </c>
       <c r="N953" t="n">
-        <v>5370.7341880342</v>
+        <v>5347.88</v>
       </c>
       <c r="O953" t="n">
-        <v>32224.4051282052</v>
+        <v>32087.28</v>
       </c>
       <c r="P953" t="n">
         <v>7900</v>
@@ -43524,10 +43524,10 @@
         <v>10</v>
       </c>
       <c r="N954" t="n">
-        <v>4593.2494352159</v>
+        <v>4578.04</v>
       </c>
       <c r="O954" t="n">
-        <v>45932.494352159</v>
+        <v>45780.4</v>
       </c>
       <c r="P954" t="n">
         <v>7500</v>
@@ -45743,10 +45743,10 @@
         <v>261</v>
       </c>
       <c r="N1000" t="n">
-        <v>7056.0857581657</v>
+        <v>7046.9398269522</v>
       </c>
       <c r="O1000" t="n">
-        <v>1841638.382881248</v>
+        <v>1839251.294834524</v>
       </c>
       <c r="P1000" t="n">
         <v>9900</v>
@@ -52360,10 +52360,10 @@
         <v>8</v>
       </c>
       <c r="N1142" t="n">
-        <v>12545.454545455</v>
+        <v>12000</v>
       </c>
       <c r="O1142" t="n">
-        <v>100363.63636364</v>
+        <v>96000</v>
       </c>
       <c r="P1142" t="n">
         <v>15000</v>
@@ -53582,10 +53582,10 @@
         <v>2</v>
       </c>
       <c r="N1169" t="n">
-        <v>18186.087111111</v>
+        <v>17986.24</v>
       </c>
       <c r="O1169" t="n">
-        <v>36372.174222222</v>
+        <v>35972.48</v>
       </c>
       <c r="P1169" t="n">
         <v>18500</v>
@@ -54275,10 +54275,10 @@
         <v>40</v>
       </c>
       <c r="N1184" t="n">
-        <v>7496.4757709251</v>
+        <v>7480</v>
       </c>
       <c r="O1184" t="n">
-        <v>299859.030837004</v>
+        <v>299200</v>
       </c>
       <c r="P1184" t="n">
         <v>9500</v>
@@ -54321,10 +54321,10 @@
         <v>22</v>
       </c>
       <c r="N1185" t="n">
-        <v>6525.1343283582</v>
+        <v>6336</v>
       </c>
       <c r="O1185" t="n">
-        <v>143552.9552238804</v>
+        <v>139392</v>
       </c>
       <c r="P1185" t="n">
         <v>7500</v>
@@ -54413,10 +54413,10 @@
         <v>5</v>
       </c>
       <c r="N1187" t="n">
-        <v>5320.824742268</v>
+        <v>5280</v>
       </c>
       <c r="O1187" t="n">
-        <v>26604.12371134</v>
+        <v>26400</v>
       </c>
       <c r="P1187" t="n">
         <v>6900</v>
@@ -57052,10 +57052,10 @@
         <v>13</v>
       </c>
       <c r="N1244" t="n">
-        <v>965.501</v>
+        <v>910.85</v>
       </c>
       <c r="O1244" t="n">
-        <v>12551.513</v>
+        <v>11841.05</v>
       </c>
       <c r="P1244" t="n">
         <v>7900</v>
@@ -57144,10 +57144,10 @@
         <v>2</v>
       </c>
       <c r="N1246" t="n">
-        <v>4936.5625</v>
+        <v>3949.25</v>
       </c>
       <c r="O1246" t="n">
-        <v>9873.125</v>
+        <v>7898.5</v>
       </c>
       <c r="P1246" t="n">
         <v>12500</v>
@@ -61941,10 +61941,10 @@
         <v>14</v>
       </c>
       <c r="N1349" t="n">
-        <v>2547.0191593353</v>
+        <v>2539.5717399804</v>
       </c>
       <c r="O1349" t="n">
-        <v>35658.2682306942</v>
+        <v>35554.0043597256</v>
       </c>
       <c r="P1349" t="n">
         <v>2900</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -17460,10 +17460,10 @@
         <v>21</v>
       </c>
       <c r="N388" t="n">
-        <v>1302.8935476464</v>
+        <v>1301.3994029851</v>
       </c>
       <c r="O388" t="n">
-        <v>27360.7645005744</v>
+        <v>27329.3874626871</v>
       </c>
       <c r="P388" t="n">
         <v>2000</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
         </is>
       </c>
     </row>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -1402,25 +1402,25 @@
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="N25" t="n">
-        <v>1854.241047619</v>
+        <v>1854.2411004785</v>
       </c>
       <c r="O25" t="n">
-        <v>1854.241047619</v>
+        <v>103837.501626796</v>
       </c>
       <c r="P25" t="n">
         <v>3200</v>
       </c>
       <c r="Q25" t="n">
-        <v>3200</v>
+        <v>179200</v>
       </c>
     </row>
     <row r="26">
@@ -10278,22 +10278,22 @@
         <v>0</v>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M228" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N228" t="n">
         <v>4502.93</v>
       </c>
       <c r="O228" t="n">
-        <v>13508.79</v>
+        <v>4502.93</v>
       </c>
       <c r="P228" t="n">
         <v>6600</v>
       </c>
       <c r="Q228" t="n">
-        <v>19800</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="229">
@@ -14233,10 +14233,10 @@
         <v>14</v>
       </c>
       <c r="N316" t="n">
-        <v>12422.462959583</v>
+        <v>12422.46296087</v>
       </c>
       <c r="O316" t="n">
-        <v>173914.481434162</v>
+        <v>173914.48145218</v>
       </c>
       <c r="P316" t="n">
         <v>19900</v>
@@ -15656,22 +15656,22 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M348" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="N348" t="n">
         <v>1126.69</v>
       </c>
       <c r="O348" t="n">
-        <v>40560.84</v>
+        <v>34927.39</v>
       </c>
       <c r="P348" t="n">
         <v>1200</v>
       </c>
       <c r="Q348" t="n">
-        <v>43200</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="349">
@@ -16984,10 +16984,10 @@
         <v>1</v>
       </c>
       <c r="N377" t="n">
-        <v>2403.5207171448</v>
+        <v>2403.5207309746</v>
       </c>
       <c r="O377" t="n">
-        <v>2403.5207171448</v>
+        <v>2403.5207309746</v>
       </c>
       <c r="P377" t="n">
         <v>3500</v>
@@ -23498,22 +23498,22 @@
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M526" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N526" t="n">
         <v>2634.61</v>
       </c>
       <c r="O526" t="n">
-        <v>26346.1</v>
+        <v>23711.49</v>
       </c>
       <c r="P526" t="n">
         <v>4200</v>
       </c>
       <c r="Q526" t="n">
-        <v>42000</v>
+        <v>37800</v>
       </c>
     </row>
     <row r="527">
@@ -31845,10 +31845,10 @@
         <v>1</v>
       </c>
       <c r="N707" t="n">
-        <v>1592.2857321429</v>
+        <v>1592.2857602862</v>
       </c>
       <c r="O707" t="n">
-        <v>1592.2857321429</v>
+        <v>1592.2857602862</v>
       </c>
       <c r="P707" t="n">
         <v>2500</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -1531,10 +1531,10 @@
         <v>12</v>
       </c>
       <c r="N28" t="n">
-        <v>6272.855198556</v>
+        <v>6272.8552079566</v>
       </c>
       <c r="O28" t="n">
-        <v>75274.26238267199</v>
+        <v>75274.2624954792</v>
       </c>
       <c r="P28" t="n">
         <v>7900</v>
@@ -1974,10 +1974,10 @@
         <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>3716.3301967213</v>
+        <v>3716.3301970443</v>
       </c>
       <c r="O39" t="n">
-        <v>7432.6603934426</v>
+        <v>7432.6603940886</v>
       </c>
       <c r="P39" t="n">
         <v>9500</v>
@@ -13378,10 +13378,10 @@
         <v>25</v>
       </c>
       <c r="N297" t="n">
-        <v>3594.2529307806</v>
+        <v>3594.2529255711</v>
       </c>
       <c r="O297" t="n">
-        <v>89856.32326951499</v>
+        <v>89856.32313927751</v>
       </c>
       <c r="P297" t="n">
         <v>6500</v>
@@ -14233,10 +14233,10 @@
         <v>14</v>
       </c>
       <c r="N316" t="n">
-        <v>12422.462986842</v>
+        <v>12422.462990777</v>
       </c>
       <c r="O316" t="n">
-        <v>173914.481815788</v>
+        <v>173914.481870878</v>
       </c>
       <c r="P316" t="n">
         <v>19900</v>
@@ -14642,10 +14642,10 @@
         <v>22</v>
       </c>
       <c r="N325" t="n">
-        <v>3041.6600148258</v>
+        <v>3041.6600148478</v>
       </c>
       <c r="O325" t="n">
-        <v>66916.52032616759</v>
+        <v>66916.5203266516</v>
       </c>
       <c r="P325" t="n">
         <v>5500</v>
@@ -16754,10 +16754,10 @@
         <v>172</v>
       </c>
       <c r="N372" t="n">
-        <v>1630.9246804626</v>
+        <v>1630.9246976176</v>
       </c>
       <c r="O372" t="n">
-        <v>280519.0450395672</v>
+        <v>280519.0479902272</v>
       </c>
       <c r="P372" t="n">
         <v>2500</v>
@@ -20316,10 +20316,10 @@
         <v>1</v>
       </c>
       <c r="N453" t="n">
-        <v>4285.1964141414</v>
+        <v>4285.1964303797</v>
       </c>
       <c r="O453" t="n">
-        <v>4285.1964141414</v>
+        <v>4285.1964303797</v>
       </c>
       <c r="P453" t="n">
         <v>6900</v>
@@ -31103,10 +31103,10 @@
         <v>23</v>
       </c>
       <c r="N691" t="n">
-        <v>1516.0387356204</v>
+        <v>1516.0387309278</v>
       </c>
       <c r="O691" t="n">
-        <v>34868.8909192692</v>
+        <v>34868.8908113394</v>
       </c>
       <c r="P691" t="n">
         <v>2300</v>
@@ -47351,10 +47351,10 @@
         <v>37</v>
       </c>
       <c r="N1033" t="n">
-        <v>465.87102642276</v>
+        <v>465.87102746694</v>
       </c>
       <c r="O1033" t="n">
-        <v>17237.22797764212</v>
+        <v>17237.22801627678</v>
       </c>
       <c r="P1033" t="n">
         <v>2500</v>
@@ -62002,10 +62002,10 @@
         <v>6</v>
       </c>
       <c r="N1350" t="n">
-        <v>2539.571774676</v>
+        <v>2539.5717817818</v>
       </c>
       <c r="O1350" t="n">
-        <v>15237.430648056</v>
+        <v>15237.4306906908</v>
       </c>
       <c r="P1350" t="n">
         <v>2900</v>
@@ -62094,10 +62094,10 @@
         <v>14</v>
       </c>
       <c r="N1352" t="n">
-        <v>4171.6684503311</v>
+        <v>4171.6684420772</v>
       </c>
       <c r="O1352" t="n">
-        <v>58403.3583046354</v>
+        <v>58403.3581890808</v>
       </c>
       <c r="P1352" t="n">
         <v>5000</v>
@@ -66479,22 +66479,22 @@
         <v>0</v>
       </c>
       <c r="L1448" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1448" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N1448" t="n">
         <v>2210</v>
       </c>
       <c r="O1448" t="n">
-        <v>13260</v>
+        <v>8840</v>
       </c>
       <c r="P1448" t="n">
         <v>2700</v>
       </c>
       <c r="Q1448" t="n">
-        <v>16200</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="1449">
@@ -66626,22 +66626,22 @@
         <v>0</v>
       </c>
       <c r="L1451" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1451" t="n">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="N1451" t="n">
         <v>425</v>
       </c>
       <c r="O1451" t="n">
-        <v>153425</v>
+        <v>150875</v>
       </c>
       <c r="P1451" t="n">
         <v>500</v>
       </c>
       <c r="Q1451" t="n">
-        <v>180500</v>
+        <v>177500</v>
       </c>
     </row>
     <row r="1452">
@@ -66675,22 +66675,22 @@
         <v>0</v>
       </c>
       <c r="L1452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1452" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N1452" t="n">
         <v>1700</v>
       </c>
       <c r="O1452" t="n">
-        <v>159800</v>
+        <v>158100</v>
       </c>
       <c r="P1452" t="n">
         <v>2000</v>
       </c>
       <c r="Q1452" t="n">
-        <v>188000</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="1453">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -850,22 +850,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="N11" t="n">
-        <v>1811.3106796117</v>
+        <v>1811.3107843137</v>
       </c>
       <c r="O11" t="n">
-        <v>575996.7961165205</v>
+        <v>561506.343137247</v>
       </c>
       <c r="P11" t="n">
         <v>2600</v>
       </c>
       <c r="Q11" t="n">
-        <v>826800</v>
+        <v>806000</v>
       </c>
     </row>
     <row r="12">
@@ -11975,10 +11975,10 @@
         <v>28</v>
       </c>
       <c r="N266" t="n">
-        <v>3230.0661344538</v>
+        <v>3230.0661016949</v>
       </c>
       <c r="O266" t="n">
-        <v>90441.8517647064</v>
+        <v>90441.8508474572</v>
       </c>
       <c r="P266" t="n">
         <v>6200</v>
@@ -12427,25 +12427,25 @@
         <v>1</v>
       </c>
       <c r="K276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N276" t="n">
         <v>9664</v>
       </c>
       <c r="O276" t="n">
-        <v>9664</v>
+        <v>0</v>
       </c>
       <c r="P276" t="n">
         <v>15900</v>
       </c>
       <c r="Q276" t="n">
-        <v>15900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -12699,22 +12699,22 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M282" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N282" t="n">
-        <v>3795.7100076321</v>
+        <v>3795.710007638</v>
       </c>
       <c r="O282" t="n">
-        <v>106279.8802136988</v>
+        <v>91097.040183312</v>
       </c>
       <c r="P282" t="n">
         <v>6200</v>
       </c>
       <c r="Q282" t="n">
-        <v>173600</v>
+        <v>148800</v>
       </c>
     </row>
     <row r="283">
@@ -12925,10 +12925,10 @@
         <v>44</v>
       </c>
       <c r="N287" t="n">
-        <v>4890.9300537634</v>
+        <v>4890.9300539811</v>
       </c>
       <c r="O287" t="n">
-        <v>215200.9223655896</v>
+        <v>215200.9223751684</v>
       </c>
       <c r="P287" t="n">
         <v>8200</v>
@@ -14462,10 +14462,10 @@
         <v>63</v>
       </c>
       <c r="N321" t="n">
-        <v>3472.2762877567</v>
+        <v>3472.2762983503</v>
       </c>
       <c r="O321" t="n">
-        <v>218753.4061286721</v>
+        <v>218753.4067960689</v>
       </c>
       <c r="P321" t="n">
         <v>5900</v>
@@ -14688,10 +14688,10 @@
         <v>48</v>
       </c>
       <c r="N326" t="n">
-        <v>4371.1712633877</v>
+        <v>4371.171263905</v>
       </c>
       <c r="O326" t="n">
-        <v>209816.2206426096</v>
+        <v>209816.22066744</v>
       </c>
       <c r="P326" t="n">
         <v>8900</v>
@@ -16713,10 +16713,10 @@
         <v>172</v>
       </c>
       <c r="N371" t="n">
-        <v>1630.9246990529</v>
+        <v>1630.9247048027</v>
       </c>
       <c r="O371" t="n">
-        <v>280519.0482370988</v>
+        <v>280519.0492260644</v>
       </c>
       <c r="P371" t="n">
         <v>2500</v>
@@ -16943,10 +16943,10 @@
         <v>1</v>
       </c>
       <c r="N376" t="n">
-        <v>2403.5211979522</v>
+        <v>2403.5212124317</v>
       </c>
       <c r="O376" t="n">
-        <v>2403.5211979522</v>
+        <v>2403.5212124317</v>
       </c>
       <c r="P376" t="n">
         <v>3500</v>
@@ -20131,10 +20131,10 @@
         <v>17</v>
       </c>
       <c r="N449" t="n">
-        <v>6207.9882231175</v>
+        <v>6213.167301168</v>
       </c>
       <c r="O449" t="n">
-        <v>105535.7997929975</v>
+        <v>105623.844119856</v>
       </c>
       <c r="P449" t="n">
         <v>9900</v>
@@ -20654,10 +20654,10 @@
         <v>42</v>
       </c>
       <c r="N461" t="n">
-        <v>3591.13</v>
+        <v>3594.9639466192</v>
       </c>
       <c r="O461" t="n">
-        <v>150827.46</v>
+        <v>150988.4857580064</v>
       </c>
       <c r="P461" t="n">
         <v>6300</v>
@@ -22570,22 +22570,22 @@
         <v>0</v>
       </c>
       <c r="L505" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M505" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="N505" t="n">
-        <v>548.14706357215</v>
+        <v>548.14704568528</v>
       </c>
       <c r="O505" t="n">
-        <v>53718.4122300707</v>
+        <v>50429.52820304576</v>
       </c>
       <c r="P505" t="n">
         <v>2000</v>
       </c>
       <c r="Q505" t="n">
-        <v>196000</v>
+        <v>184000</v>
       </c>
     </row>
     <row r="506">
@@ -26873,10 +26873,10 @@
         <v>15</v>
       </c>
       <c r="N599" t="n">
-        <v>8858.16</v>
+        <v>8873.1568848758</v>
       </c>
       <c r="O599" t="n">
-        <v>132872.4</v>
+        <v>133097.353273137</v>
       </c>
       <c r="P599" t="n">
         <v>15500</v>
@@ -28630,10 +28630,10 @@
         <v>2</v>
       </c>
       <c r="N637" t="n">
-        <v>6849.2</v>
+        <v>6862.329456869</v>
       </c>
       <c r="O637" t="n">
-        <v>13698.4</v>
+        <v>13724.658913738</v>
       </c>
       <c r="P637" t="n">
         <v>11500</v>
@@ -30972,10 +30972,10 @@
         <v>23</v>
       </c>
       <c r="N688" t="n">
-        <v>1516.0387272539</v>
+        <v>1516.0387269907</v>
       </c>
       <c r="O688" t="n">
-        <v>34868.8907268397</v>
+        <v>34868.8907207861</v>
       </c>
       <c r="P688" t="n">
         <v>2300</v>
@@ -31156,10 +31156,10 @@
         <v>87</v>
       </c>
       <c r="N692" t="n">
-        <v>1771.0893205318</v>
+        <v>1771.0891278195</v>
       </c>
       <c r="O692" t="n">
-        <v>154084.7708862666</v>
+        <v>154084.7541202965</v>
       </c>
       <c r="P692" t="n">
         <v>2500</v>
@@ -31478,10 +31478,10 @@
         <v>66</v>
       </c>
       <c r="N699" t="n">
-        <v>3224.5699223947</v>
+        <v>3224.5699334073</v>
       </c>
       <c r="O699" t="n">
-        <v>212821.6148780502</v>
+        <v>212821.6156048818</v>
       </c>
       <c r="P699" t="n">
         <v>4500</v>
@@ -31524,10 +31524,10 @@
         <v>91</v>
       </c>
       <c r="N700" t="n">
-        <v>1655.9291188041</v>
+        <v>1655.9290150913</v>
       </c>
       <c r="O700" t="n">
-        <v>150689.5498111731</v>
+        <v>150689.5403733083</v>
       </c>
       <c r="P700" t="n">
         <v>2500</v>
@@ -36795,10 +36795,10 @@
         <v>58</v>
       </c>
       <c r="N813" t="n">
-        <v>3110.8359666534</v>
+        <v>3110.8359331476</v>
       </c>
       <c r="O813" t="n">
-        <v>180428.4860658972</v>
+        <v>180428.4841225608</v>
       </c>
       <c r="P813" t="n">
         <v>4500</v>
@@ -37020,22 +37020,22 @@
         <v>0</v>
       </c>
       <c r="L818" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M818" t="n">
-        <v>418</v>
+        <v>370</v>
       </c>
       <c r="N818" t="n">
-        <v>703.79469605084</v>
+        <v>703.79468467395</v>
       </c>
       <c r="O818" t="n">
-        <v>294186.1829492511</v>
+        <v>260404.0333293615</v>
       </c>
       <c r="P818" t="n">
         <v>900</v>
       </c>
       <c r="Q818" t="n">
-        <v>376200</v>
+        <v>333000</v>
       </c>
     </row>
     <row r="819">
@@ -40006,10 +40006,10 @@
         <v>5</v>
       </c>
       <c r="N881" t="n">
-        <v>2832.1953125</v>
+        <v>2832.1953968254</v>
       </c>
       <c r="O881" t="n">
-        <v>14160.9765625</v>
+        <v>14160.976984127</v>
       </c>
       <c r="P881" t="n">
         <v>12900</v>
@@ -42464,22 +42464,22 @@
         <v>0</v>
       </c>
       <c r="L932" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M932" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N932" t="n">
         <v>3000.33</v>
       </c>
       <c r="O932" t="n">
-        <v>498054.78</v>
+        <v>492054.12</v>
       </c>
       <c r="P932" t="n">
         <v>2900</v>
       </c>
       <c r="Q932" t="n">
-        <v>481400</v>
+        <v>475600</v>
       </c>
     </row>
     <row r="933">
@@ -53945,22 +53945,22 @@
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1177" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N1177" t="n">
         <v>6336</v>
       </c>
       <c r="O1177" t="n">
-        <v>101376</v>
+        <v>88704</v>
       </c>
       <c r="P1177" t="n">
         <v>7500</v>
       </c>
       <c r="Q1177" t="n">
-        <v>120000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="1178">
@@ -54221,22 +54221,22 @@
         <v>0</v>
       </c>
       <c r="L1183" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1183" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N1183" t="n">
         <v>6160</v>
       </c>
       <c r="O1183" t="n">
-        <v>850080</v>
+        <v>825440</v>
       </c>
       <c r="P1183" t="n">
         <v>7500</v>
       </c>
       <c r="Q1183" t="n">
-        <v>1035000</v>
+        <v>1005000</v>
       </c>
     </row>
     <row r="1184">
@@ -54558,22 +54558,22 @@
         <v>0</v>
       </c>
       <c r="L1190" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M1190" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N1190" t="n">
         <v>9240</v>
       </c>
       <c r="O1190" t="n">
-        <v>693000</v>
+        <v>619080</v>
       </c>
       <c r="P1190" t="n">
         <v>11500</v>
       </c>
       <c r="Q1190" t="n">
-        <v>862500</v>
+        <v>770500</v>
       </c>
     </row>
     <row r="1191">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -15517,22 +15517,22 @@
         <v>0</v>
       </c>
       <c r="L345" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M345" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N345" t="n">
         <v>1387.55</v>
       </c>
       <c r="O345" t="n">
-        <v>36076.3</v>
+        <v>30526.1</v>
       </c>
       <c r="P345" t="n">
         <v>2300</v>
       </c>
       <c r="Q345" t="n">
-        <v>59800</v>
+        <v>50600</v>
       </c>
     </row>
     <row r="346">
@@ -36887,10 +36887,10 @@
         <v>437</v>
       </c>
       <c r="N815" t="n">
-        <v>703.79463731331</v>
+        <v>703.79463559345</v>
       </c>
       <c r="O815" t="n">
-        <v>307558.2565059165</v>
+        <v>307558.2557543376</v>
       </c>
       <c r="P815" t="n">
         <v>900</v>
@@ -61679,10 +61679,10 @@
         <v>14</v>
       </c>
       <c r="N1343" t="n">
-        <v>4171.6683165468</v>
+        <v>4171.668314121</v>
       </c>
       <c r="O1343" t="n">
-        <v>58403.35643165521</v>
+        <v>58403.35639769399</v>
       </c>
       <c r="P1343" t="n">
         <v>5000</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -759,28 +759,28 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N9" t="n">
         <v>27000</v>
       </c>
       <c r="O9" t="n">
-        <v>405000</v>
+        <v>378000</v>
       </c>
       <c r="P9" t="n">
         <v>20000</v>
       </c>
       <c r="Q9" t="n">
-        <v>300000</v>
+        <v>280000</v>
       </c>
     </row>
     <row r="10">
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>4</v>
@@ -1362,28 +1362,28 @@
         </is>
       </c>
       <c r="J24" t="n">
+        <v>9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
         <v>8</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>9</v>
       </c>
       <c r="N24" t="n">
         <v>27000</v>
       </c>
       <c r="O24" t="n">
-        <v>243000</v>
+        <v>216000</v>
       </c>
       <c r="P24" t="n">
         <v>20000</v>
       </c>
       <c r="Q24" t="n">
-        <v>180000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="25">
@@ -11367,22 +11367,22 @@
         <v>0</v>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M253" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N253" t="n">
         <v>10600</v>
       </c>
       <c r="O253" t="n">
-        <v>159000</v>
+        <v>127200</v>
       </c>
       <c r="P253" t="n">
         <v>17200</v>
       </c>
       <c r="Q253" t="n">
-        <v>258000</v>
+        <v>206400</v>
       </c>
     </row>
     <row r="254">
@@ -11410,10 +11410,10 @@
         <v>29</v>
       </c>
       <c r="K254" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L254" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
         <v>29</v>
@@ -13094,10 +13094,10 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="K291" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L291" t="n">
         <v>0</v>
@@ -13941,28 +13941,28 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K310" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M310" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N310" t="n">
         <v>2665.4</v>
       </c>
       <c r="O310" t="n">
-        <v>45311.8</v>
+        <v>42646.4</v>
       </c>
       <c r="P310" t="n">
         <v>20900</v>
       </c>
       <c r="Q310" t="n">
-        <v>355300</v>
+        <v>334400</v>
       </c>
     </row>
     <row r="311">
@@ -14450,10 +14450,10 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="K321" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L321" t="n">
         <v>0</v>
@@ -18198,22 +18198,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M404" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N404" t="n">
         <v>7028</v>
       </c>
       <c r="O404" t="n">
-        <v>217868</v>
+        <v>203812</v>
       </c>
       <c r="P404" t="n">
         <v>15900</v>
       </c>
       <c r="Q404" t="n">
-        <v>492900</v>
+        <v>461100</v>
       </c>
     </row>
     <row r="405">
@@ -19858,10 +19858,10 @@
         </is>
       </c>
       <c r="J443" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K443" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L443" t="n">
         <v>0</v>
@@ -20078,10 +20078,10 @@
         </is>
       </c>
       <c r="J448" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="K448" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L448" t="n">
         <v>0</v>
@@ -20438,22 +20438,22 @@
         <v>0</v>
       </c>
       <c r="L456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M456" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N456" t="n">
         <v>38263.73</v>
       </c>
       <c r="O456" t="n">
-        <v>267846.11</v>
+        <v>229582.38</v>
       </c>
       <c r="P456" t="n">
         <v>61900</v>
       </c>
       <c r="Q456" t="n">
-        <v>433300</v>
+        <v>371400</v>
       </c>
     </row>
     <row r="457">
@@ -20601,28 +20601,28 @@
         </is>
       </c>
       <c r="J460" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K460" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L460" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M460" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N460" t="n">
         <v>3591.13</v>
       </c>
       <c r="O460" t="n">
-        <v>50275.82</v>
+        <v>43093.56</v>
       </c>
       <c r="P460" t="n">
         <v>6300</v>
       </c>
       <c r="Q460" t="n">
-        <v>88200</v>
+        <v>75600</v>
       </c>
     </row>
     <row r="461">
@@ -20786,22 +20786,22 @@
         <v>0</v>
       </c>
       <c r="L464" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M464" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N464" t="n">
         <v>12214</v>
       </c>
       <c r="O464" t="n">
-        <v>24428</v>
+        <v>0</v>
       </c>
       <c r="P464" t="n">
         <v>20900</v>
       </c>
       <c r="Q464" t="n">
-        <v>41800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="465">
@@ -21610,22 +21610,22 @@
         <v>0</v>
       </c>
       <c r="L483" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M483" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N483" t="n">
         <v>6925.19</v>
       </c>
       <c r="O483" t="n">
-        <v>69251.89999999999</v>
+        <v>55401.52</v>
       </c>
       <c r="P483" t="n">
         <v>12800</v>
       </c>
       <c r="Q483" t="n">
-        <v>128000</v>
+        <v>102400</v>
       </c>
     </row>
     <row r="484">
@@ -22569,10 +22569,10 @@
         </is>
       </c>
       <c r="J505" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K505" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L505" t="n">
         <v>0</v>
@@ -23239,22 +23239,22 @@
         <v>0</v>
       </c>
       <c r="L520" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M520" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N520" t="n">
         <v>7700</v>
       </c>
       <c r="O520" t="n">
-        <v>146300</v>
+        <v>123200</v>
       </c>
       <c r="P520" t="n">
         <v>13900</v>
       </c>
       <c r="Q520" t="n">
-        <v>264100</v>
+        <v>222400</v>
       </c>
     </row>
     <row r="521">
@@ -24618,10 +24618,10 @@
         </is>
       </c>
       <c r="J550" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="K550" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L550" t="n">
         <v>0</v>
@@ -26969,22 +26969,22 @@
         <v>0</v>
       </c>
       <c r="L601" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M601" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N601" t="n">
         <v>5858</v>
       </c>
       <c r="O601" t="n">
-        <v>35148</v>
+        <v>29290</v>
       </c>
       <c r="P601" t="n">
         <v>9500</v>
       </c>
       <c r="Q601" t="n">
-        <v>57000</v>
+        <v>47500</v>
       </c>
     </row>
     <row r="602">
@@ -27754,10 +27754,10 @@
         </is>
       </c>
       <c r="J618" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K618" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L618" t="n">
         <v>0</v>
@@ -27846,10 +27846,10 @@
         </is>
       </c>
       <c r="J620" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K620" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L620" t="n">
         <v>0</v>
@@ -27898,22 +27898,22 @@
         <v>0</v>
       </c>
       <c r="L621" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M621" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="N621" t="n">
         <v>4907.8227973568</v>
       </c>
       <c r="O621" t="n">
-        <v>260114.6082599104</v>
+        <v>230667.6714757696</v>
       </c>
       <c r="P621" t="n">
         <v>8200</v>
       </c>
       <c r="Q621" t="n">
-        <v>434600</v>
+        <v>385400</v>
       </c>
     </row>
     <row r="622">
@@ -28404,22 +28404,22 @@
         <v>0</v>
       </c>
       <c r="L632" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M632" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N632" t="n">
         <v>11922</v>
       </c>
       <c r="O632" t="n">
-        <v>83454</v>
+        <v>59610</v>
       </c>
       <c r="P632" t="n">
         <v>19900</v>
       </c>
       <c r="Q632" t="n">
-        <v>139300</v>
+        <v>99500</v>
       </c>
     </row>
     <row r="633">
@@ -28726,22 +28726,22 @@
         <v>0</v>
       </c>
       <c r="L639" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M639" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N639" t="n">
         <v>8637</v>
       </c>
       <c r="O639" t="n">
-        <v>77733</v>
+        <v>69096</v>
       </c>
       <c r="P639" t="n">
         <v>14500</v>
       </c>
       <c r="Q639" t="n">
-        <v>130500</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="640">
@@ -28858,10 +28858,10 @@
         </is>
       </c>
       <c r="J642" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K642" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L642" t="n">
         <v>0</v>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="J643" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K643" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L643" t="n">
         <v>0</v>
@@ -29134,10 +29134,10 @@
         </is>
       </c>
       <c r="J648" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K648" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L648" t="n">
         <v>0</v>
@@ -30421,22 +30421,22 @@
         <v>0</v>
       </c>
       <c r="L676" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M676" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N676" t="n">
         <v>3639.35</v>
       </c>
       <c r="O676" t="n">
-        <v>58229.6</v>
+        <v>54590.25</v>
       </c>
       <c r="P676" t="n">
         <v>7500</v>
       </c>
       <c r="Q676" t="n">
-        <v>120000</v>
+        <v>112500</v>
       </c>
     </row>
     <row r="677">
@@ -30513,22 +30513,22 @@
         <v>0</v>
       </c>
       <c r="L678" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M678" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N678" t="n">
         <v>5640</v>
       </c>
       <c r="O678" t="n">
-        <v>118440</v>
+        <v>112800</v>
       </c>
       <c r="P678" t="n">
         <v>9900</v>
       </c>
       <c r="Q678" t="n">
-        <v>207900</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="679">
@@ -30559,22 +30559,22 @@
         <v>0</v>
       </c>
       <c r="L679" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M679" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N679" t="n">
         <v>10713.21</v>
       </c>
       <c r="O679" t="n">
-        <v>203550.99</v>
+        <v>192837.78</v>
       </c>
       <c r="P679" t="n">
         <v>20900</v>
       </c>
       <c r="Q679" t="n">
-        <v>397100</v>
+        <v>376200</v>
       </c>
     </row>
     <row r="680">
@@ -32350,10 +32350,10 @@
         </is>
       </c>
       <c r="J718" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K718" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L718" t="n">
         <v>0</v>
@@ -32448,10 +32448,10 @@
         </is>
       </c>
       <c r="J720" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K720" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L720" t="n">
         <v>0</v>
@@ -32497,10 +32497,10 @@
         </is>
       </c>
       <c r="J721" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K721" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L721" t="n">
         <v>0</v>
@@ -32546,10 +32546,10 @@
         </is>
       </c>
       <c r="J722" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="K722" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L722" t="n">
         <v>0</v>
@@ -39535,22 +39535,22 @@
         <v>0</v>
       </c>
       <c r="L871" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M871" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N871" t="n">
         <v>10548.76</v>
       </c>
       <c r="O871" t="n">
-        <v>84390.08</v>
+        <v>73841.32000000001</v>
       </c>
       <c r="P871" t="n">
         <v>35900</v>
       </c>
       <c r="Q871" t="n">
-        <v>287200</v>
+        <v>251300</v>
       </c>
     </row>
     <row r="872">
@@ -40540,28 +40540,28 @@
         </is>
       </c>
       <c r="J892" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K892" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L892" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M892" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N892" t="n">
         <v>5798.41</v>
       </c>
       <c r="O892" t="n">
-        <v>98572.97</v>
+        <v>92774.56</v>
       </c>
       <c r="P892" t="n">
         <v>14900</v>
       </c>
       <c r="Q892" t="n">
-        <v>253300</v>
+        <v>238400</v>
       </c>
     </row>
     <row r="893">
@@ -40586,10 +40586,10 @@
         </is>
       </c>
       <c r="J893" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K893" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L893" t="n">
         <v>0</v>
@@ -40638,22 +40638,22 @@
         <v>0</v>
       </c>
       <c r="L894" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M894" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N894" t="n">
         <v>3100.87</v>
       </c>
       <c r="O894" t="n">
-        <v>83723.48999999999</v>
+        <v>77521.75</v>
       </c>
       <c r="P894" t="n">
         <v>9900</v>
       </c>
       <c r="Q894" t="n">
-        <v>267300</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="895">
@@ -41701,22 +41701,22 @@
         <v>0</v>
       </c>
       <c r="L916" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M916" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N916" t="n">
         <v>11085.19</v>
       </c>
       <c r="O916" t="n">
-        <v>144107.47</v>
+        <v>133022.28</v>
       </c>
       <c r="P916" t="n">
         <v>25900</v>
       </c>
       <c r="Q916" t="n">
-        <v>336700</v>
+        <v>310800</v>
       </c>
     </row>
     <row r="917">
@@ -41995,22 +41995,22 @@
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M922" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N922" t="n">
         <v>5430.86</v>
       </c>
       <c r="O922" t="n">
-        <v>65170.31999999999</v>
+        <v>54308.6</v>
       </c>
       <c r="P922" t="n">
         <v>13900</v>
       </c>
       <c r="Q922" t="n">
-        <v>166800</v>
+        <v>139000</v>
       </c>
     </row>
     <row r="923">
@@ -42139,10 +42139,10 @@
         <v>12</v>
       </c>
       <c r="K925" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L925" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M925" t="n">
         <v>12</v>
@@ -42234,10 +42234,10 @@
         </is>
       </c>
       <c r="J927" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K927" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L927" t="n">
         <v>0</v>
@@ -42615,10 +42615,10 @@
         </is>
       </c>
       <c r="J935" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K935" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L935" t="n">
         <v>0</v>
@@ -43054,22 +43054,22 @@
         <v>0</v>
       </c>
       <c r="L944" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M944" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N944" t="n">
         <v>3911.35</v>
       </c>
       <c r="O944" t="n">
-        <v>15645.4</v>
+        <v>7822.7</v>
       </c>
       <c r="P944" t="n">
         <v>7900</v>
       </c>
       <c r="Q944" t="n">
-        <v>31600</v>
+        <v>15800</v>
       </c>
     </row>
     <row r="945">
@@ -44271,22 +44271,22 @@
         <v>0</v>
       </c>
       <c r="L969" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M969" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N969" t="n">
         <v>15347.45</v>
       </c>
       <c r="O969" t="n">
-        <v>291601.55</v>
+        <v>276254.1</v>
       </c>
       <c r="P969" t="n">
         <v>23900</v>
       </c>
       <c r="Q969" t="n">
-        <v>454100</v>
+        <v>430200</v>
       </c>
     </row>
     <row r="970">
@@ -44314,10 +44314,10 @@
         </is>
       </c>
       <c r="J970" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K970" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L970" t="n">
         <v>0</v>
@@ -47952,22 +47952,22 @@
         <v>0</v>
       </c>
       <c r="L1046" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1046" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N1046" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1046" t="n">
-        <v>31819</v>
+        <v>12727.6</v>
       </c>
       <c r="P1046" t="n">
         <v>5100</v>
       </c>
       <c r="Q1046" t="n">
-        <v>51000</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="1047">
@@ -57736,10 +57736,10 @@
         </is>
       </c>
       <c r="J1258" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K1258" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L1258" t="n">
         <v>0</v>
@@ -58600,22 +58600,22 @@
         <v>0</v>
       </c>
       <c r="L1276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1276" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N1276" t="n">
         <v>22654.339166667</v>
       </c>
       <c r="O1276" t="n">
-        <v>158580.374166669</v>
+        <v>135926.035000002</v>
       </c>
       <c r="P1276" t="n">
         <v>58900</v>
       </c>
       <c r="Q1276" t="n">
-        <v>412300</v>
+        <v>353400</v>
       </c>
     </row>
     <row r="1277">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -556,10 +556,10 @@
         <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27065.693430657</v>
       </c>
       <c r="O4" t="n">
-        <v>270000</v>
+        <v>270656.93430657</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -771,10 +771,10 @@
         <v>14</v>
       </c>
       <c r="N9" t="n">
-        <v>27000</v>
+        <v>27109.756097561</v>
       </c>
       <c r="O9" t="n">
-        <v>378000</v>
+        <v>379536.585365854</v>
       </c>
       <c r="P9" t="n">
         <v>20000</v>
@@ -1335,10 +1335,10 @@
         <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>27000</v>
+        <v>27267.326732673</v>
       </c>
       <c r="O23" t="n">
-        <v>108000</v>
+        <v>109069.306930692</v>
       </c>
       <c r="P23" t="n">
         <v>20000</v>
@@ -1374,10 +1374,10 @@
         <v>8</v>
       </c>
       <c r="N24" t="n">
-        <v>27000</v>
+        <v>27151.898734177</v>
       </c>
       <c r="O24" t="n">
-        <v>216000</v>
+        <v>217215.189873416</v>
       </c>
       <c r="P24" t="n">
         <v>20000</v>
@@ -1609,10 +1609,10 @@
         <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>3926.8370711297</v>
+        <v>3926.837066527</v>
       </c>
       <c r="O30" t="n">
-        <v>54975.7189958158</v>
+        <v>54975.718931378</v>
       </c>
       <c r="P30" t="n">
         <v>4800</v>
@@ -1974,10 +1974,10 @@
         <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>3716.3301970443</v>
+        <v>3716.3301973684</v>
       </c>
       <c r="O39" t="n">
-        <v>7432.6603940886</v>
+        <v>7432.6603947368</v>
       </c>
       <c r="P39" t="n">
         <v>9500</v>
@@ -11327,10 +11327,10 @@
         <v>4</v>
       </c>
       <c r="N252" t="n">
-        <v>2582.2548125</v>
+        <v>2582.2547989556</v>
       </c>
       <c r="O252" t="n">
-        <v>10329.01925</v>
+        <v>10329.0191958224</v>
       </c>
       <c r="P252" t="n">
         <v>4500</v>
@@ -11373,10 +11373,10 @@
         <v>12</v>
       </c>
       <c r="N253" t="n">
-        <v>10600</v>
+        <v>10614.851138354</v>
       </c>
       <c r="O253" t="n">
-        <v>127200</v>
+        <v>127378.213660248</v>
       </c>
       <c r="P253" t="n">
         <v>17200</v>
@@ -11975,10 +11975,10 @@
         <v>43</v>
       </c>
       <c r="N266" t="n">
-        <v>3230.0657538462</v>
+        <v>3230.0657009346</v>
       </c>
       <c r="O266" t="n">
-        <v>138892.8274153866</v>
+        <v>138892.8251401878</v>
       </c>
       <c r="P266" t="n">
         <v>6200</v>
@@ -12876,10 +12876,10 @@
         <v>43</v>
       </c>
       <c r="N286" t="n">
-        <v>4890.9300552868</v>
+        <v>4890.930055517</v>
       </c>
       <c r="O286" t="n">
-        <v>210309.9923773324</v>
+        <v>210309.992387231</v>
       </c>
       <c r="P286" t="n">
         <v>8200</v>
@@ -13644,10 +13644,10 @@
         <v>8</v>
       </c>
       <c r="N303" t="n">
-        <v>14822.378817006</v>
+        <v>14822.378814083</v>
       </c>
       <c r="O303" t="n">
-        <v>118579.030536048</v>
+        <v>118579.030512664</v>
       </c>
       <c r="P303" t="n">
         <v>24900</v>
@@ -14227,22 +14227,22 @@
         <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M316" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N316" t="n">
-        <v>12422.463007951</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O316" t="n">
-        <v>285716.649182873</v>
+        <v>248449.26026548</v>
       </c>
       <c r="P316" t="n">
         <v>19900</v>
       </c>
       <c r="Q316" t="n">
-        <v>457700</v>
+        <v>398000</v>
       </c>
     </row>
     <row r="317">
@@ -14462,10 +14462,10 @@
         <v>67</v>
       </c>
       <c r="N321" t="n">
-        <v>3472.2763500602</v>
+        <v>3472.2763717066</v>
       </c>
       <c r="O321" t="n">
-        <v>232642.5154540334</v>
+        <v>232642.5169043422</v>
       </c>
       <c r="P321" t="n">
         <v>5900</v>
@@ -14642,10 +14642,10 @@
         <v>22</v>
       </c>
       <c r="N325" t="n">
-        <v>3041.6600149925</v>
+        <v>3041.660015015</v>
       </c>
       <c r="O325" t="n">
-        <v>66916.520329835</v>
+        <v>66916.52033033001</v>
       </c>
       <c r="P325" t="n">
         <v>5500</v>
@@ -14688,10 +14688,10 @@
         <v>48</v>
       </c>
       <c r="N326" t="n">
-        <v>4371.1729689003</v>
+        <v>4371.1729703288</v>
       </c>
       <c r="O326" t="n">
-        <v>209816.3025072144</v>
+        <v>209816.3025757824</v>
       </c>
       <c r="P326" t="n">
         <v>8900</v>
@@ -14778,10 +14778,10 @@
         <v>43</v>
       </c>
       <c r="N328" t="n">
-        <v>1592.5645263158</v>
+        <v>1592.5644086022</v>
       </c>
       <c r="O328" t="n">
-        <v>68480.27463157941</v>
+        <v>68480.2695698946</v>
       </c>
       <c r="P328" t="n">
         <v>3900</v>
@@ -16672,10 +16672,10 @@
         <v>172</v>
       </c>
       <c r="N370" t="n">
-        <v>1630.9249342316</v>
+        <v>1630.925009772</v>
       </c>
       <c r="O370" t="n">
-        <v>280519.0886878352</v>
+        <v>280519.101680784</v>
       </c>
       <c r="P370" t="n">
         <v>2500</v>
@@ -16764,10 +16764,10 @@
         <v>29</v>
       </c>
       <c r="N372" t="n">
-        <v>1690.5739608434</v>
+        <v>1690.5736115326</v>
       </c>
       <c r="O372" t="n">
-        <v>49026.64486445861</v>
+        <v>49026.6347344454</v>
       </c>
       <c r="P372" t="n">
         <v>2900</v>
@@ -16810,10 +16810,10 @@
         <v>12</v>
       </c>
       <c r="N373" t="n">
-        <v>1550.1949322169</v>
+        <v>1550.1949414115</v>
       </c>
       <c r="O373" t="n">
-        <v>18602.3391866028</v>
+        <v>18602.339296938</v>
       </c>
       <c r="P373" t="n">
         <v>2500</v>
@@ -16902,10 +16902,10 @@
         <v>1</v>
       </c>
       <c r="N375" t="n">
-        <v>2403.5224548084</v>
+        <v>2403.5228513613</v>
       </c>
       <c r="O375" t="n">
-        <v>2403.5224548084</v>
+        <v>2403.5228513613</v>
       </c>
       <c r="P375" t="n">
         <v>3500</v>
@@ -17159,10 +17159,10 @@
         <v>7</v>
       </c>
       <c r="N381" t="n">
-        <v>1830.7551149425</v>
+        <v>1830.7548795181</v>
       </c>
       <c r="O381" t="n">
-        <v>12815.2858045975</v>
+        <v>12815.2841566267</v>
       </c>
       <c r="P381" t="n">
         <v>3150</v>
@@ -18910,22 +18910,22 @@
         <v>0</v>
       </c>
       <c r="L420" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M420" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N420" t="n">
         <v>9338</v>
       </c>
       <c r="O420" t="n">
-        <v>149408</v>
+        <v>112056</v>
       </c>
       <c r="P420" t="n">
         <v>15500</v>
       </c>
       <c r="Q420" t="n">
-        <v>248000</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="421">
@@ -19414,10 +19414,10 @@
         <v>83</v>
       </c>
       <c r="N432" t="n">
-        <v>2029.8742253521</v>
+        <v>2029.8742541123</v>
       </c>
       <c r="O432" t="n">
-        <v>168479.5607042243</v>
+        <v>168479.5630913209</v>
       </c>
       <c r="P432" t="n">
         <v>3600</v>
@@ -19660,10 +19660,10 @@
         <v>9</v>
       </c>
       <c r="N438" t="n">
-        <v>2680.7396931747</v>
+        <v>2680.7396929825</v>
       </c>
       <c r="O438" t="n">
-        <v>24126.6572385723</v>
+        <v>24126.6572368425</v>
       </c>
       <c r="P438" t="n">
         <v>4900</v>
@@ -19957,10 +19957,10 @@
         <v>7</v>
       </c>
       <c r="N445" t="n">
-        <v>30611</v>
+        <v>30745.062773723</v>
       </c>
       <c r="O445" t="n">
-        <v>214277</v>
+        <v>215215.439416061</v>
       </c>
       <c r="P445" t="n">
         <v>38900</v>
@@ -20090,10 +20090,10 @@
         <v>43</v>
       </c>
       <c r="N448" t="n">
-        <v>6207.9882021366</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O448" t="n">
-        <v>266943.4926918738</v>
+        <v>266943.4926592583</v>
       </c>
       <c r="P448" t="n">
         <v>9900</v>
@@ -20185,10 +20185,10 @@
         <v>1</v>
       </c>
       <c r="N450" t="n">
-        <v>4285.1965633075</v>
+        <v>4285.1966145833</v>
       </c>
       <c r="O450" t="n">
-        <v>4285.1965633075</v>
+        <v>4285.1966145833</v>
       </c>
       <c r="P450" t="n">
         <v>6900</v>
@@ -20485,10 +20485,10 @@
         <v>2</v>
       </c>
       <c r="N457" t="n">
-        <v>1106</v>
+        <v>1111.1642023346</v>
       </c>
       <c r="O457" t="n">
-        <v>2212</v>
+        <v>2222.3284046692</v>
       </c>
       <c r="P457" t="n">
         <v>2100</v>
@@ -20572,10 +20572,10 @@
         <v>22</v>
       </c>
       <c r="N459" t="n">
-        <v>4814.2633769677</v>
+        <v>4814.2633736737</v>
       </c>
       <c r="O459" t="n">
-        <v>105913.7942932894</v>
+        <v>105913.7942208214</v>
       </c>
       <c r="P459" t="n">
         <v>9900</v>
@@ -20783,25 +20783,25 @@
         <v>2</v>
       </c>
       <c r="K464" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L464" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M464" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N464" t="n">
         <v>12214</v>
       </c>
       <c r="O464" t="n">
-        <v>0</v>
+        <v>48856</v>
       </c>
       <c r="P464" t="n">
         <v>20900</v>
       </c>
       <c r="Q464" t="n">
-        <v>0</v>
+        <v>83600</v>
       </c>
     </row>
     <row r="465">
@@ -21176,10 +21176,10 @@
         <v>11</v>
       </c>
       <c r="N473" t="n">
-        <v>27123.764688797</v>
+        <v>27123.764610526</v>
       </c>
       <c r="O473" t="n">
-        <v>298361.411576767</v>
+        <v>298361.410715786</v>
       </c>
       <c r="P473" t="n">
         <v>44500</v>
@@ -21309,10 +21309,10 @@
         <v>2</v>
       </c>
       <c r="N476" t="n">
-        <v>8332.7796042216</v>
+        <v>8332.7795967742</v>
       </c>
       <c r="O476" t="n">
-        <v>16665.5592084432</v>
+        <v>16665.5591935484</v>
       </c>
       <c r="P476" t="n">
         <v>14900</v>
@@ -21442,10 +21442,10 @@
         <v>16</v>
       </c>
       <c r="N479" t="n">
-        <v>1561.0066122098</v>
+        <v>1561.0072654155</v>
       </c>
       <c r="O479" t="n">
-        <v>24976.1057953568</v>
+        <v>24976.116246648</v>
       </c>
       <c r="P479" t="n">
         <v>2900</v>
@@ -21575,10 +21575,10 @@
         <v>30</v>
       </c>
       <c r="N482" t="n">
-        <v>26854</v>
+        <v>27080.935211268</v>
       </c>
       <c r="O482" t="n">
-        <v>805620</v>
+        <v>812428.0563380399</v>
       </c>
       <c r="P482" t="n">
         <v>43900</v>
@@ -21744,10 +21744,10 @@
         <v>15</v>
       </c>
       <c r="N486" t="n">
-        <v>2568.8354081633</v>
+        <v>2568.8353767123</v>
       </c>
       <c r="O486" t="n">
-        <v>38532.5311224495</v>
+        <v>38532.5306506845</v>
       </c>
       <c r="P486" t="n">
         <v>4500</v>
@@ -23245,10 +23245,10 @@
         <v>16</v>
       </c>
       <c r="N520" t="n">
-        <v>7700</v>
+        <v>7738.024691358</v>
       </c>
       <c r="O520" t="n">
-        <v>123200</v>
+        <v>123808.395061728</v>
       </c>
       <c r="P520" t="n">
         <v>13900</v>
@@ -24758,10 +24758,10 @@
         <v>152</v>
       </c>
       <c r="N553" t="n">
-        <v>1778.4728840436</v>
+        <v>1778.4728878597</v>
       </c>
       <c r="O553" t="n">
-        <v>270327.8783746272</v>
+        <v>270327.8789546744</v>
       </c>
       <c r="P553" t="n">
         <v>4900</v>
@@ -24942,10 +24942,10 @@
         <v>5</v>
       </c>
       <c r="N557" t="n">
-        <v>16058</v>
+        <v>16177.301634473</v>
       </c>
       <c r="O557" t="n">
-        <v>80290</v>
+        <v>80886.50817236501</v>
       </c>
       <c r="P557" t="n">
         <v>25900</v>
@@ -25678,10 +25678,10 @@
         <v>7</v>
       </c>
       <c r="N573" t="n">
-        <v>3259.2102666667</v>
+        <v>3259.2102702703</v>
       </c>
       <c r="O573" t="n">
-        <v>22814.4718666669</v>
+        <v>22814.4718918921</v>
       </c>
       <c r="P573" t="n">
         <v>5300</v>
@@ -26511,22 +26511,22 @@
         <v>0</v>
       </c>
       <c r="L591" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M591" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N591" t="n">
         <v>24847</v>
       </c>
       <c r="O591" t="n">
-        <v>124235</v>
+        <v>0</v>
       </c>
       <c r="P591" t="n">
         <v>39900</v>
       </c>
       <c r="Q591" t="n">
-        <v>199500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="592">
@@ -27021,10 +27021,10 @@
         <v>72</v>
       </c>
       <c r="N602" t="n">
-        <v>2252.3008997955</v>
+        <v>2252.3011740042</v>
       </c>
       <c r="O602" t="n">
-        <v>162165.664785276</v>
+        <v>162165.6845283024</v>
       </c>
       <c r="P602" t="n">
         <v>3900</v>
@@ -27490,10 +27490,10 @@
         <v>4</v>
       </c>
       <c r="N612" t="n">
-        <v>3519</v>
+        <v>4129.9375</v>
       </c>
       <c r="O612" t="n">
-        <v>14076</v>
+        <v>16519.75</v>
       </c>
       <c r="P612" t="n">
         <v>5900</v>
@@ -27668,22 +27668,22 @@
         <v>0</v>
       </c>
       <c r="L616" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M616" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="N616" t="n">
         <v>4544</v>
       </c>
       <c r="O616" t="n">
-        <v>468032</v>
+        <v>454400</v>
       </c>
       <c r="P616" t="n">
         <v>7900</v>
       </c>
       <c r="Q616" t="n">
-        <v>813700</v>
+        <v>790000</v>
       </c>
     </row>
     <row r="617">
@@ -27904,10 +27904,10 @@
         <v>47</v>
       </c>
       <c r="N621" t="n">
-        <v>4907.8227973568</v>
+        <v>4907.8228159645</v>
       </c>
       <c r="O621" t="n">
-        <v>230667.6714757696</v>
+        <v>230667.6723503315</v>
       </c>
       <c r="P621" t="n">
         <v>8200</v>
@@ -28220,22 +28220,22 @@
         <v>0</v>
       </c>
       <c r="L628" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M628" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N628" t="n">
         <v>33000</v>
       </c>
       <c r="O628" t="n">
-        <v>429000</v>
+        <v>330000</v>
       </c>
       <c r="P628" t="n">
         <v>52900</v>
       </c>
       <c r="Q628" t="n">
-        <v>687700</v>
+        <v>529000</v>
       </c>
     </row>
     <row r="629">
@@ -29100,10 +29100,10 @@
         <v>26</v>
       </c>
       <c r="N647" t="n">
-        <v>13565</v>
+        <v>13585.998452012</v>
       </c>
       <c r="O647" t="n">
-        <v>352690</v>
+        <v>353235.959752312</v>
       </c>
       <c r="P647" t="n">
         <v>22500</v>
@@ -29284,10 +29284,10 @@
         <v>1</v>
       </c>
       <c r="N651" t="n">
-        <v>23439</v>
+        <v>24040</v>
       </c>
       <c r="O651" t="n">
-        <v>23439</v>
+        <v>24040</v>
       </c>
       <c r="P651" t="n">
         <v>37900</v>
@@ -29330,10 +29330,10 @@
         <v>1</v>
       </c>
       <c r="N652" t="n">
-        <v>19008</v>
+        <v>19059.165545087</v>
       </c>
       <c r="O652" t="n">
-        <v>19008</v>
+        <v>19059.165545087</v>
       </c>
       <c r="P652" t="n">
         <v>30900</v>
@@ -29422,10 +29422,10 @@
         <v>17</v>
       </c>
       <c r="N654" t="n">
-        <v>17992</v>
+        <v>18038.854166667</v>
       </c>
       <c r="O654" t="n">
-        <v>305864</v>
+        <v>306660.520833339</v>
       </c>
       <c r="P654" t="n">
         <v>28900</v>
@@ -29560,10 +29560,10 @@
         <v>30</v>
       </c>
       <c r="N657" t="n">
-        <v>17075.989515789</v>
+        <v>17112.014810127</v>
       </c>
       <c r="O657" t="n">
-        <v>512279.68547367</v>
+        <v>513360.44430381</v>
       </c>
       <c r="P657" t="n">
         <v>27500</v>
@@ -30611,10 +30611,10 @@
         <v>6</v>
       </c>
       <c r="N680" t="n">
-        <v>12489</v>
+        <v>12769.651685393</v>
       </c>
       <c r="O680" t="n">
-        <v>74934</v>
+        <v>76617.910112358</v>
       </c>
       <c r="P680" t="n">
         <v>20900</v>
@@ -31304,10 +31304,10 @@
         <v>28</v>
       </c>
       <c r="N695" t="n">
-        <v>3306.5942675159</v>
+        <v>3306.5942583732</v>
       </c>
       <c r="O695" t="n">
-        <v>92584.6394904452</v>
+        <v>92584.6392344496</v>
       </c>
       <c r="P695" t="n">
         <v>4900</v>
@@ -31442,10 +31442,10 @@
         <v>185</v>
       </c>
       <c r="N698" t="n">
-        <v>2056.0812616427</v>
+        <v>2056.081010453</v>
       </c>
       <c r="O698" t="n">
-        <v>380375.0334038995</v>
+        <v>380374.986933805</v>
       </c>
       <c r="P698" t="n">
         <v>2900</v>
@@ -31534,10 +31534,10 @@
         <v>50</v>
       </c>
       <c r="N700" t="n">
-        <v>1655.9287880016</v>
+        <v>1655.9287789047</v>
       </c>
       <c r="O700" t="n">
-        <v>82796.43940007999</v>
+        <v>82796.438945235</v>
       </c>
       <c r="P700" t="n">
         <v>2500</v>
@@ -31813,10 +31813,10 @@
         <v>1</v>
       </c>
       <c r="N706" t="n">
-        <v>1592.2874455446</v>
+        <v>1592.2885084034</v>
       </c>
       <c r="O706" t="n">
-        <v>1592.2874455446</v>
+        <v>1592.2885084034</v>
       </c>
       <c r="P706" t="n">
         <v>2500</v>
@@ -32174,10 +32174,10 @@
         <v>3</v>
       </c>
       <c r="N714" t="n">
-        <v>2556.7485294118</v>
+        <v>2556.7486567164</v>
       </c>
       <c r="O714" t="n">
-        <v>7670.245588235401</v>
+        <v>7670.245970149201</v>
       </c>
       <c r="P714" t="n">
         <v>3900</v>
@@ -32264,10 +32264,10 @@
         <v>108</v>
       </c>
       <c r="N716" t="n">
-        <v>692.15251958462</v>
+        <v>692.1525362185999</v>
       </c>
       <c r="O716" t="n">
-        <v>74752.47211513895</v>
+        <v>74752.47391160879</v>
       </c>
       <c r="P716" t="n">
         <v>1200</v>
@@ -34896,10 +34896,10 @@
         <v>30</v>
       </c>
       <c r="N772" t="n">
-        <v>1690.8700095969</v>
+        <v>1690.8700097561</v>
       </c>
       <c r="O772" t="n">
-        <v>50726.100287907</v>
+        <v>50726.100292683</v>
       </c>
       <c r="P772" t="n">
         <v>3000</v>
@@ -36252,10 +36252,10 @@
         <v>154</v>
       </c>
       <c r="N801" t="n">
-        <v>517.29656001551</v>
+        <v>517.29673853391</v>
       </c>
       <c r="O801" t="n">
-        <v>79663.67024238853</v>
+        <v>79663.69773422214</v>
       </c>
       <c r="P801" t="n">
         <v>900</v>
@@ -36626,10 +36626,10 @@
         <v>1</v>
       </c>
       <c r="N809" t="n">
-        <v>3259.1346835443</v>
+        <v>3259.1347844828</v>
       </c>
       <c r="O809" t="n">
-        <v>3259.1346835443</v>
+        <v>3259.1347844828</v>
       </c>
       <c r="P809" t="n">
         <v>3600</v>
@@ -36857,10 +36857,10 @@
         <v>53</v>
       </c>
       <c r="N814" t="n">
-        <v>3110.8352523988</v>
+        <v>3110.8351781971</v>
       </c>
       <c r="O814" t="n">
-        <v>164874.2683771364</v>
+        <v>164874.2644444463</v>
       </c>
       <c r="P814" t="n">
         <v>4500</v>
@@ -37088,10 +37088,10 @@
         <v>288</v>
       </c>
       <c r="N819" t="n">
-        <v>703.79459507493</v>
+        <v>703.79459259958</v>
       </c>
       <c r="O819" t="n">
-        <v>202692.8433815798</v>
+        <v>202692.842668679</v>
       </c>
       <c r="P819" t="n">
         <v>900</v>
@@ -37739,10 +37739,10 @@
         <v>4</v>
       </c>
       <c r="N833" t="n">
-        <v>2501.384</v>
+        <v>2501.3837931034</v>
       </c>
       <c r="O833" t="n">
-        <v>10005.536</v>
+        <v>10005.5351724136</v>
       </c>
       <c r="P833" t="n">
         <v>4100</v>
@@ -40068,10 +40068,10 @@
         <v>5</v>
       </c>
       <c r="N882" t="n">
-        <v>2832.195862069</v>
+        <v>2986.6792727273</v>
       </c>
       <c r="O882" t="n">
-        <v>14160.979310345</v>
+        <v>14933.3963636365</v>
       </c>
       <c r="P882" t="n">
         <v>12900</v>
@@ -41073,10 +41073,10 @@
         <v>4</v>
       </c>
       <c r="N903" t="n">
-        <v>13164.13</v>
+        <v>15985.015</v>
       </c>
       <c r="O903" t="n">
-        <v>52656.52</v>
+        <v>63940.06</v>
       </c>
       <c r="P903" t="n">
         <v>39900</v>
@@ -41214,22 +41214,22 @@
         <v>0</v>
       </c>
       <c r="L906" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M906" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="N906" t="n">
-        <v>12448.354</v>
+        <v>12448.355263158</v>
       </c>
       <c r="O906" t="n">
-        <v>211622.018</v>
+        <v>136931.907894738</v>
       </c>
       <c r="P906" t="n">
         <v>22900</v>
       </c>
       <c r="Q906" t="n">
-        <v>389300</v>
+        <v>251900</v>
       </c>
     </row>
     <row r="907">
@@ -41903,10 +41903,10 @@
         <v>1</v>
       </c>
       <c r="N920" t="n">
-        <v>2992.5766666667</v>
+        <v>4208.3109375</v>
       </c>
       <c r="O920" t="n">
-        <v>2992.5766666667</v>
+        <v>4208.3109375</v>
       </c>
       <c r="P920" t="n">
         <v>6000</v>
@@ -42436,22 +42436,22 @@
         <v>0</v>
       </c>
       <c r="L931" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M931" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N931" t="n">
         <v>11229.38</v>
       </c>
       <c r="O931" t="n">
-        <v>134752.56</v>
+        <v>101064.42</v>
       </c>
       <c r="P931" t="n">
         <v>23900</v>
       </c>
       <c r="Q931" t="n">
-        <v>286800</v>
+        <v>215100</v>
       </c>
     </row>
     <row r="932">
@@ -42823,10 +42823,10 @@
         <v>5</v>
       </c>
       <c r="N939" t="n">
-        <v>3067.0906293706</v>
+        <v>3099.6039575972</v>
       </c>
       <c r="O939" t="n">
-        <v>15335.453146853</v>
+        <v>15498.019787986</v>
       </c>
       <c r="P939" t="n">
         <v>7200</v>
@@ -43983,10 +43983,10 @@
         <v>3</v>
       </c>
       <c r="N963" t="n">
-        <v>10737.5255</v>
+        <v>10737.525384615</v>
       </c>
       <c r="O963" t="n">
-        <v>32212.5765</v>
+        <v>32212.576153845</v>
       </c>
       <c r="P963" t="n">
         <v>18900</v>
@@ -44277,10 +44277,10 @@
         <v>18</v>
       </c>
       <c r="N969" t="n">
-        <v>15347.45</v>
+        <v>15516.103296703</v>
       </c>
       <c r="O969" t="n">
-        <v>276254.1</v>
+        <v>279289.859340654</v>
       </c>
       <c r="P969" t="n">
         <v>23900</v>
@@ -44752,10 +44752,10 @@
         <v>11</v>
       </c>
       <c r="N979" t="n">
-        <v>5216.9</v>
+        <v>5254.1635714286</v>
       </c>
       <c r="O979" t="n">
-        <v>57385.89999999999</v>
+        <v>57795.7992857146</v>
       </c>
       <c r="P979" t="n">
         <v>20500</v>
@@ -47135,10 +47135,10 @@
         <v>73</v>
       </c>
       <c r="N1028" t="n">
-        <v>430.60997520149</v>
+        <v>430.6099751861</v>
       </c>
       <c r="O1028" t="n">
-        <v>31434.52818970877</v>
+        <v>31434.5281885853</v>
       </c>
       <c r="P1028" t="n">
         <v>2200</v>
@@ -48231,10 +48231,10 @@
         <v>14</v>
       </c>
       <c r="N1052" t="n">
-        <v>22951.704647137</v>
+        <v>22951.704432133</v>
       </c>
       <c r="O1052" t="n">
-        <v>321323.865059918</v>
+        <v>321323.862049862</v>
       </c>
       <c r="P1052" t="n">
         <v>37900</v>
@@ -54675,10 +54675,10 @@
         <v>116</v>
       </c>
       <c r="N1192" t="n">
-        <v>9240</v>
+        <v>9401.162790697699</v>
       </c>
       <c r="O1192" t="n">
-        <v>1071840</v>
+        <v>1090534.883720933</v>
       </c>
       <c r="P1192" t="n">
         <v>11500</v>
@@ -61789,10 +61789,10 @@
         <v>3</v>
       </c>
       <c r="N1345" t="n">
-        <v>2539.5719057816</v>
+        <v>2539.5719098712</v>
       </c>
       <c r="O1345" t="n">
-        <v>7618.715717344799</v>
+        <v>7618.715729613601</v>
       </c>
       <c r="P1345" t="n">
         <v>2900</v>
@@ -61881,10 +61881,10 @@
         <v>14</v>
       </c>
       <c r="N1347" t="n">
-        <v>4171.6683018868</v>
+        <v>4171.6682869693</v>
       </c>
       <c r="O1347" t="n">
-        <v>58403.3562264152</v>
+        <v>58403.35601757021</v>
       </c>
       <c r="P1347" t="n">
         <v>5000</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -771,10 +771,10 @@
         <v>14</v>
       </c>
       <c r="N9" t="n">
-        <v>27109.756097561</v>
+        <v>27000</v>
       </c>
       <c r="O9" t="n">
-        <v>379536.585365854</v>
+        <v>378000</v>
       </c>
       <c r="P9" t="n">
         <v>20000</v>
@@ -856,10 +856,10 @@
         <v>307</v>
       </c>
       <c r="N11" t="n">
-        <v>1811.3112820513</v>
+        <v>1811.3108641975</v>
       </c>
       <c r="O11" t="n">
-        <v>556072.563589749</v>
+        <v>556072.4353086324</v>
       </c>
       <c r="P11" t="n">
         <v>2600</v>
@@ -11327,10 +11327,10 @@
         <v>4</v>
       </c>
       <c r="N252" t="n">
-        <v>2582.25476203</v>
+        <v>2586.3633253779</v>
       </c>
       <c r="O252" t="n">
-        <v>10329.01904812</v>
+        <v>10345.4533015116</v>
       </c>
       <c r="P252" t="n">
         <v>4500</v>
@@ -11975,10 +11975,10 @@
         <v>43</v>
       </c>
       <c r="N266" t="n">
-        <v>3230.0657009346</v>
+        <v>3230.0656603774</v>
       </c>
       <c r="O266" t="n">
-        <v>138892.8251401878</v>
+        <v>138892.8233962282</v>
       </c>
       <c r="P266" t="n">
         <v>6200</v>
@@ -14462,10 +14462,10 @@
         <v>67</v>
       </c>
       <c r="N321" t="n">
-        <v>3472.2763744227</v>
+        <v>3472.276379862</v>
       </c>
       <c r="O321" t="n">
-        <v>232642.5170863209</v>
+        <v>232642.517450754</v>
       </c>
       <c r="P321" t="n">
         <v>5900</v>
@@ -16718,10 +16718,10 @@
         <v>3</v>
       </c>
       <c r="N371" t="n">
-        <v>1467.2914141414</v>
+        <v>1467.3004273504</v>
       </c>
       <c r="O371" t="n">
-        <v>4401.8742424242</v>
+        <v>4401.9012820512</v>
       </c>
       <c r="P371" t="n">
         <v>2500</v>
@@ -16764,10 +16764,10 @@
         <v>29</v>
       </c>
       <c r="N372" t="n">
-        <v>1690.5719339623</v>
+        <v>1690.5726046512</v>
       </c>
       <c r="O372" t="n">
-        <v>49026.5860849067</v>
+        <v>49026.6055348848</v>
       </c>
       <c r="P372" t="n">
         <v>2900</v>
@@ -16810,10 +16810,10 @@
         <v>12</v>
       </c>
       <c r="N373" t="n">
-        <v>1550.1950026961</v>
+        <v>1550.1949625568</v>
       </c>
       <c r="O373" t="n">
-        <v>18602.3400323532</v>
+        <v>18602.3395506816</v>
       </c>
       <c r="P373" t="n">
         <v>2500</v>
@@ -16902,10 +16902,10 @@
         <v>1</v>
       </c>
       <c r="N375" t="n">
-        <v>2403.522961183</v>
+        <v>2403.5229357459</v>
       </c>
       <c r="O375" t="n">
-        <v>2403.522961183</v>
+        <v>2403.5229357459</v>
       </c>
       <c r="P375" t="n">
         <v>3500</v>
@@ -19414,10 +19414,10 @@
         <v>83</v>
       </c>
       <c r="N432" t="n">
-        <v>2029.8742541123</v>
+        <v>2029.8742613636</v>
       </c>
       <c r="O432" t="n">
-        <v>168479.5630913209</v>
+        <v>168479.5636931788</v>
       </c>
       <c r="P432" t="n">
         <v>3600</v>
@@ -19957,10 +19957,10 @@
         <v>7</v>
       </c>
       <c r="N445" t="n">
-        <v>30745.062773723</v>
+        <v>30611</v>
       </c>
       <c r="O445" t="n">
-        <v>215215.439416061</v>
+        <v>214277</v>
       </c>
       <c r="P445" t="n">
         <v>38900</v>
@@ -20090,10 +20090,10 @@
         <v>43</v>
       </c>
       <c r="N448" t="n">
-        <v>6207.9882003658</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O448" t="n">
-        <v>266943.4926157294</v>
+        <v>266943.4926592583</v>
       </c>
       <c r="P448" t="n">
         <v>9900</v>
@@ -20572,10 +20572,10 @@
         <v>22</v>
       </c>
       <c r="N459" t="n">
-        <v>4814.2633472037</v>
+        <v>4814.2633516301</v>
       </c>
       <c r="O459" t="n">
-        <v>105913.7936384814</v>
+        <v>105913.7937358622</v>
       </c>
       <c r="P459" t="n">
         <v>9900</v>
@@ -21176,10 +21176,10 @@
         <v>11</v>
       </c>
       <c r="N473" t="n">
-        <v>27123.764610526</v>
+        <v>27123.764587738</v>
       </c>
       <c r="O473" t="n">
-        <v>298361.410715786</v>
+        <v>298361.410465118</v>
       </c>
       <c r="P473" t="n">
         <v>44500</v>
@@ -21575,10 +21575,10 @@
         <v>30</v>
       </c>
       <c r="N482" t="n">
-        <v>27080.935211268</v>
+        <v>26854</v>
       </c>
       <c r="O482" t="n">
-        <v>812428.0563380399</v>
+        <v>805620</v>
       </c>
       <c r="P482" t="n">
         <v>43900</v>
@@ -24256,10 +24256,10 @@
         <v>29</v>
       </c>
       <c r="N542" t="n">
-        <v>9188.98</v>
+        <v>9456.2957818182</v>
       </c>
       <c r="O542" t="n">
-        <v>266480.42</v>
+        <v>274232.5776727278</v>
       </c>
       <c r="P542" t="n">
         <v>12900</v>
@@ -28180,10 +28180,10 @@
         <v>10</v>
       </c>
       <c r="N627" t="n">
-        <v>33000</v>
+        <v>35444.444444444</v>
       </c>
       <c r="O627" t="n">
-        <v>330000</v>
+        <v>354444.44444444</v>
       </c>
       <c r="P627" t="n">
         <v>52900</v>
@@ -29054,10 +29054,10 @@
         <v>26</v>
       </c>
       <c r="N646" t="n">
-        <v>13585.998452012</v>
+        <v>13565</v>
       </c>
       <c r="O646" t="n">
-        <v>353235.959752312</v>
+        <v>352690</v>
       </c>
       <c r="P646" t="n">
         <v>22500</v>
@@ -29284,10 +29284,10 @@
         <v>1</v>
       </c>
       <c r="N651" t="n">
-        <v>19059.165545087</v>
+        <v>19008</v>
       </c>
       <c r="O651" t="n">
-        <v>19059.165545087</v>
+        <v>19008</v>
       </c>
       <c r="P651" t="n">
         <v>30900</v>
@@ -29376,10 +29376,10 @@
         <v>17</v>
       </c>
       <c r="N653" t="n">
-        <v>18038.854166667</v>
+        <v>17992</v>
       </c>
       <c r="O653" t="n">
-        <v>306660.520833339</v>
+        <v>305864</v>
       </c>
       <c r="P653" t="n">
         <v>28900</v>
@@ -29514,10 +29514,10 @@
         <v>30</v>
       </c>
       <c r="N656" t="n">
-        <v>17112.014810127</v>
+        <v>17075.989514768</v>
       </c>
       <c r="O656" t="n">
-        <v>513360.44430381</v>
+        <v>512279.68544304</v>
       </c>
       <c r="P656" t="n">
         <v>27500</v>
@@ -30565,10 +30565,10 @@
         <v>6</v>
       </c>
       <c r="N679" t="n">
-        <v>12769.651685393</v>
+        <v>12489</v>
       </c>
       <c r="O679" t="n">
-        <v>76617.910112358</v>
+        <v>74934</v>
       </c>
       <c r="P679" t="n">
         <v>20900</v>
@@ -30936,10 +30936,10 @@
         <v>8</v>
       </c>
       <c r="N687" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386990066</v>
       </c>
       <c r="O687" t="n">
-        <v>12128.309578836</v>
+        <v>12128.3095920528</v>
       </c>
       <c r="P687" t="n">
         <v>2300</v>
@@ -31074,10 +31074,10 @@
         <v>156</v>
       </c>
       <c r="N690" t="n">
-        <v>1907.3924305556</v>
+        <v>1907.3922142857</v>
       </c>
       <c r="O690" t="n">
-        <v>297553.2191666736</v>
+        <v>297553.1854285692</v>
       </c>
       <c r="P690" t="n">
         <v>2500</v>
@@ -31212,10 +31212,10 @@
         <v>272</v>
       </c>
       <c r="N693" t="n">
-        <v>1803.0176111361</v>
+        <v>1803.0176523702</v>
       </c>
       <c r="O693" t="n">
-        <v>490420.7902290192</v>
+        <v>490420.8014446944</v>
       </c>
       <c r="P693" t="n">
         <v>2500</v>
@@ -31304,10 +31304,10 @@
         <v>207</v>
       </c>
       <c r="N695" t="n">
-        <v>2122.1634163581</v>
+        <v>2122.1634141414</v>
       </c>
       <c r="O695" t="n">
-        <v>439287.8271861267</v>
+        <v>439287.8267272699</v>
       </c>
       <c r="P695" t="n">
         <v>2900</v>
@@ -31442,10 +31442,10 @@
         <v>66</v>
       </c>
       <c r="N698" t="n">
-        <v>3224.5700336323</v>
+        <v>3224.5700392597</v>
       </c>
       <c r="O698" t="n">
-        <v>212821.6222197318</v>
+        <v>212821.6225911402</v>
       </c>
       <c r="P698" t="n">
         <v>4500</v>
@@ -31488,10 +31488,10 @@
         <v>50</v>
       </c>
       <c r="N699" t="n">
-        <v>1655.9287789047</v>
+        <v>1655.9286125978</v>
       </c>
       <c r="O699" t="n">
-        <v>82796.438945235</v>
+        <v>82796.43062989</v>
       </c>
       <c r="P699" t="n">
         <v>2500</v>
@@ -31767,10 +31767,10 @@
         <v>1</v>
       </c>
       <c r="N705" t="n">
-        <v>1592.2886257928</v>
+        <v>1592.2887446809</v>
       </c>
       <c r="O705" t="n">
-        <v>1592.2886257928</v>
+        <v>1592.2887446809</v>
       </c>
       <c r="P705" t="n">
         <v>2500</v>
@@ -31949,10 +31949,10 @@
         <v>471</v>
       </c>
       <c r="N709" t="n">
-        <v>1259.2752009274</v>
+        <v>1259.2751769231</v>
       </c>
       <c r="O709" t="n">
-        <v>593118.6196368054</v>
+        <v>593118.6083307801</v>
       </c>
       <c r="P709" t="n">
         <v>1900</v>
@@ -32218,10 +32218,10 @@
         <v>108</v>
       </c>
       <c r="N715" t="n">
-        <v>692.1525418121701</v>
+        <v>692.15254743047</v>
       </c>
       <c r="O715" t="n">
-        <v>74752.47451571436</v>
+        <v>74752.47512249077</v>
       </c>
       <c r="P715" t="n">
         <v>1200</v>
@@ -33135,10 +33135,10 @@
         <v>49</v>
       </c>
       <c r="N734" t="n">
-        <v>8945.379999999999</v>
+        <v>8949.4124778362</v>
       </c>
       <c r="O734" t="n">
-        <v>438323.6199999999</v>
+        <v>438521.2114139738</v>
       </c>
       <c r="P734" t="n">
         <v>14900</v>
@@ -36206,10 +36206,10 @@
         <v>154</v>
       </c>
       <c r="N800" t="n">
-        <v>517.29691759113</v>
+        <v>517.29686746988</v>
       </c>
       <c r="O800" t="n">
-        <v>79663.72530903401</v>
+        <v>79663.71759036151</v>
       </c>
       <c r="P800" t="n">
         <v>900</v>
@@ -37042,10 +37042,10 @@
         <v>288</v>
       </c>
       <c r="N818" t="n">
-        <v>703.79458866348</v>
+        <v>703.7945904135599</v>
       </c>
       <c r="O818" t="n">
-        <v>202692.8415350822</v>
+        <v>202692.8420391052</v>
       </c>
       <c r="P818" t="n">
         <v>900</v>
@@ -40022,10 +40022,10 @@
         <v>5</v>
       </c>
       <c r="N881" t="n">
-        <v>2986.6792727273</v>
+        <v>2832.1961818182</v>
       </c>
       <c r="O881" t="n">
-        <v>14933.3963636365</v>
+        <v>14160.980909091</v>
       </c>
       <c r="P881" t="n">
         <v>12900</v>
@@ -41027,10 +41027,10 @@
         <v>4</v>
       </c>
       <c r="N902" t="n">
-        <v>15985.015</v>
+        <v>13164.13</v>
       </c>
       <c r="O902" t="n">
-        <v>63940.06</v>
+        <v>52656.52</v>
       </c>
       <c r="P902" t="n">
         <v>39900</v>
@@ -41370,10 +41370,10 @@
         <v>7</v>
       </c>
       <c r="N909" t="n">
-        <v>9746.8802061856</v>
+        <v>9746.8802105263</v>
       </c>
       <c r="O909" t="n">
-        <v>68228.16144329921</v>
+        <v>68228.1614736841</v>
       </c>
       <c r="P909" t="n">
         <v>18500</v>
@@ -43937,10 +43937,10 @@
         <v>3</v>
       </c>
       <c r="N962" t="n">
-        <v>10737.525384615</v>
+        <v>19429.807619048</v>
       </c>
       <c r="O962" t="n">
-        <v>32212.576153845</v>
+        <v>58289.422857144</v>
       </c>
       <c r="P962" t="n">
         <v>18900</v>
@@ -44706,10 +44706,10 @@
         <v>11</v>
       </c>
       <c r="N978" t="n">
-        <v>5254.1635714286</v>
+        <v>5216.9</v>
       </c>
       <c r="O978" t="n">
-        <v>57795.7992857146</v>
+        <v>57385.89999999999</v>
       </c>
       <c r="P978" t="n">
         <v>20500</v>
@@ -47138,10 +47138,10 @@
         <v>37</v>
       </c>
       <c r="N1028" t="n">
-        <v>465.87103377687</v>
+        <v>465.87103696099</v>
       </c>
       <c r="O1028" t="n">
-        <v>17237.22824974419</v>
+        <v>17237.22836755663</v>
       </c>
       <c r="P1028" t="n">
         <v>2500</v>
@@ -48185,10 +48185,10 @@
         <v>14</v>
       </c>
       <c r="N1051" t="n">
-        <v>22951.704393305</v>
+        <v>22951.704377622</v>
       </c>
       <c r="O1051" t="n">
-        <v>321323.86150627</v>
+        <v>321323.861286708</v>
       </c>
       <c r="P1051" t="n">
         <v>37900</v>
@@ -58320,10 +58320,10 @@
         <v>16</v>
       </c>
       <c r="N1270" t="n">
-        <v>2432.1360526316</v>
+        <v>2432.1363013699</v>
       </c>
       <c r="O1270" t="n">
-        <v>38914.1768421056</v>
+        <v>38914.1808219184</v>
       </c>
       <c r="P1270" t="n">
         <v>4500</v>
@@ -61789,10 +61789,10 @@
         <v>17</v>
       </c>
       <c r="N1345" t="n">
-        <v>4687.9754746137</v>
+        <v>4719.2286444444</v>
       </c>
       <c r="O1345" t="n">
-        <v>79695.5830684329</v>
+        <v>80226.8869555548</v>
       </c>
       <c r="P1345" t="n">
         <v>5500</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-29</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1051,10 +1051,10 @@
         <v>9</v>
       </c>
       <c r="N16" t="n">
-        <v>5758.9597772829</v>
+        <v>5758.9597767857</v>
       </c>
       <c r="O16" t="n">
-        <v>51830.6379955461</v>
+        <v>51830.6379910713</v>
       </c>
       <c r="P16" t="n">
         <v>16900</v>
@@ -1740,10 +1740,10 @@
         <v>8</v>
       </c>
       <c r="N33" t="n">
-        <v>22510.483207547</v>
+        <v>22510.483076923</v>
       </c>
       <c r="O33" t="n">
-        <v>180083.865660376</v>
+        <v>180083.864615384</v>
       </c>
       <c r="P33" t="n">
         <v>44900</v>
@@ -1974,10 +1974,10 @@
         <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>3716.3301973684</v>
+        <v>3716.3301980198</v>
       </c>
       <c r="O39" t="n">
-        <v>7432.6603947368</v>
+        <v>7432.6603960396</v>
       </c>
       <c r="P39" t="n">
         <v>9500</v>
@@ -2805,10 +2805,10 @@
         <v>17</v>
       </c>
       <c r="N59" t="n">
-        <v>3910.6279262673</v>
+        <v>3910.6278971963</v>
       </c>
       <c r="O59" t="n">
-        <v>66480.6747465441</v>
+        <v>66480.67425233711</v>
       </c>
       <c r="P59" t="n">
         <v>9100</v>
@@ -11327,10 +11327,10 @@
         <v>4</v>
       </c>
       <c r="N252" t="n">
-        <v>2586.3633253779</v>
+        <v>2582.2547091633</v>
       </c>
       <c r="O252" t="n">
-        <v>10345.4533015116</v>
+        <v>10329.0188366532</v>
       </c>
       <c r="P252" t="n">
         <v>4500</v>
@@ -11419,10 +11419,10 @@
         <v>29</v>
       </c>
       <c r="N254" t="n">
-        <v>5216.8958101422</v>
+        <v>5216.8958023544</v>
       </c>
       <c r="O254" t="n">
-        <v>151289.9784941238</v>
+        <v>151289.9782682776</v>
       </c>
       <c r="P254" t="n">
         <v>8500</v>
@@ -11747,10 +11747,10 @@
         <v>279</v>
       </c>
       <c r="N261" t="n">
-        <v>3158.8608436687</v>
+        <v>3158.8608437109</v>
       </c>
       <c r="O261" t="n">
-        <v>881322.1753835673</v>
+        <v>881322.1753953411</v>
       </c>
       <c r="P261" t="n">
         <v>5600</v>
@@ -12656,10 +12656,10 @@
         <v>23</v>
       </c>
       <c r="N281" t="n">
-        <v>3795.7100076453</v>
+        <v>3795.7100076628</v>
       </c>
       <c r="O281" t="n">
-        <v>87301.3301758419</v>
+        <v>87301.3301762444</v>
       </c>
       <c r="P281" t="n">
         <v>6200</v>
@@ -12882,10 +12882,10 @@
         <v>210309.9924310953</v>
       </c>
       <c r="P286" t="n">
-        <v>8200</v>
+        <v>8900</v>
       </c>
       <c r="Q286" t="n">
-        <v>352600</v>
+        <v>382700</v>
       </c>
     </row>
     <row r="287">
@@ -13775,10 +13775,10 @@
         <v>35</v>
       </c>
       <c r="N306" t="n">
-        <v>5191.4800286123</v>
+        <v>5191.4800286533</v>
       </c>
       <c r="O306" t="n">
-        <v>181701.8010014305</v>
+        <v>181701.8010028655</v>
       </c>
       <c r="P306" t="n">
         <v>9100</v>
@@ -14462,10 +14462,10 @@
         <v>67</v>
       </c>
       <c r="N321" t="n">
-        <v>3472.276379862</v>
+        <v>3472.276393501</v>
       </c>
       <c r="O321" t="n">
-        <v>232642.517450754</v>
+        <v>232642.518364567</v>
       </c>
       <c r="P321" t="n">
         <v>5900</v>
@@ -14642,10 +14642,10 @@
         <v>22</v>
       </c>
       <c r="N325" t="n">
-        <v>3041.6600151515</v>
+        <v>3041.660015186</v>
       </c>
       <c r="O325" t="n">
-        <v>66916.520333333</v>
+        <v>66916.520334092</v>
       </c>
       <c r="P325" t="n">
         <v>5500</v>
@@ -14778,10 +14778,10 @@
         <v>43</v>
       </c>
       <c r="N328" t="n">
-        <v>1592.5643478261</v>
+        <v>1592.564335512</v>
       </c>
       <c r="O328" t="n">
-        <v>68480.2669565223</v>
+        <v>68480.266427016</v>
       </c>
       <c r="P328" t="n">
         <v>3900</v>
@@ -16672,10 +16672,10 @@
         <v>172</v>
       </c>
       <c r="N370" t="n">
-        <v>1630.9251181364</v>
+        <v>1630.9251335113</v>
       </c>
       <c r="O370" t="n">
-        <v>280519.1203194608</v>
+        <v>280519.1229639436</v>
       </c>
       <c r="P370" t="n">
         <v>2500</v>
@@ -16902,10 +16902,10 @@
         <v>1</v>
       </c>
       <c r="N375" t="n">
-        <v>2403.5229357459</v>
+        <v>2403.523063498</v>
       </c>
       <c r="O375" t="n">
-        <v>2403.5229357459</v>
+        <v>2403.523063498</v>
       </c>
       <c r="P375" t="n">
         <v>3500</v>
@@ -19001,10 +19001,10 @@
         <v>6</v>
       </c>
       <c r="N422" t="n">
-        <v>4196.8725467746</v>
+        <v>4196.8725524769</v>
       </c>
       <c r="O422" t="n">
-        <v>25181.2352806476</v>
+        <v>25181.2353148614</v>
       </c>
       <c r="P422" t="n">
         <v>5900</v>
@@ -19455,10 +19455,10 @@
         <v>18</v>
       </c>
       <c r="N433" t="n">
-        <v>22485.695378691</v>
+        <v>22485.69534282</v>
       </c>
       <c r="O433" t="n">
-        <v>404742.5168164381</v>
+        <v>404742.51617076</v>
       </c>
       <c r="P433" t="n">
         <v>36500</v>
@@ -19660,10 +19660,10 @@
         <v>9</v>
       </c>
       <c r="N438" t="n">
-        <v>2680.7396929825</v>
+        <v>2680.7396925972</v>
       </c>
       <c r="O438" t="n">
-        <v>24126.6572368425</v>
+        <v>24126.6572333748</v>
       </c>
       <c r="P438" t="n">
         <v>4900</v>
@@ -19701,10 +19701,10 @@
         <v>17</v>
       </c>
       <c r="N439" t="n">
-        <v>880.32993798065</v>
+        <v>880.329947852</v>
       </c>
       <c r="O439" t="n">
-        <v>14965.60894567105</v>
+        <v>14965.609113484</v>
       </c>
       <c r="P439" t="n">
         <v>1200</v>
@@ -20090,10 +20090,10 @@
         <v>43</v>
       </c>
       <c r="N448" t="n">
-        <v>6207.9882013781</v>
+        <v>6207.9881978301</v>
       </c>
       <c r="O448" t="n">
-        <v>266943.4926592583</v>
+        <v>266943.4925066943</v>
       </c>
       <c r="P448" t="n">
         <v>9900</v>
@@ -20185,10 +20185,10 @@
         <v>1</v>
       </c>
       <c r="N450" t="n">
-        <v>4285.1966145833</v>
+        <v>4285.1966318538</v>
       </c>
       <c r="O450" t="n">
-        <v>4285.1966145833</v>
+        <v>4285.1966318538</v>
       </c>
       <c r="P450" t="n">
         <v>6900</v>
@@ -20572,16 +20572,16 @@
         <v>22</v>
       </c>
       <c r="N459" t="n">
-        <v>4814.2633516301</v>
+        <v>4814.2633494176</v>
       </c>
       <c r="O459" t="n">
-        <v>105913.7937358622</v>
+        <v>105913.7936871872</v>
       </c>
       <c r="P459" t="n">
-        <v>9900</v>
+        <v>7900</v>
       </c>
       <c r="Q459" t="n">
-        <v>217800</v>
+        <v>173800</v>
       </c>
     </row>
     <row r="460">
@@ -21309,10 +21309,10 @@
         <v>2</v>
       </c>
       <c r="N476" t="n">
-        <v>8332.7795967742</v>
+        <v>8332.7795945946</v>
       </c>
       <c r="O476" t="n">
-        <v>16665.5591935484</v>
+        <v>16665.5591891892</v>
       </c>
       <c r="P476" t="n">
         <v>14900</v>
@@ -21442,10 +21442,10 @@
         <v>16</v>
       </c>
       <c r="N479" t="n">
-        <v>1561.0074054054</v>
+        <v>1561.0125437573</v>
       </c>
       <c r="O479" t="n">
-        <v>24976.1184864864</v>
+        <v>24976.2007001168</v>
       </c>
       <c r="P479" t="n">
         <v>2900</v>
@@ -24256,10 +24256,10 @@
         <v>29</v>
       </c>
       <c r="N542" t="n">
-        <v>9456.2957818182</v>
+        <v>9188.98</v>
       </c>
       <c r="O542" t="n">
-        <v>274232.5776727278</v>
+        <v>266480.42</v>
       </c>
       <c r="P542" t="n">
         <v>12900</v>
@@ -27858,10 +27858,10 @@
         <v>47</v>
       </c>
       <c r="N620" t="n">
-        <v>4907.8228222222</v>
+        <v>4907.8228863636</v>
       </c>
       <c r="O620" t="n">
-        <v>230667.6726444434</v>
+        <v>230667.6756590892</v>
       </c>
       <c r="P620" t="n">
         <v>8200</v>
@@ -28134,10 +28134,10 @@
         <v>46</v>
       </c>
       <c r="N626" t="n">
-        <v>3903.7403351955</v>
+        <v>3903.7404686036</v>
       </c>
       <c r="O626" t="n">
-        <v>179572.055418993</v>
+        <v>179572.0615557656</v>
       </c>
       <c r="P626" t="n">
         <v>7500</v>
@@ -28180,10 +28180,10 @@
         <v>10</v>
       </c>
       <c r="N627" t="n">
-        <v>35444.444444444</v>
+        <v>33000</v>
       </c>
       <c r="O627" t="n">
-        <v>354444.44444444</v>
+        <v>330000</v>
       </c>
       <c r="P627" t="n">
         <v>52900</v>
@@ -28502,10 +28502,10 @@
         <v>16</v>
       </c>
       <c r="N634" t="n">
-        <v>5869.1723052295</v>
+        <v>5869.1722639485</v>
       </c>
       <c r="O634" t="n">
-        <v>93906.756883672</v>
+        <v>93906.75622317599</v>
       </c>
       <c r="P634" t="n">
         <v>9500</v>
@@ -30936,10 +30936,10 @@
         <v>8</v>
       </c>
       <c r="N687" t="n">
-        <v>1516.0386990066</v>
+        <v>1516.0386973545</v>
       </c>
       <c r="O687" t="n">
-        <v>12128.3095920528</v>
+        <v>12128.309578836</v>
       </c>
       <c r="P687" t="n">
         <v>2300</v>
@@ -31028,10 +31028,10 @@
         <v>144</v>
       </c>
       <c r="N689" t="n">
-        <v>2458.5122658275</v>
+        <v>2458.5122572276</v>
       </c>
       <c r="O689" t="n">
-        <v>354025.76627916</v>
+        <v>354025.7650407744</v>
       </c>
       <c r="P689" t="n">
         <v>3500</v>
@@ -31212,10 +31212,10 @@
         <v>272</v>
       </c>
       <c r="N693" t="n">
-        <v>1803.0176523702</v>
+        <v>1803.0176696833</v>
       </c>
       <c r="O693" t="n">
-        <v>490420.8014446944</v>
+        <v>490420.8061538576</v>
       </c>
       <c r="P693" t="n">
         <v>2500</v>
@@ -31350,10 +31350,10 @@
         <v>82</v>
       </c>
       <c r="N696" t="n">
-        <v>2108.8000229358</v>
+        <v>2108.8001384083</v>
       </c>
       <c r="O696" t="n">
-        <v>172921.6018807356</v>
+        <v>172921.6113494806</v>
       </c>
       <c r="P696" t="n">
         <v>2900</v>
@@ -31396,10 +31396,10 @@
         <v>185</v>
       </c>
       <c r="N697" t="n">
-        <v>2056.081010453</v>
+        <v>2056.0810065359</v>
       </c>
       <c r="O697" t="n">
-        <v>380374.986933805</v>
+        <v>380374.9862091415</v>
       </c>
       <c r="P697" t="n">
         <v>2900</v>
@@ -31767,10 +31767,10 @@
         <v>1</v>
       </c>
       <c r="N705" t="n">
-        <v>1592.2887446809</v>
+        <v>1592.2892358079</v>
       </c>
       <c r="O705" t="n">
-        <v>1592.2887446809</v>
+        <v>1592.2892358079</v>
       </c>
       <c r="P705" t="n">
         <v>2500</v>
@@ -31949,10 +31949,10 @@
         <v>471</v>
       </c>
       <c r="N709" t="n">
-        <v>1259.2751769231</v>
+        <v>1259.2751809084</v>
       </c>
       <c r="O709" t="n">
-        <v>593118.6083307801</v>
+        <v>593118.6102078564</v>
       </c>
       <c r="P709" t="n">
         <v>1900</v>
@@ -32218,10 +32218,10 @@
         <v>108</v>
       </c>
       <c r="N715" t="n">
-        <v>692.15254743047</v>
+        <v>692.15255307366</v>
       </c>
       <c r="O715" t="n">
-        <v>74752.47512249077</v>
+        <v>74752.47573195527</v>
       </c>
       <c r="P715" t="n">
         <v>1200</v>
@@ -33135,10 +33135,10 @@
         <v>49</v>
       </c>
       <c r="N734" t="n">
-        <v>8949.4124778362</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O734" t="n">
-        <v>438521.2114139738</v>
+        <v>438323.6199999999</v>
       </c>
       <c r="P734" t="n">
         <v>14900</v>
@@ -34850,10 +34850,10 @@
         <v>30</v>
       </c>
       <c r="N771" t="n">
-        <v>1690.8700097895</v>
+        <v>1690.8700098184</v>
       </c>
       <c r="O771" t="n">
-        <v>50726.100293685</v>
+        <v>50726.100294552</v>
       </c>
       <c r="P771" t="n">
         <v>3000</v>
@@ -37042,10 +37042,10 @@
         <v>288</v>
       </c>
       <c r="N818" t="n">
-        <v>703.7945904135599</v>
+        <v>703.79458486774</v>
       </c>
       <c r="O818" t="n">
-        <v>202692.8420391052</v>
+        <v>202692.8404419091</v>
       </c>
       <c r="P818" t="n">
         <v>900</v>
@@ -43937,10 +43937,10 @@
         <v>3</v>
       </c>
       <c r="N962" t="n">
-        <v>19429.807619048</v>
+        <v>10737.525135135</v>
       </c>
       <c r="O962" t="n">
-        <v>58289.422857144</v>
+        <v>32212.575405405</v>
       </c>
       <c r="P962" t="n">
         <v>18900</v>
@@ -49195,10 +49195,10 @@
         <v>99</v>
       </c>
       <c r="N1073" t="n">
-        <v>219.99758867125</v>
+        <v>219.9969793366</v>
       </c>
       <c r="O1073" t="n">
-        <v>21779.76127845375</v>
+        <v>21779.7009543234</v>
       </c>
       <c r="P1073" t="n">
         <v>260</v>
@@ -57891,10 +57891,10 @@
         <v>5</v>
       </c>
       <c r="N1261" t="n">
-        <v>1319.3610989011</v>
+        <v>1319.3611070111</v>
       </c>
       <c r="O1261" t="n">
-        <v>6596.805494505499</v>
+        <v>6596.805535055501</v>
       </c>
       <c r="P1261" t="n">
         <v>3500</v>
@@ -61789,10 +61789,10 @@
         <v>17</v>
       </c>
       <c r="N1345" t="n">
-        <v>4719.2286444444</v>
+        <v>4687.9755111111</v>
       </c>
       <c r="O1345" t="n">
-        <v>80226.8869555548</v>
+        <v>79695.5836888887</v>
       </c>
       <c r="P1345" t="n">
         <v>5500</v>
@@ -61835,10 +61835,10 @@
         <v>14</v>
       </c>
       <c r="N1346" t="n">
-        <v>4171.6682692308</v>
+        <v>4171.6682164634</v>
       </c>
       <c r="O1346" t="n">
-        <v>58403.3557692312</v>
+        <v>58403.3550304876</v>
       </c>
       <c r="P1346" t="n">
         <v>5000</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -2130,10 +2130,10 @@
         <v>18</v>
       </c>
       <c r="N43" t="n">
-        <v>21333.69</v>
+        <v>21425.250901288</v>
       </c>
       <c r="O43" t="n">
-        <v>384006.42</v>
+        <v>385654.516223184</v>
       </c>
       <c r="P43" t="n">
         <v>30000</v>
@@ -10681,10 +10681,10 @@
         <v>50</v>
       </c>
       <c r="N237" t="n">
-        <v>13593.35</v>
+        <v>13694.165945612</v>
       </c>
       <c r="O237" t="n">
-        <v>679667.5</v>
+        <v>684708.2972805999</v>
       </c>
       <c r="P237" t="n">
         <v>25500</v>
@@ -11327,10 +11327,10 @@
         <v>4</v>
       </c>
       <c r="N252" t="n">
-        <v>2582.2547091633</v>
+        <v>2582.2546851654</v>
       </c>
       <c r="O252" t="n">
-        <v>10329.0188366532</v>
+        <v>10329.0187406616</v>
       </c>
       <c r="P252" t="n">
         <v>4500</v>
@@ -12876,10 +12876,10 @@
         <v>43</v>
       </c>
       <c r="N286" t="n">
-        <v>4890.9300565371</v>
+        <v>4890.9300570207</v>
       </c>
       <c r="O286" t="n">
-        <v>210309.9924310953</v>
+        <v>210309.9924518901</v>
       </c>
       <c r="P286" t="n">
         <v>8900</v>
@@ -13644,10 +13644,10 @@
         <v>8</v>
       </c>
       <c r="N303" t="n">
-        <v>14822.378814083</v>
+        <v>14831.53974042</v>
       </c>
       <c r="O303" t="n">
-        <v>118579.030512664</v>
+        <v>118652.31792336</v>
       </c>
       <c r="P303" t="n">
         <v>24900</v>
@@ -14233,10 +14233,10 @@
         <v>20</v>
       </c>
       <c r="N316" t="n">
-        <v>12422.46300928</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O316" t="n">
-        <v>248449.2601856</v>
+        <v>248449.26026548</v>
       </c>
       <c r="P316" t="n">
         <v>19900</v>
@@ -14462,10 +14462,10 @@
         <v>67</v>
       </c>
       <c r="N321" t="n">
-        <v>3472.276393501</v>
+        <v>3472.2764071985</v>
       </c>
       <c r="O321" t="n">
-        <v>232642.518364567</v>
+        <v>232642.5192822995</v>
       </c>
       <c r="P321" t="n">
         <v>5900</v>
@@ -14688,10 +14688,10 @@
         <v>48</v>
       </c>
       <c r="N326" t="n">
-        <v>4371.1729731899</v>
+        <v>4371.1729736673</v>
       </c>
       <c r="O326" t="n">
-        <v>209816.3027131152</v>
+        <v>209816.3027360304</v>
       </c>
       <c r="P326" t="n">
         <v>8900</v>
@@ -16672,10 +16672,10 @@
         <v>172</v>
       </c>
       <c r="N370" t="n">
-        <v>1630.9251335113</v>
+        <v>1633.1055147059</v>
       </c>
       <c r="O370" t="n">
-        <v>280519.1229639436</v>
+        <v>280894.1485294148</v>
       </c>
       <c r="P370" t="n">
         <v>2500</v>
@@ -16810,10 +16810,10 @@
         <v>12</v>
       </c>
       <c r="N373" t="n">
-        <v>1550.1949625568</v>
+        <v>1550.1949638844</v>
       </c>
       <c r="O373" t="n">
-        <v>18602.3395506816</v>
+        <v>18602.3395666128</v>
       </c>
       <c r="P373" t="n">
         <v>2500</v>
@@ -16902,10 +16902,10 @@
         <v>1</v>
       </c>
       <c r="N375" t="n">
-        <v>2403.523063498</v>
+        <v>2404.4159026746</v>
       </c>
       <c r="O375" t="n">
-        <v>2403.523063498</v>
+        <v>2404.4159026746</v>
       </c>
       <c r="P375" t="n">
         <v>3500</v>
@@ -18508,10 +18508,10 @@
         <v>1</v>
       </c>
       <c r="N411" t="n">
-        <v>18071.26</v>
+        <v>18238.586481481</v>
       </c>
       <c r="O411" t="n">
-        <v>18071.26</v>
+        <v>18238.586481481</v>
       </c>
       <c r="P411" t="n">
         <v>23900</v>
@@ -20572,10 +20572,10 @@
         <v>22</v>
       </c>
       <c r="N459" t="n">
-        <v>4814.2633494176</v>
+        <v>4814.2633472037</v>
       </c>
       <c r="O459" t="n">
-        <v>105913.7936871872</v>
+        <v>105913.7936384814</v>
       </c>
       <c r="P459" t="n">
         <v>7900</v>
@@ -21176,10 +21176,10 @@
         <v>11</v>
       </c>
       <c r="N473" t="n">
-        <v>27123.764587738</v>
+        <v>27123.764576271</v>
       </c>
       <c r="O473" t="n">
-        <v>298361.410465118</v>
+        <v>298361.410338981</v>
       </c>
       <c r="P473" t="n">
         <v>44500</v>
@@ -22052,10 +22052,10 @@
         <v>8</v>
       </c>
       <c r="N493" t="n">
-        <v>8968.24</v>
+        <v>9120.244067796601</v>
       </c>
       <c r="O493" t="n">
-        <v>71745.92</v>
+        <v>72961.9525423728</v>
       </c>
       <c r="P493" t="n">
         <v>18600</v>
@@ -22581,10 +22581,10 @@
         <v>26</v>
       </c>
       <c r="N505" t="n">
-        <v>12981.59</v>
+        <v>13033.935120968</v>
       </c>
       <c r="O505" t="n">
-        <v>337521.34</v>
+        <v>338882.313145168</v>
       </c>
       <c r="P505" t="n">
         <v>21900</v>
@@ -24256,10 +24256,10 @@
         <v>29</v>
       </c>
       <c r="N542" t="n">
-        <v>9188.98</v>
+        <v>9254.3819928826</v>
       </c>
       <c r="O542" t="n">
-        <v>266480.42</v>
+        <v>268377.0777935954</v>
       </c>
       <c r="P542" t="n">
         <v>12900</v>
@@ -24988,10 +24988,10 @@
         <v>2</v>
       </c>
       <c r="N558" t="n">
-        <v>25534</v>
+        <v>25577.697661152</v>
       </c>
       <c r="O558" t="n">
-        <v>51068</v>
+        <v>51155.395322304</v>
       </c>
       <c r="P558" t="n">
         <v>40900</v>
@@ -25678,10 +25678,10 @@
         <v>7</v>
       </c>
       <c r="N573" t="n">
-        <v>3259.2102666667</v>
+        <v>3259.2102702703</v>
       </c>
       <c r="O573" t="n">
-        <v>22814.4718666669</v>
+        <v>22814.4718918921</v>
       </c>
       <c r="P573" t="n">
         <v>5300</v>
@@ -26008,10 +26008,10 @@
         <v>45</v>
       </c>
       <c r="N580" t="n">
-        <v>2260</v>
+        <v>2280.7339449541</v>
       </c>
       <c r="O580" t="n">
-        <v>101700</v>
+        <v>102633.0275229345</v>
       </c>
       <c r="P580" t="n">
         <v>3800</v>
@@ -27536,10 +27536,10 @@
         <v>14</v>
       </c>
       <c r="N613" t="n">
-        <v>9003</v>
+        <v>9018.1565656566</v>
       </c>
       <c r="O613" t="n">
-        <v>126042</v>
+        <v>126254.1919191924</v>
       </c>
       <c r="P613" t="n">
         <v>14900</v>
@@ -29376,10 +29376,10 @@
         <v>17</v>
       </c>
       <c r="N653" t="n">
-        <v>17992</v>
+        <v>18015.518954248</v>
       </c>
       <c r="O653" t="n">
-        <v>305864</v>
+        <v>306263.822222216</v>
       </c>
       <c r="P653" t="n">
         <v>28900</v>
@@ -30936,10 +30936,10 @@
         <v>8</v>
       </c>
       <c r="N687" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386972166</v>
       </c>
       <c r="O687" t="n">
-        <v>12128.309578836</v>
+        <v>12128.3095777328</v>
       </c>
       <c r="P687" t="n">
         <v>2300</v>
@@ -31074,10 +31074,10 @@
         <v>156</v>
       </c>
       <c r="N690" t="n">
-        <v>1907.3922142857</v>
+        <v>1909.6656257449</v>
       </c>
       <c r="O690" t="n">
-        <v>297553.1854285692</v>
+        <v>297907.8376162044</v>
       </c>
       <c r="P690" t="n">
         <v>2500</v>
@@ -31212,10 +31212,10 @@
         <v>272</v>
       </c>
       <c r="N693" t="n">
-        <v>1803.0176696833</v>
+        <v>1803.0176731553</v>
       </c>
       <c r="O693" t="n">
-        <v>490420.8061538576</v>
+        <v>490420.8070982416</v>
       </c>
       <c r="P693" t="n">
         <v>2500</v>
@@ -31258,10 +31258,10 @@
         <v>28</v>
       </c>
       <c r="N694" t="n">
-        <v>3306.5942675159</v>
+        <v>3306.5942492013</v>
       </c>
       <c r="O694" t="n">
-        <v>92584.6394904452</v>
+        <v>92584.63897763641</v>
       </c>
       <c r="P694" t="n">
         <v>4900</v>
@@ -31767,10 +31767,10 @@
         <v>1</v>
       </c>
       <c r="N705" t="n">
-        <v>1592.2892358079</v>
+        <v>1595.7734573304</v>
       </c>
       <c r="O705" t="n">
-        <v>1592.2892358079</v>
+        <v>1595.7734573304</v>
       </c>
       <c r="P705" t="n">
         <v>2500</v>
@@ -31949,10 +31949,10 @@
         <v>471</v>
       </c>
       <c r="N709" t="n">
-        <v>1259.2751809084</v>
+        <v>1259.2751822382</v>
       </c>
       <c r="O709" t="n">
-        <v>593118.6102078564</v>
+        <v>593118.6108341921</v>
       </c>
       <c r="P709" t="n">
         <v>1900</v>
@@ -32365,10 +32365,10 @@
         <v>11</v>
       </c>
       <c r="N718" t="n">
-        <v>13518</v>
+        <v>13521.774923206</v>
       </c>
       <c r="O718" t="n">
-        <v>148698</v>
+        <v>148739.524155266</v>
       </c>
       <c r="P718" t="n">
         <v>21900</v>
@@ -37042,10 +37042,10 @@
         <v>288</v>
       </c>
       <c r="N818" t="n">
-        <v>703.79458486774</v>
+        <v>703.7945831140599</v>
       </c>
       <c r="O818" t="n">
-        <v>202692.8404419091</v>
+        <v>202692.8399368493</v>
       </c>
       <c r="P818" t="n">
         <v>900</v>
@@ -41419,10 +41419,10 @@
         <v>1</v>
       </c>
       <c r="N910" t="n">
-        <v>7653.955</v>
+        <v>8747.3771428571</v>
       </c>
       <c r="O910" t="n">
-        <v>7653.955</v>
+        <v>8747.3771428571</v>
       </c>
       <c r="P910" t="n">
         <v>11900</v>
@@ -43695,10 +43695,10 @@
         <v>3</v>
       </c>
       <c r="N957" t="n">
-        <v>22042.26</v>
+        <v>23737.818461538</v>
       </c>
       <c r="O957" t="n">
-        <v>66126.78</v>
+        <v>71213.455384614</v>
       </c>
       <c r="P957" t="n">
         <v>56000</v>
@@ -43937,10 +43937,10 @@
         <v>3</v>
       </c>
       <c r="N962" t="n">
-        <v>10737.525135135</v>
+        <v>10737.525</v>
       </c>
       <c r="O962" t="n">
-        <v>32212.575405405</v>
+        <v>32212.575</v>
       </c>
       <c r="P962" t="n">
         <v>18900</v>
@@ -48185,10 +48185,10 @@
         <v>14</v>
       </c>
       <c r="N1051" t="n">
-        <v>22951.704377622</v>
+        <v>22951.704345992</v>
       </c>
       <c r="O1051" t="n">
-        <v>321323.861286708</v>
+        <v>321323.860843888</v>
       </c>
       <c r="P1051" t="n">
         <v>37900</v>
@@ -54439,10 +54439,10 @@
         <v>33</v>
       </c>
       <c r="N1187" t="n">
-        <v>7920</v>
+        <v>7953.8461538462</v>
       </c>
       <c r="O1187" t="n">
-        <v>261360</v>
+        <v>262476.9230769246</v>
       </c>
       <c r="P1187" t="n">
         <v>10500</v>
@@ -54537,10 +54537,10 @@
         <v>6</v>
       </c>
       <c r="N1189" t="n">
-        <v>7920</v>
+        <v>7971.0967741935</v>
       </c>
       <c r="O1189" t="n">
-        <v>47520</v>
+        <v>47826.580645161</v>
       </c>
       <c r="P1189" t="n">
         <v>10500</v>
@@ -54675,10 +54675,10 @@
         <v>25</v>
       </c>
       <c r="N1192" t="n">
-        <v>4576</v>
+        <v>4591.2533333333</v>
       </c>
       <c r="O1192" t="n">
-        <v>114400</v>
+        <v>114781.3333333325</v>
       </c>
       <c r="P1192" t="n">
         <v>5900</v>
@@ -54721,10 +54721,10 @@
         <v>24</v>
       </c>
       <c r="N1193" t="n">
-        <v>5280</v>
+        <v>5285.1815505397</v>
       </c>
       <c r="O1193" t="n">
-        <v>126720</v>
+        <v>126844.3572129528</v>
       </c>
       <c r="P1193" t="n">
         <v>6900</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -1818,10 +1818,10 @@
         <v>59</v>
       </c>
       <c r="N35" t="n">
-        <v>2474.7033461538</v>
+        <v>2474.7028512397</v>
       </c>
       <c r="O35" t="n">
-        <v>146007.4974230742</v>
+        <v>146007.4682231423</v>
       </c>
       <c r="P35" t="n">
         <v>4500</v>
@@ -1974,10 +1974,10 @@
         <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>3716.3301980198</v>
+        <v>3716.3301983471</v>
       </c>
       <c r="O39" t="n">
-        <v>7432.6603960396</v>
+        <v>7432.6603966942</v>
       </c>
       <c r="P39" t="n">
         <v>9500</v>
@@ -2091,10 +2091,10 @@
         <v>12</v>
       </c>
       <c r="N42" t="n">
-        <v>27000</v>
+        <v>27051.823416507</v>
       </c>
       <c r="O42" t="n">
-        <v>324000</v>
+        <v>324621.880998084</v>
       </c>
       <c r="P42" t="n">
         <v>30000</v>
@@ -2130,10 +2130,10 @@
         <v>18</v>
       </c>
       <c r="N43" t="n">
-        <v>21425.250901288</v>
+        <v>21333.69</v>
       </c>
       <c r="O43" t="n">
-        <v>385654.516223184</v>
+        <v>384006.42</v>
       </c>
       <c r="P43" t="n">
         <v>30000</v>
@@ -2211,10 +2211,10 @@
         <v>8</v>
       </c>
       <c r="N45" t="n">
-        <v>15403.521104651</v>
+        <v>15403.521169591</v>
       </c>
       <c r="O45" t="n">
-        <v>123228.168837208</v>
+        <v>123228.169356728</v>
       </c>
       <c r="P45" t="n">
         <v>33500</v>
@@ -2328,10 +2328,10 @@
         <v>7</v>
       </c>
       <c r="N48" t="n">
-        <v>14857.623287671</v>
+        <v>14857.623302752</v>
       </c>
       <c r="O48" t="n">
-        <v>104003.363013697</v>
+        <v>104003.363119264</v>
       </c>
       <c r="P48" t="n">
         <v>34900</v>
@@ -3395,10 +3395,10 @@
         <v>5</v>
       </c>
       <c r="N72" t="n">
-        <v>15711.963708609</v>
+        <v>15711.963537415</v>
       </c>
       <c r="O72" t="n">
-        <v>78559.818543045</v>
+        <v>78559.817687075</v>
       </c>
       <c r="P72" t="n">
         <v>28500</v>
@@ -5025,10 +5025,10 @@
         <v>11</v>
       </c>
       <c r="N110" t="n">
-        <v>27000</v>
+        <v>27118.421052632</v>
       </c>
       <c r="O110" t="n">
-        <v>297000</v>
+        <v>298302.631578952</v>
       </c>
       <c r="P110" t="n">
         <v>20000</v>
@@ -9941,10 +9941,10 @@
         <v>24</v>
       </c>
       <c r="N220" t="n">
-        <v>4937.3101888412</v>
+        <v>4937.3101890034</v>
       </c>
       <c r="O220" t="n">
-        <v>118495.4445321888</v>
+        <v>118495.4445360816</v>
       </c>
       <c r="P220" t="n">
         <v>7500</v>
@@ -10681,10 +10681,10 @@
         <v>50</v>
       </c>
       <c r="N237" t="n">
-        <v>13694.165945612</v>
+        <v>13593.35</v>
       </c>
       <c r="O237" t="n">
-        <v>684708.2972805999</v>
+        <v>679667.5</v>
       </c>
       <c r="P237" t="n">
         <v>25500</v>
@@ -11327,10 +11327,10 @@
         <v>4</v>
       </c>
       <c r="N252" t="n">
-        <v>2582.2546851654</v>
+        <v>2582.2546595174</v>
       </c>
       <c r="O252" t="n">
-        <v>10329.0187406616</v>
+        <v>10329.0186380696</v>
       </c>
       <c r="P252" t="n">
         <v>4500</v>
@@ -11747,10 +11747,10 @@
         <v>279</v>
       </c>
       <c r="N261" t="n">
-        <v>3158.8608437109</v>
+        <v>3158.8608442176</v>
       </c>
       <c r="O261" t="n">
-        <v>881322.1753953411</v>
+        <v>881322.1755367104</v>
       </c>
       <c r="P261" t="n">
         <v>5600</v>
@@ -12656,10 +12656,10 @@
         <v>23</v>
       </c>
       <c r="N281" t="n">
-        <v>3795.7100076628</v>
+        <v>3795.7100076717</v>
       </c>
       <c r="O281" t="n">
-        <v>87301.3301762444</v>
+        <v>87301.3301764491</v>
       </c>
       <c r="P281" t="n">
         <v>6200</v>
@@ -12876,10 +12876,10 @@
         <v>43</v>
       </c>
       <c r="N286" t="n">
-        <v>4890.9300570207</v>
+        <v>4890.9300571837</v>
       </c>
       <c r="O286" t="n">
-        <v>210309.9924518901</v>
+        <v>210309.9924588991</v>
       </c>
       <c r="P286" t="n">
         <v>8900</v>
@@ -13598,10 +13598,10 @@
         <v>29</v>
       </c>
       <c r="N302" t="n">
-        <v>3240.8500597015</v>
+        <v>3240.8500619195</v>
       </c>
       <c r="O302" t="n">
-        <v>93984.6517313435</v>
+        <v>93984.6517956655</v>
       </c>
       <c r="P302" t="n">
         <v>5200</v>
@@ -13644,10 +13644,10 @@
         <v>8</v>
       </c>
       <c r="N303" t="n">
-        <v>14831.53974042</v>
+        <v>14822.378811881</v>
       </c>
       <c r="O303" t="n">
-        <v>118652.31792336</v>
+        <v>118579.030495048</v>
       </c>
       <c r="P303" t="n">
         <v>24900</v>
@@ -14233,10 +14233,10 @@
         <v>20</v>
       </c>
       <c r="N316" t="n">
-        <v>12422.463013274</v>
+        <v>12422.46301728</v>
       </c>
       <c r="O316" t="n">
-        <v>248449.26026548</v>
+        <v>248449.2603456</v>
       </c>
       <c r="P316" t="n">
         <v>19900</v>
@@ -14462,10 +14462,10 @@
         <v>67</v>
       </c>
       <c r="N321" t="n">
-        <v>3472.2764071985</v>
+        <v>3472.2764292368</v>
       </c>
       <c r="O321" t="n">
-        <v>232642.5192822995</v>
+        <v>232642.5207588656</v>
       </c>
       <c r="P321" t="n">
         <v>5900</v>
@@ -14688,10 +14688,10 @@
         <v>48</v>
       </c>
       <c r="N326" t="n">
-        <v>4371.1729736673</v>
+        <v>4371.1729765349</v>
       </c>
       <c r="O326" t="n">
-        <v>209816.3027360304</v>
+        <v>209816.3028736752</v>
       </c>
       <c r="P326" t="n">
         <v>8900</v>
@@ -16672,10 +16672,10 @@
         <v>172</v>
       </c>
       <c r="N370" t="n">
-        <v>1633.1055147059</v>
+        <v>1630.9252455662</v>
       </c>
       <c r="O370" t="n">
-        <v>280894.1485294148</v>
+        <v>280519.1422373864</v>
       </c>
       <c r="P370" t="n">
         <v>2500</v>
@@ -16764,10 +16764,10 @@
         <v>29</v>
       </c>
       <c r="N372" t="n">
-        <v>1690.5726046512</v>
+        <v>1690.5719339623</v>
       </c>
       <c r="O372" t="n">
-        <v>49026.6055348848</v>
+        <v>49026.5860849067</v>
       </c>
       <c r="P372" t="n">
         <v>2900</v>
@@ -16810,10 +16810,10 @@
         <v>12</v>
       </c>
       <c r="N373" t="n">
-        <v>1550.1949638844</v>
+        <v>1550.1949858928</v>
       </c>
       <c r="O373" t="n">
-        <v>18602.3395666128</v>
+        <v>18602.3398307136</v>
       </c>
       <c r="P373" t="n">
         <v>2500</v>
@@ -16902,10 +16902,10 @@
         <v>1</v>
       </c>
       <c r="N375" t="n">
-        <v>2404.4159026746</v>
+        <v>2403.5234112326</v>
       </c>
       <c r="O375" t="n">
-        <v>2404.4159026746</v>
+        <v>2403.5234112326</v>
       </c>
       <c r="P375" t="n">
         <v>3500</v>
@@ -17792,10 +17792,10 @@
         <v>7</v>
       </c>
       <c r="N395" t="n">
-        <v>10034.5</v>
+        <v>10166.532894737</v>
       </c>
       <c r="O395" t="n">
-        <v>70241.5</v>
+        <v>71165.730263159</v>
       </c>
       <c r="P395" t="n">
         <v>12900</v>
@@ -19083,10 +19083,10 @@
         <v>6</v>
       </c>
       <c r="N424" t="n">
-        <v>7537.4724786325</v>
+        <v>7537.4727619048</v>
       </c>
       <c r="O424" t="n">
-        <v>45224.834871795</v>
+        <v>45224.8365714288</v>
       </c>
       <c r="P424" t="n">
         <v>8900</v>
@@ -19414,10 +19414,10 @@
         <v>83</v>
       </c>
       <c r="N432" t="n">
-        <v>2029.8742613636</v>
+        <v>2029.8742906178</v>
       </c>
       <c r="O432" t="n">
-        <v>168479.5636931788</v>
+        <v>168479.5661212774</v>
       </c>
       <c r="P432" t="n">
         <v>3600</v>
@@ -20090,10 +20090,10 @@
         <v>43</v>
       </c>
       <c r="N448" t="n">
-        <v>6207.9881978301</v>
+        <v>6207.9881950325</v>
       </c>
       <c r="O448" t="n">
-        <v>266943.4925066943</v>
+        <v>266943.4923863975</v>
       </c>
       <c r="P448" t="n">
         <v>9900</v>
@@ -20572,10 +20572,10 @@
         <v>22</v>
       </c>
       <c r="N459" t="n">
-        <v>4814.2633472037</v>
+        <v>4814.263336112</v>
       </c>
       <c r="O459" t="n">
-        <v>105913.7936384814</v>
+        <v>105913.793394464</v>
       </c>
       <c r="P459" t="n">
         <v>7900</v>
@@ -21309,10 +21309,10 @@
         <v>2</v>
       </c>
       <c r="N476" t="n">
-        <v>8332.7795945946</v>
+        <v>8332.7795901639</v>
       </c>
       <c r="O476" t="n">
-        <v>16665.5591891892</v>
+        <v>16665.5591803278</v>
       </c>
       <c r="P476" t="n">
         <v>14900</v>
@@ -21442,10 +21442,10 @@
         <v>16</v>
       </c>
       <c r="N479" t="n">
-        <v>1561.0125437573</v>
+        <v>1561.0077085243</v>
       </c>
       <c r="O479" t="n">
-        <v>24976.2007001168</v>
+        <v>24976.1233363888</v>
       </c>
       <c r="P479" t="n">
         <v>2900</v>
@@ -22581,10 +22581,10 @@
         <v>26</v>
       </c>
       <c r="N505" t="n">
-        <v>13033.935120968</v>
+        <v>12981.59</v>
       </c>
       <c r="O505" t="n">
-        <v>338882.313145168</v>
+        <v>337521.34</v>
       </c>
       <c r="P505" t="n">
         <v>21900</v>
@@ -24630,10 +24630,10 @@
         <v>63</v>
       </c>
       <c r="N550" t="n">
-        <v>3646</v>
+        <v>3656.7445972495</v>
       </c>
       <c r="O550" t="n">
-        <v>229698</v>
+        <v>230374.9096267185</v>
       </c>
       <c r="P550" t="n">
         <v>6900</v>
@@ -24712,10 +24712,10 @@
         <v>3</v>
       </c>
       <c r="N552" t="n">
-        <v>3486</v>
+        <v>3488.1801125704</v>
       </c>
       <c r="O552" t="n">
-        <v>10458</v>
+        <v>10464.5403377112</v>
       </c>
       <c r="P552" t="n">
         <v>6900</v>
@@ -24758,10 +24758,10 @@
         <v>152</v>
       </c>
       <c r="N553" t="n">
-        <v>1778.4728955224</v>
+        <v>1779.3581483325</v>
       </c>
       <c r="O553" t="n">
-        <v>270327.8801194048</v>
+        <v>270462.43854654</v>
       </c>
       <c r="P553" t="n">
         <v>4900</v>
@@ -24988,10 +24988,10 @@
         <v>2</v>
       </c>
       <c r="N558" t="n">
-        <v>25577.697661152</v>
+        <v>25534</v>
       </c>
       <c r="O558" t="n">
-        <v>51155.395322304</v>
+        <v>51068</v>
       </c>
       <c r="P558" t="n">
         <v>40900</v>
@@ -26975,10 +26975,10 @@
         <v>72</v>
       </c>
       <c r="N601" t="n">
-        <v>2252.3013646055</v>
+        <v>2252.3013888889</v>
       </c>
       <c r="O601" t="n">
-        <v>162165.698251596</v>
+        <v>162165.7000000008</v>
       </c>
       <c r="P601" t="n">
         <v>3900</v>
@@ -27165,10 +27165,10 @@
         <v>74</v>
       </c>
       <c r="N605" t="n">
-        <v>2328.1186316472</v>
+        <v>2328.1186298701</v>
       </c>
       <c r="O605" t="n">
-        <v>172280.7787418928</v>
+        <v>172280.7786103874</v>
       </c>
       <c r="P605" t="n">
         <v>4500</v>
@@ -27211,10 +27211,10 @@
         <v>10</v>
       </c>
       <c r="N606" t="n">
-        <v>21676</v>
+        <v>21700.382452193</v>
       </c>
       <c r="O606" t="n">
-        <v>216760</v>
+        <v>217003.82452193</v>
       </c>
       <c r="P606" t="n">
         <v>34900</v>
@@ -27536,10 +27536,10 @@
         <v>14</v>
       </c>
       <c r="N613" t="n">
-        <v>9018.1565656566</v>
+        <v>9003</v>
       </c>
       <c r="O613" t="n">
-        <v>126254.1919191924</v>
+        <v>126042</v>
       </c>
       <c r="P613" t="n">
         <v>14900</v>
@@ -27858,10 +27858,10 @@
         <v>47</v>
       </c>
       <c r="N620" t="n">
-        <v>4907.8228863636</v>
+        <v>4907.8230382775</v>
       </c>
       <c r="O620" t="n">
-        <v>230667.6756590892</v>
+        <v>230667.6827990425</v>
       </c>
       <c r="P620" t="n">
         <v>8200</v>
@@ -30519,10 +30519,10 @@
         <v>18</v>
       </c>
       <c r="N678" t="n">
-        <v>10713.21</v>
+        <v>10736.550326797</v>
       </c>
       <c r="O678" t="n">
-        <v>192837.78</v>
+        <v>193257.905882346</v>
       </c>
       <c r="P678" t="n">
         <v>20900</v>
@@ -30936,10 +30936,10 @@
         <v>8</v>
       </c>
       <c r="N687" t="n">
-        <v>1516.0386972166</v>
+        <v>1516.0386977679</v>
       </c>
       <c r="O687" t="n">
-        <v>12128.3095777328</v>
+        <v>12128.3095821432</v>
       </c>
       <c r="P687" t="n">
         <v>2300</v>
@@ -31028,10 +31028,10 @@
         <v>144</v>
       </c>
       <c r="N689" t="n">
-        <v>2458.5122572276</v>
+        <v>2458.5121994025</v>
       </c>
       <c r="O689" t="n">
-        <v>354025.7650407744</v>
+        <v>354025.75671396</v>
       </c>
       <c r="P689" t="n">
         <v>3500</v>
@@ -31166,10 +31166,10 @@
         <v>154</v>
       </c>
       <c r="N692" t="n">
-        <v>2079.3831463696</v>
+        <v>2079.3831437356</v>
       </c>
       <c r="O692" t="n">
-        <v>320225.0045409184</v>
+        <v>320225.0041352824</v>
       </c>
       <c r="P692" t="n">
         <v>2900</v>
@@ -31212,10 +31212,10 @@
         <v>272</v>
       </c>
       <c r="N693" t="n">
-        <v>1803.0176731553</v>
+        <v>1803.0177185792</v>
       </c>
       <c r="O693" t="n">
-        <v>490420.8070982416</v>
+        <v>490420.8194535424</v>
       </c>
       <c r="P693" t="n">
         <v>2500</v>
@@ -31350,10 +31350,10 @@
         <v>82</v>
       </c>
       <c r="N696" t="n">
-        <v>2108.8001384083</v>
+        <v>2108.8003733956</v>
       </c>
       <c r="O696" t="n">
-        <v>172921.6113494806</v>
+        <v>172921.6306184392</v>
       </c>
       <c r="P696" t="n">
         <v>2900</v>
@@ -31442,10 +31442,10 @@
         <v>66</v>
       </c>
       <c r="N698" t="n">
-        <v>3224.5700392597</v>
+        <v>3224.5700448934</v>
       </c>
       <c r="O698" t="n">
-        <v>212821.6225911402</v>
+        <v>212821.6229629644</v>
       </c>
       <c r="P698" t="n">
         <v>4500</v>
@@ -31767,10 +31767,10 @@
         <v>1</v>
       </c>
       <c r="N705" t="n">
-        <v>1595.7734573304</v>
+        <v>1592.2894481236</v>
       </c>
       <c r="O705" t="n">
-        <v>1595.7734573304</v>
+        <v>1592.2894481236</v>
       </c>
       <c r="P705" t="n">
         <v>2500</v>
@@ -31949,10 +31949,10 @@
         <v>471</v>
       </c>
       <c r="N709" t="n">
-        <v>1259.2751822382</v>
+        <v>1259.2752022675</v>
       </c>
       <c r="O709" t="n">
-        <v>593118.6108341921</v>
+        <v>593118.6202679925</v>
       </c>
       <c r="P709" t="n">
         <v>1900</v>
@@ -32365,10 +32365,10 @@
         <v>11</v>
       </c>
       <c r="N718" t="n">
-        <v>13521.774923206</v>
+        <v>13518</v>
       </c>
       <c r="O718" t="n">
-        <v>148739.524155266</v>
+        <v>148698</v>
       </c>
       <c r="P718" t="n">
         <v>21900</v>
@@ -34850,10 +34850,10 @@
         <v>30</v>
       </c>
       <c r="N771" t="n">
-        <v>1690.8700098184</v>
+        <v>1690.8700098765</v>
       </c>
       <c r="O771" t="n">
-        <v>50726.100294552</v>
+        <v>50726.100296295</v>
       </c>
       <c r="P771" t="n">
         <v>3000</v>
@@ -35144,10 +35144,10 @@
         <v>6</v>
       </c>
       <c r="N777" t="n">
-        <v>2270.3215151515</v>
+        <v>2270.3217241379</v>
       </c>
       <c r="O777" t="n">
-        <v>13621.929090909</v>
+        <v>13621.9303448274</v>
       </c>
       <c r="P777" t="n">
         <v>3900</v>
@@ -35188,10 +35188,10 @@
         <v>256</v>
       </c>
       <c r="N778" t="n">
-        <v>481.48790068997</v>
+        <v>481.48790045249</v>
       </c>
       <c r="O778" t="n">
-        <v>123260.9025766323</v>
+        <v>123260.9025158374</v>
       </c>
       <c r="P778" t="n">
         <v>650</v>
@@ -36023,10 +36023,10 @@
         <v>24</v>
       </c>
       <c r="N796" t="n">
-        <v>4032.3967801047</v>
+        <v>4032.3967716535</v>
       </c>
       <c r="O796" t="n">
-        <v>96777.5227225128</v>
+        <v>96777.52251968399</v>
       </c>
       <c r="P796" t="n">
         <v>4200</v>
@@ -36206,10 +36206,10 @@
         <v>154</v>
       </c>
       <c r="N800" t="n">
-        <v>517.29686746988</v>
+        <v>517.29687747036</v>
       </c>
       <c r="O800" t="n">
-        <v>79663.71759036151</v>
+        <v>79663.71913043543</v>
       </c>
       <c r="P800" t="n">
         <v>900</v>
@@ -37042,10 +37042,10 @@
         <v>288</v>
       </c>
       <c r="N818" t="n">
-        <v>703.7945831140599</v>
+        <v>703.79457726026</v>
       </c>
       <c r="O818" t="n">
-        <v>202692.8399368493</v>
+        <v>202692.8382509549</v>
       </c>
       <c r="P818" t="n">
         <v>900</v>
@@ -37693,10 +37693,10 @@
         <v>4</v>
       </c>
       <c r="N832" t="n">
-        <v>2501.3837931034</v>
+        <v>2501.3837572254</v>
       </c>
       <c r="O832" t="n">
-        <v>10005.5351724136</v>
+        <v>10005.5350289016</v>
       </c>
       <c r="P832" t="n">
         <v>4100</v>
@@ -40022,10 +40022,10 @@
         <v>5</v>
       </c>
       <c r="N881" t="n">
-        <v>2832.1961818182</v>
+        <v>2832.1965384615</v>
       </c>
       <c r="O881" t="n">
-        <v>14160.980909091</v>
+        <v>14160.9826923075</v>
       </c>
       <c r="P881" t="n">
         <v>12900</v>
@@ -41076,10 +41076,10 @@
         <v>10</v>
       </c>
       <c r="N903" t="n">
-        <v>16670.89</v>
+        <v>17351.334489796</v>
       </c>
       <c r="O903" t="n">
-        <v>166708.9</v>
+        <v>173513.34489796</v>
       </c>
       <c r="P903" t="n">
         <v>25500</v>
@@ -41125,10 +41125,10 @@
         <v>1</v>
       </c>
       <c r="N904" t="n">
-        <v>10084.09</v>
+        <v>10840.39675</v>
       </c>
       <c r="O904" t="n">
-        <v>10084.09</v>
+        <v>10840.39675</v>
       </c>
       <c r="P904" t="n">
         <v>17900</v>
@@ -41370,10 +41370,10 @@
         <v>7</v>
       </c>
       <c r="N909" t="n">
-        <v>9746.8802105263</v>
+        <v>9746.880217391301</v>
       </c>
       <c r="O909" t="n">
-        <v>68228.1614736841</v>
+        <v>68228.16152173911</v>
       </c>
       <c r="P909" t="n">
         <v>18500</v>
@@ -41955,10 +41955,10 @@
         <v>10</v>
       </c>
       <c r="N921" t="n">
-        <v>5430.86</v>
+        <v>5546.410212766</v>
       </c>
       <c r="O921" t="n">
-        <v>54308.6</v>
+        <v>55464.10212766</v>
       </c>
       <c r="P921" t="n">
         <v>13900</v>
@@ -43937,10 +43937,10 @@
         <v>3</v>
       </c>
       <c r="N962" t="n">
-        <v>10737.525</v>
+        <v>10737.524705882</v>
       </c>
       <c r="O962" t="n">
-        <v>32212.575</v>
+        <v>32212.574117646</v>
       </c>
       <c r="P962" t="n">
         <v>18900</v>
@@ -45389,10 +45389,10 @@
         <v>9</v>
       </c>
       <c r="N992" t="n">
-        <v>15033.815</v>
+        <v>15033.814705882</v>
       </c>
       <c r="O992" t="n">
-        <v>135304.335</v>
+        <v>135304.332352938</v>
       </c>
       <c r="P992" t="n">
         <v>19900</v>
@@ -45536,10 +45536,10 @@
         <v>4</v>
       </c>
       <c r="N995" t="n">
-        <v>8931.4411111111</v>
+        <v>8931.4411764706</v>
       </c>
       <c r="O995" t="n">
-        <v>35725.7644444444</v>
+        <v>35725.7647058824</v>
       </c>
       <c r="P995" t="n">
         <v>19900</v>
@@ -47725,10 +47725,10 @@
         <v>108</v>
       </c>
       <c r="N1041" t="n">
-        <v>1008.8110899183</v>
+        <v>1008.8107756233</v>
       </c>
       <c r="O1041" t="n">
-        <v>108951.5977111764</v>
+        <v>108951.5637673164</v>
       </c>
       <c r="P1041" t="n">
         <v>1500</v>
@@ -48185,10 +48185,10 @@
         <v>14</v>
       </c>
       <c r="N1051" t="n">
-        <v>22951.704345992</v>
+        <v>22951.704248927</v>
       </c>
       <c r="O1051" t="n">
-        <v>321323.860843888</v>
+        <v>321323.859484978</v>
       </c>
       <c r="P1051" t="n">
         <v>37900</v>
@@ -48328,10 +48328,10 @@
         <v>4</v>
       </c>
       <c r="N1054" t="n">
-        <v>1547.8829824561</v>
+        <v>1547.8830909091</v>
       </c>
       <c r="O1054" t="n">
-        <v>6191.5319298244</v>
+        <v>6191.5323636364</v>
       </c>
       <c r="P1054" t="n">
         <v>5500</v>
@@ -54439,10 +54439,10 @@
         <v>33</v>
       </c>
       <c r="N1187" t="n">
-        <v>7953.8461538462</v>
+        <v>7920</v>
       </c>
       <c r="O1187" t="n">
-        <v>262476.9230769246</v>
+        <v>261360</v>
       </c>
       <c r="P1187" t="n">
         <v>10500</v>
@@ -54537,10 +54537,10 @@
         <v>6</v>
       </c>
       <c r="N1189" t="n">
-        <v>7971.0967741935</v>
+        <v>7920</v>
       </c>
       <c r="O1189" t="n">
-        <v>47826.580645161</v>
+        <v>47520</v>
       </c>
       <c r="P1189" t="n">
         <v>10500</v>
@@ -54675,10 +54675,10 @@
         <v>25</v>
       </c>
       <c r="N1192" t="n">
-        <v>4591.2533333333</v>
+        <v>4576</v>
       </c>
       <c r="O1192" t="n">
-        <v>114781.3333333325</v>
+        <v>114400</v>
       </c>
       <c r="P1192" t="n">
         <v>5900</v>
@@ -57891,10 +57891,10 @@
         <v>5</v>
       </c>
       <c r="N1261" t="n">
-        <v>1319.3611070111</v>
+        <v>1319.3612448133</v>
       </c>
       <c r="O1261" t="n">
-        <v>6596.805535055501</v>
+        <v>6596.806224066499</v>
       </c>
       <c r="P1261" t="n">
         <v>3500</v>
